--- a/roles/platform-engineering/ladder.xlsx
+++ b/roles/platform-engineering/ladder.xlsx
@@ -901,7 +901,7 @@
       </c>
       <c r="D4" s="6" t="inlineStr">
         <is>
-          <t>proposed</t>
+          <t>OPS-31</t>
         </is>
       </c>
       <c r="E4" s="4" t="inlineStr">
@@ -1072,7 +1072,7 @@
       </c>
       <c r="D7" s="6" t="inlineStr">
         <is>
-          <t>proposed</t>
+          <t>OPS-32</t>
         </is>
       </c>
       <c r="E7" s="4" t="inlineStr">
@@ -2155,7 +2155,7 @@
       </c>
       <c r="D26" s="6" t="inlineStr">
         <is>
-          <t>proposed</t>
+          <t>SEC-18</t>
         </is>
       </c>
       <c r="E26" s="4" t="inlineStr">

--- a/roles/platform-engineering/ladder.xlsx
+++ b/roles/platform-engineering/ladder.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Overview" sheetId="1" state="visible" r:id="rId1"/>
     <sheet name="Competency Matrix" sheetId="2" state="visible" r:id="rId2"/>
     <sheet name="Rating Template" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="Sources" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Sources &amp; Theory" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -696,20 +696,21 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K38"/>
+  <dimension ref="A1:L38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
     <col width="18" customWidth="1" min="2" max="2"/>
     <col width="24" customWidth="1" min="3" max="3"/>
     <col width="12" customWidth="1" min="4" max="4"/>
-    <col width="40" customWidth="1" min="5" max="5"/>
-    <col width="55" customWidth="1" min="6" max="6"/>
+    <col width="45" customWidth="1" min="5" max="5"/>
+    <col width="45" customWidth="1" min="6" max="6"/>
     <col width="55" customWidth="1" min="7" max="7"/>
     <col width="55" customWidth="1" min="8" max="8"/>
     <col width="55" customWidth="1" min="9" max="9"/>
     <col width="55" customWidth="1" min="10" max="10"/>
     <col width="55" customWidth="1" min="11" max="11"/>
+    <col width="55" customWidth="1" min="12" max="12"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -735,35 +736,40 @@
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>Theory Anchor</t>
+          <t>What it covers</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
+          <t>Theory anchor &amp; why</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
           <t>E1</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>E2</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>E3</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>E4</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>E5</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>E6</t>
         </is>
@@ -792,37 +798,42 @@
       </c>
       <c r="E2" s="4" t="inlineStr">
         <is>
-          <t>Noda, Storey, Forsgren &amp; Greiler, "DevEx: What Actually Drives Productivity" (ACM Queue, 2023)</t>
+          <t>Uncovering user needs and validating problems through interviews, observation, and experimentation.</t>
         </is>
       </c>
       <c r="F2" s="4" t="inlineStr">
         <is>
-          <t>Depth: Shadows platform users and sits in on interviews and support rotations, writing up the friction they hit - reproduces a reported pain point end to end before proposing a fix, and asks users clarifying questions rather than assuming intent. Scope: observations feed a single task or bug report.</t>
+          <t>Noda, Storey, Forsgren &amp; Greiler, DevEx: What Actually Drives Productivity, ACM Queue 21(2) (2023) — grounds discovery in evidence about how developers actually experience the platform, not provider assumptions.</t>
         </is>
       </c>
       <c r="G2" s="4" t="inlineStr">
         <is>
-          <t>Depth: Runs structured interviews and support-channel reviews with the internal engineers using their component, turning raw notes into ranked friction lists the team acts on. Distinguishes what users say from what their workflow shows. Scope: the feedback loop for one component.</t>
+          <t>Depth: Runs scripted customer interviews and notes findings under a senior researcher's guidance. Evidenced by: Shadows platform users and sits in on interviews and support rotations, writing up the friction they hit. Scope: task.</t>
         </is>
       </c>
       <c r="H2" s="4" t="inlineStr">
         <is>
-          <t>Depth: Designs and runs the discovery process for a capability - recurring user touchpoints, journey maps, and a friction backlog that visibly drives the roadmap. Separates what users ask for from the workflow problem underneath and shows the evidence for the difference. Scope: all internal users of a platform capability.</t>
+          <t>Depth: Plans and conducts standard discovery for a feature, synthesizing themes with normal review. Evidenced by: Runs structured interviews and support-channel reviews with the internal engineers using their component. Scope: component.</t>
         </is>
       </c>
       <c r="I2" s="4" t="inlineStr">
         <is>
-          <t>Depth: Synthesizes research across several product teams into shared personas and friction maps other platform teams adopt, and coaches engineers on interview and synthesis technique instead of letting them guess. Scope: research practice spanning multiple platform teams.</t>
+          <t>Depth: Independently frames ambiguous problems, selects fitting methods, and separates signal from noise. Evidenced by: Designs and runs the discovery process for a capability. Scope: capability / domain (terminal level).</t>
         </is>
       </c>
       <c r="J2" s="4" t="inlineStr">
         <is>
-          <t>Depth: Establishes the organization's standing platform research practice - instrumented feedback loops, research repositories, and a cadence leaders cite in planning. Scope: how the whole platform organization learns about its users.</t>
+          <t>Depth: Designs the team's discovery approach and untangles findings others find contradictory. Evidenced by: Synthesizes research across several product teams into shared personas and friction maps other platform teams adopt. Scope: multiple teams.</t>
         </is>
       </c>
       <c r="K2" s="4" t="inlineStr">
         <is>
-          <t>Depth: Represents the internal developer experience at company level, bringing longitudinal user evidence that redirects company-scale platform investment. Scope: company-wide developer population.</t>
+          <t>Depth: Sets the org's research strategy and anticipates emerging customer needs before they surface. Evidenced by: Establishes the organization's standing platform research practice. Scope: organization.</t>
+        </is>
+      </c>
+      <c r="L2" s="4" t="inlineStr">
+        <is>
+          <t>Depth: Defines what rigorous product discovery means and shapes the discipline's practice externally. Evidenced by: Represents the internal developer experience at company level. Scope: company.</t>
         </is>
       </c>
     </row>
@@ -849,37 +860,42 @@
       </c>
       <c r="E3" s="4" t="inlineStr">
         <is>
-          <t>Forsgren, Humble &amp; Kim, *Accelerate* (2018)</t>
+          <t>Defining success metrics and interpreting product data to evaluate impact and guide iteration.</t>
         </is>
       </c>
       <c r="F3" s="4" t="inlineStr">
         <is>
-          <t>Depth: Pulls and charts existing adoption and usage numbers accurately when asked, and explains what each metric does and does not show. Scope: metrics for a single feature or task.</t>
+          <t>Forsgren, Humble &amp; Kim, Accelerate: The Science of Lean Software and DevOps (IT Revolution Press, 2018) — supplies the outcome metrics that make voluntary platform adoption measurable and defensible.</t>
         </is>
       </c>
       <c r="G3" s="4" t="inlineStr">
         <is>
-          <t>Depth: Instruments their component with adoption, retention, and satisfaction signals and reviews them in team rituals, spotting when a launch quietly failed to land. Scope: one component's metric set.</t>
+          <t>Depth: Pulls and reports defined product metrics under direction. Evidenced by: Pulls and charts existing adoption and usage numbers accurately when asked. Scope: task.</t>
         </is>
       </c>
       <c r="H3" s="4" t="inlineStr">
         <is>
-          <t>Depth: Defines the success metrics for a capability - voluntary adoption, time-to-onboard, retention, satisfaction - and kills or reworks features the numbers say are not earning use. Explicitly distinguishes mandated usage from chosen usage in reporting. Scope: a capability's product scorecard, reviewed with its internal customers.</t>
+          <t>Depth: Builds and interprets metric dashboards for a product with normal review. Evidenced by: Instruments their component with adoption, retention, and satisfaction signals. Scope: component.</t>
         </is>
       </c>
       <c r="I3" s="4" t="inlineStr">
         <is>
-          <t>Depth: Standardizes how several platform teams measure adoption so their numbers compose, and uses cross-team funnels to find where users leak off the paved road. Challenges vanity metrics in other teams' reviews. Scope: comparable measurement across multiple teams.</t>
+          <t>Depth: Independently designs metric frameworks and draws sound conclusions from messy data. Evidenced by: Defines the success metrics for a capability. Scope: capability / domain (terminal level).</t>
         </is>
       </c>
       <c r="J3" s="4" t="inlineStr">
         <is>
-          <t>Depth: Owns the organization's platform scorecard - the small set of adoption and developer-outcome metrics leadership steers by - and ties platform investment cases to it. Scope: organization-level platform health.</t>
+          <t>Depth: Defines the measurement model teams adopt and diagnoses misleading metrics others trust. Evidenced by: Standardizes how several platform teams measure adoption so their numbers compose. Scope: multiple teams.</t>
         </is>
       </c>
       <c r="K3" s="4" t="inlineStr">
         <is>
-          <t>Depth: Frames platform value in company terms - delivery performance, engineering cost, risk - and defends or redirects company-scale investment with that evidence. Scope: company investment decisions.</t>
+          <t>Depth: Sets product-analytics strategy across the org and anticipates which signals will matter. Evidenced by: Owns the organization's platform scorecard. Scope: organization.</t>
+        </is>
+      </c>
+      <c r="L3" s="4" t="inlineStr">
+        <is>
+          <t>Depth: Defines rigorous product measurement for the discipline and is cited externally on it. Evidenced by: Frames platform value in company terms. Scope: company.</t>
         </is>
       </c>
     </row>
@@ -906,37 +922,42 @@
       </c>
       <c r="E4" s="4" t="inlineStr">
         <is>
-          <t>Skelton &amp; Pais, *Team Topologies* (2019)</t>
+          <t>Scopes an internal platform to the smallest set of APIs, tools, docs, and services that accelerates its consumers - making explicit build-buy-adopt decisions and retiring surface area that no longer earns its maintenance cost.</t>
         </is>
       </c>
       <c r="F4" s="4" t="inlineStr">
         <is>
-          <t>Depth: Checks for an existing tool, service, or open-source option before writing new code and asks whether a proposed task is needed by a real user, citing the request that motivates it. Scope: their own task queue.</t>
+          <t>Skelton &amp; Pais, Team Topologies (IT Revolution, 2019) — defines the Thinnest Viable Platform -- the sizing test every build-buy-adopt and retirement decision here is judged against.</t>
         </is>
       </c>
       <c r="G4" s="4" t="inlineStr">
         <is>
-          <t>Depth: Proposes wrapping or configuring an existing service instead of building new when it meets the need, writing the comparison down and defending the removal of unused features. Scope: build-versus-reuse choices in one component.</t>
+          <t>Depth: Checks for an existing tool, service, or open-source option before writing new code and raises what they find; asks whether a proposed task serves a real user need. Evidenced by: Finds that an existing internal CLI already covers most of a proposed new tool's use case and raises it in planning instead of starting a new build. Scope: task.</t>
         </is>
       </c>
       <c r="H4" s="4" t="inlineStr">
         <is>
-          <t>Depth: Keeps a capability at its thinnest viable size - makes explicit build-buy-adopt decisions with documented reasoning, scopes to the thinnest version that serves proven demand (often a wrapper, a template, or documentation rather than new software), and retires surface area that no longer earns its maintenance cost. Scope: a capability's whole footprint.</t>
+          <t>Depth: Proposes wrapping or configuring an existing service instead of building new when it meets the need, writing the comparison down and defending removal of unused features in their own component. Evidenced by: Recommends adopting the org's existing secrets-manager service instead of building a bespoke wrapper for their component, and writes up the build-vs-adopt comparison that settles it. Scope: component.</t>
         </is>
       </c>
       <c r="I4" s="4" t="inlineStr">
         <is>
-          <t>Depth: Arbitrates overlap and sprawl between platform teams - merging duplicate offerings, cutting under-used surface, and setting the bar for what deserves to be platform at all. Scope: portfolio boundaries across multiple teams.</t>
+          <t>Depth: Keeps a whole capability at its thinnest viable size - makes explicit, documented build-buy-adopt decisions, ships the thinnest version that serves proven demand, and retires surface area whose maintenance cost exceeds its value. Evidenced by: Retires half a capability's plugin surface after usage telemetry shows only two of eight plugins are load-bearing, documenting the build-buy-adopt call for what stays. Scope: capability / domain (terminal level).</t>
         </is>
       </c>
       <c r="J4" s="4" t="inlineStr">
         <is>
-          <t>Depth: Shapes the organization's platform boundary - what the platform will and will not own versus product teams and vendors - and retires whole offerings whose maintenance cost exceeds their leverage. Scope: the organization's platform portfolio.</t>
+          <t>Depth: Arbitrates overlap and sprawl across teams - merges duplicate offerings, cuts under-used surface, and sets the bar for what deserves to be shared platform at all. Evidenced by: Merges two platform teams' overlapping feature-flag services into one and retires the duplicate. Scope: multiple teams.</t>
         </is>
       </c>
       <c r="K4" s="4" t="inlineStr">
         <is>
-          <t>Depth: Keeps the company's platform ambition honest - publicly weighing platform build-out against buying, adopting open source, or doing nothing, in principles executives reference. Scope: company build/buy/retire posture.</t>
+          <t>Depth: Shapes the organization's platform boundary - what the platform owns versus product teams versus vendors - and drives the organization to shed what it should not own. Evidenced by: Draws the line for what the platform organization owns versus what product teams should just buy, and gets teams to hand back components that crossed it. Scope: organization.</t>
+        </is>
+      </c>
+      <c r="L4" s="4" t="inlineStr">
+        <is>
+          <t>Depth: Sets the build-buy-adopt principles an entire company references, keeping company-scale platform investment proportional to the delivery it unlocks. Evidenced by: Kills a company-wide platform initiative whose maintenance cost has outgrown the delivery it unlocks, over objections that the build already happened. Scope: company.</t>
         </is>
       </c>
     </row>
@@ -963,37 +984,42 @@
       </c>
       <c r="E5" s="4" t="inlineStr">
         <is>
-          <t>Perri, *Escaping the Build Trap* (2018)</t>
+          <t>Sequencing initiatives across products and horizons against goals, capacity, and dependencies.</t>
         </is>
       </c>
       <c r="F5" s="4" t="inlineStr">
         <is>
-          <t>Depth: Explains why their current task is on the roadmap and which named internal customer it serves; flags when a task seems disconnected from user need. Scope: their own task queue.</t>
+          <t>Perri, Escaping the Build Trap: How Effective Product Management Creates Real Value (O'Reilly, 2018) — holds the platform roadmap to outcome-over-output product discipline rather than an infrastructure ticket queue.</t>
         </is>
       </c>
       <c r="G5" s="4" t="inlineStr">
         <is>
-          <t>Depth: Sequences their component's backlog by user impact - writes short proposals that weigh demand evidence against effort and negotiates scope with their lead. Scope: one component's roadmap.</t>
+          <t>Depth: Maintains roadmap items and updates status under guidance. Evidenced by: Explains why their current task is on the roadmap. Scope: task.</t>
         </is>
       </c>
       <c r="H5" s="4" t="inlineStr">
         <is>
-          <t>Depth: Owns the roadmap for a platform capability - balances new features, migrations, deprecations, and operational debt with explicit trade-off reasoning, and says no to requests with a documented rationale that users accept. Scope: a capability across its customer teams.</t>
+          <t>Depth: Builds and sequences a credible roadmap for one product with normal review. Evidenced by: Sequences their component's backlog by user impact. Scope: component.</t>
         </is>
       </c>
       <c r="I5" s="4" t="inlineStr">
         <is>
-          <t>Depth: Aligns roadmaps across platform teams - surfaces collisions and gaps between team plans and brokers the sequencing that unblocks shared bets. Scope: multi-team planning cycles.</t>
+          <t>Depth: Independently balances competing priorities and replans confidently under shifting constraints. Evidenced by: Owns the roadmap for a platform capability. Scope: capability / domain (terminal level).</t>
         </is>
       </c>
       <c r="J5" s="4" t="inlineStr">
         <is>
-          <t>Depth: Drives the platform organization's investment strategy - the annual plan's biggest items trace to cases they built, including the ones that redirect headcount. Scope: organization.</t>
+          <t>Depth: Designs the planning approach others use and resolves cross-team portfolio conflicts. Evidenced by: Aligns roadmaps across platform teams. Scope: multiple teams.</t>
         </is>
       </c>
       <c r="K5" s="4" t="inlineStr">
         <is>
-          <t>Depth: Sets multi-year platform direction for the company - decides which capabilities the company builds, buys, or retires, and the bets hold up over years. Scope: company-wide.</t>
+          <t>Depth: Sets portfolio planning strategy and foresees where investment should shift next. Evidenced by: Drives the platform organization's investment strategy. Scope: organization.</t>
+        </is>
+      </c>
+      <c r="L5" s="4" t="inlineStr">
+        <is>
+          <t>Depth: Defines portfolio-planning best practice for the field and is recognized for it. Evidenced by: Sets multi-year platform direction for the company. Scope: company.</t>
         </is>
       </c>
     </row>
@@ -1020,37 +1046,42 @@
       </c>
       <c r="E6" s="4" t="inlineStr">
         <is>
-          <t>Spotify Engineering, "How We Use Golden Paths to Solve Fragmentation in Our Software Ecosystem" (2020)</t>
+          <t>Build self-service internal platforms and paved paths that streamline delivery.</t>
         </is>
       </c>
       <c r="F6" s="4" t="inlineStr">
         <is>
-          <t>Depth: Follows the golden path as a real user would and reports exactly where it breaks - files precise friction reports against templates, docs, and starter kits. Scope: their own use of the paved road.</t>
+          <t>Spotify Engineering, How We Use Golden Paths to Solve Fragmentation in Our Software Ecosystem (Spotify Engineering Blog, 2020) — the named industry pattern this competency's templates, defaults, and escape hatches implement.</t>
         </is>
       </c>
       <c r="G6" s="4" t="inlineStr">
         <is>
-          <t>Depth: Builds and maintains golden-path assets for their component - templates, scaffolding, and starter repos kept working, current, and tested - and fixes path breakages users report within the team's SLA. Scope: one segment of the paved road.</t>
+          <t>Depth: Maintains existing self-service platform components under review, addressing documented user requests. Evidenced by: Follows the golden path as a real user would and reports exactly where it breaks. Scope: task.</t>
         </is>
       </c>
       <c r="H6" s="4" t="inlineStr">
         <is>
-          <t>Depth: Designs a golden path for a whole use case end to end - from repo creation to production - that a new team completes without hand-holding, with visible escape hatches that are not the default. Makes the paved road easier than the workaround rather than mandating it, and tracks completion rates and drop-off points. Scope: the default path for every team using the capability.</t>
+          <t>Depth: Independently builds and supports standard platform capabilities and templates for routine developer needs with review. Evidenced by: Builds and maintains golden-path assets for their component. Scope: component.</t>
         </is>
       </c>
       <c r="I6" s="4" t="inlineStr">
         <is>
-          <t>Depth: Reconciles golden paths across teams into coherent journeys, deciding where paths diverge legitimately versus where fragmentation is accidental, and reviews new paths before launch. Scope: the portfolio of paths across multiple platform teams.</t>
+          <t>Depth: Designs self-service workflows for ambiguous needs, reducing friction and resolving hard abstraction and adoption issues. Evidenced by: Designs a golden path for a whole use case end to end. Scope: capability / domain (terminal level).</t>
         </is>
       </c>
       <c r="J6" s="4" t="inlineStr">
         <is>
-          <t>Depth: Defines the organization's paved-road strategy - which paths exist, what support each tier gets, and how off-road teams re-board - and drives the long tail of snowflake systems onto supported paths. Scope: organization-wide path portfolio.</t>
+          <t>Depth: Defines platform architecture and golden paths others adopt, solving deep developer-experience and leverage problems. Evidenced by: Reconciles golden paths across teams into coherent journeys. Scope: multiple teams.</t>
         </is>
       </c>
       <c r="K6" s="4" t="inlineStr">
         <is>
-          <t>Depth: Makes the paved road the company default by economics and quality, not policy - visible in most new services starting on-path without a mandate. Scope: company-wide engineering practice.</t>
+          <t>Depth: Sets organization-wide platform strategy, anticipating how developer-experience engineering should evolve. Evidenced by: Defines the organization's paved-road strategy. Scope: organization.</t>
+        </is>
+      </c>
+      <c r="L6" s="4" t="inlineStr">
+        <is>
+          <t>Depth: Defines what excellent platform engineering means for the field, shaping industry developer-experience practice. Evidenced by: Makes the paved road the company default by economics and quality, not policy. Scope: company.</t>
         </is>
       </c>
     </row>
@@ -1077,37 +1108,42 @@
       </c>
       <c r="E7" s="4" t="inlineStr">
         <is>
-          <t>Skelton &amp; Pais, *Team Topologies* (2019), applying Sweller's cognitive load theory (1988)</t>
+          <t>Designs tooling, interfaces, and abstractions to minimize the extraneous cognitive load imposed on the teams that consume them - deciding deliberately what consumers must and must not need to know, and measuring the load imposed.</t>
         </is>
       </c>
       <c r="F7" s="4" t="inlineStr">
         <is>
-          <t>Depth: Names the exact docs, errors, and setup steps that forced them to understand internals a user should not need, and files concrete simplification issues. Scope: workflows they personally execute.</t>
+          <t>Sweller, Cognitive Load During Problem Solving: Effects on Learning, Cognitive Science 12(2), 257-285 (1988) — makes load reduction the platform's defining purpose rather than optional polish.</t>
         </is>
       </c>
       <c r="G7" s="4" t="inlineStr">
         <is>
-          <t>Depth: Reduces the concepts and steps a user must hold to use their component - collapsing configuration, defaulting decisions, rewriting errors to say what to do next - and shows the before/after. Scope: one component's user-facing surface.</t>
+          <t>Depth: Names the exact docs, errors, and setup steps that forced them to understand internals a consumer should not need, and files concrete simplification issues. Evidenced by: Flags that provisioning a database requires reading the underlying Terraform module's internals just to fill in one required field, and files the doc fix. Scope: task.</t>
         </is>
       </c>
       <c r="H7" s="4" t="inlineStr">
         <is>
-          <t>Depth: Designs a capability's abstractions around what users must not have to know - a first-time user succeeds without reading internals - measuring load with time-to-first-success and support-ticket themes and treating regressions as defects. Scope: a capability's entire developer-facing surface.</t>
+          <t>Depth: Reduces the concepts and steps a consumer must hold to use their component - collapsing configuration, defaulting decisions, rewriting errors to say what to do next - and shows the before/after. Evidenced by: Collapses a twelve-field service-creation form down to two required fields by defaulting the rest, and shows the before/after time-to-first-deploy. Scope: component.</t>
         </is>
       </c>
       <c r="I7" s="4" t="inlineStr">
         <is>
-          <t>Depth: Audits cognitive load across team boundaries - quantifies onboarding time, concepts-to-learn, and ticket themes - and drives the cross-team simplifications no single team could make. Scope: workflows spanning multiple platform teams.</t>
+          <t>Depth: Designs a capability's abstractions around what consumers must not have to know, so a first-time user succeeds without reading internals; measures load with time-to-first-success and support-ticket themes and treats regressions as defects. Evidenced by: Rewrites a capability's onboarding so a first-time consumer ships without reading the implementation, tracking time-to-first-success as the load metric. Scope: capability / domain (terminal level).</t>
         </is>
       </c>
       <c r="J7" s="4" t="inlineStr">
         <is>
-          <t>Depth: Makes cognitive load a first-class organizational measure - sets load budgets for what a product team must and must not need to know to ship, and vetoes platform designs that externalize complexity onto product teams. Scope: the platform organization's whole surface area.</t>
+          <t>Depth: Audits cognitive load across team boundaries - quantifying onboarding time, concepts-to-learn, and ticket themes - and drives the cross-boundary simplifications no single team could make. Evidenced by: Finds three teams independently solved the same secrets-rotation problem because none could see the others' internals, and drives the shared fix across all three. Scope: multiple teams.</t>
         </is>
       </c>
       <c r="K7" s="4" t="inlineStr">
         <is>
-          <t>Depth: Shapes company technology and team-boundary choices explicitly around team cognitive load, arguing in writing for fewer, deeper abstractions over sprawling optionality. Scope: company operating model.</t>
+          <t>Depth: Makes cognitive load a first-class organizational measure with explicit load budgets, vetoing designs that externalize complexity onto consuming teams. Evidenced by: Sets an explicit cognitive-load budget per platform surface and vetoes a design that would have pushed new required concepts onto every consuming team. Scope: organization.</t>
+        </is>
+      </c>
+      <c r="L7" s="4" t="inlineStr">
+        <is>
+          <t>Depth: Shapes company-level technology and team-boundary choices explicitly around team cognitive load, arguing for fewer, deeper abstractions over sprawling optionality. Evidenced by: Argues successfully against a company-wide multi-cloud push on cognitive-load grounds -- fewer, deeper abstractions over optionality -- and the simpler single-cloud default ships instead. Scope: company.</t>
         </is>
       </c>
     </row>
@@ -1134,37 +1170,42 @@
       </c>
       <c r="E8" s="4" t="inlineStr">
         <is>
-          <t>Conway, "How Do Committees Invent?" (Datamation, 1968)</t>
+          <t>Structures software — modules, boundaries, interfaces.</t>
         </is>
       </c>
       <c r="F8" s="4" t="inlineStr">
         <is>
-          <t>Depth: Explains the platform's architecture in their own words and navigates its diagrams to find the code that matters for a task; implements designs specified by others, asking questions that surface hidden assumptions. Scope: implements within an existing design.</t>
+          <t>Conway, How Do Committees Invent?, Datamation 14(4), 28-31 (1968) — platform architecture and team boundaries must be designed together, or Conway's Law designs them for you.</t>
         </is>
       </c>
       <c r="G8" s="4" t="inlineStr">
         <is>
-          <t>Depth: Designs a component within an established architecture, writing a short design note that names the alternatives considered, and spots when a change fights the existing structure. Scope: one component's internal design.</t>
+          <t>Depth: Implements designs specified by others; asks why, not just how. Evidenced by: Explains the platform's architecture in their own words. Scope: task.</t>
         </is>
       </c>
       <c r="H8" s="4" t="inlineStr">
         <is>
-          <t>Depth: Selects patterns by trade-off in design docs that name alternatives, failure modes, and evolution paths - designs multi-tenant platform services for isolation, quota, and noisy-neighbor behavior, and catches coupling and scaling problems in others' designs before build. Scope: owns architecture for a capability and runs its design reviews.</t>
+          <t>Depth: Designs sound components; understands coupling, cohesion, interface design. Evidenced by: Designs a component within an established architecture. Scope: component.</t>
         </is>
       </c>
       <c r="I8" s="4" t="inlineStr">
         <is>
-          <t>Depth: Drives designs that cut across several teams' systems - shared control planes, tenancy models, extension points - and gets them agreed in writing. Scope: architecture spanning multiple teams' services.</t>
+          <t>Depth: Designs systems for evolution: clean seams, versioned interfaces, replaceable parts. Evidenced by: Selects patterns by trade-off in design docs that name alternatives, failure modes, and evolution paths. Scope: capability / domain (terminal level).</t>
         </is>
       </c>
       <c r="J8" s="4" t="inlineStr">
         <is>
-          <t>Depth: Sets the architectural direction the platform organization builds against and removes the systemic obstacles - legacy coupling, ownership gaps - that block it. Scope: organization-wide platform architecture.</t>
+          <t>Depth: Mastery of architecture for complex systems; sets patterns and prevents drift. Evidenced by: Drives designs that cut across several teams' systems. Scope: multiple teams.</t>
         </is>
       </c>
       <c r="K8" s="4" t="inlineStr">
         <is>
-          <t>Depth: Makes the company's foundational architecture bets - the small number of structural decisions everything else assumes - and answers for the ones that fail. Scope: company architecture.</t>
+          <t>Depth: Sets multi-year architecture direction across the org. Evidenced by: Sets the architectural direction the platform organization builds against. Scope: organization.</t>
+        </is>
+      </c>
+      <c r="L8" s="4" t="inlineStr">
+        <is>
+          <t>Depth: Authoritative and externally credible; defines architectural approach others follow. Evidenced by: Makes the company's foundational architecture bets. Scope: company.</t>
         </is>
       </c>
     </row>
@@ -1191,37 +1232,42 @@
       </c>
       <c r="E9" s="4" t="inlineStr">
         <is>
-          <t>Winters, Manshreck &amp; Wright, *Software Engineering at Google* (2020) - Hyrum's Law</t>
+          <t>Designs clean, durable interfaces between systems.</t>
         </is>
       </c>
       <c r="F9" s="4" t="inlineStr">
         <is>
-          <t>Depth: Uses the platform's APIs correctly from documentation alone and files precise reports where docs and behavior diverge; small additions match naming and error conventions without being told. Scope: consumes and extends interfaces on assigned tasks.</t>
+          <t>Winters, Manshreck &amp; Wright, Software Engineering at Google: Lessons Learned from Programming Over Time (O'Reilly, 2020) — justifies treating interfaces as long-lived contracts and breaking changes as incidents.</t>
         </is>
       </c>
       <c r="G9" s="4" t="inlineStr">
         <is>
-          <t>Depth: Extends a component's interface without breaking consumers - additive changes, correct versioning, honest error messages - and writes contract tests for the behavior promised. Scope: one component's public surface.</t>
+          <t>Depth: Understands HTTP/REST and the deploy pipeline; makes guided changes. Evidenced by: Uses the platform's APIs correctly from documentation alone. Scope: task.</t>
         </is>
       </c>
       <c r="H9" s="4" t="inlineStr">
         <is>
-          <t>Depth: Designs a capability's interface as a long-lived product contract - consistent naming, misuse-resistant defaults, explicit versioning and compatibility guarantees, errors a user can act on without reading source - and treats a breaking change to users as an incident. Reviews proposed interfaces for what users will accidentally depend on. Scope: the contract surface of a capability and its review bar.</t>
+          <t>Depth: Designs clean APIs; understands rate limits, retries, timeouts, idempotency. Evidenced by: Extends a component's interface without breaking consumers. Scope: component.</t>
         </is>
       </c>
       <c r="I9" s="4" t="inlineStr">
         <is>
-          <t>Depth: Aligns interface conventions across several teams' APIs so the platform feels like one product, and adjudicates breaking-change disputes between producers and consumers. Scope: interface consistency across multiple teams.</t>
+          <t>Depth: Designs services for scale and cost; understands distributed failure modes. Evidenced by: Designs a capability's interface as a long-lived product contract. Scope: capability / domain (terminal level).</t>
         </is>
       </c>
       <c r="J9" s="4" t="inlineStr">
         <is>
-          <t>Depth: Owns the organization's interface standards - versioning policy, deprecation windows, compatibility rules - and the review mechanism that enforces them without bottlenecking teams. Scope: organization-wide interface governance.</t>
+          <t>Depth: Expert in platform/service design (multi-tenancy, capacity, shared services). Evidenced by: Aligns interface conventions across several teams' APIs so the platform feels like one product. Scope: multiple teams.</t>
         </is>
       </c>
       <c r="K9" s="4" t="inlineStr">
         <is>
-          <t>Depth: Sets the company's contract with its developers - which guarantees the company makes, for how long, to whom - and the fundamental interfaces carry their design signature for years. Scope: company-level contracts.</t>
+          <t>Depth: Sets interface standards used across the org. Evidenced by: Owns the organization's interface standards. Scope: organization.</t>
+        </is>
+      </c>
+      <c r="L9" s="4" t="inlineStr">
+        <is>
+          <t>Depth: Defines company-wide API approach; trusted with irreversible interface bets. Evidenced by: Sets the company's contract with its developers. Scope: company.</t>
         </is>
       </c>
     </row>
@@ -1248,37 +1294,42 @@
       </c>
       <c r="E10" s="4" t="inlineStr">
         <is>
-          <t>Fowler, *Refactoring* (2nd ed., 2018)</t>
+          <t>Keeps code healthy, modular and maintainable.</t>
         </is>
       </c>
       <c r="F10" s="4" t="inlineStr">
         <is>
-          <t>Depth: Ships small, working changes that follow the codebase's conventions and pass review with minor feedback - readable diffs, honest naming - and responds to review by fixing the class of problem, not just the instance. Scope: task-sized changes with guidance.</t>
+          <t>Fowler, Refactoring: Improving the Design of Existing Code, 2nd Edition (Addison-Wesley, 2018) — sets the craft bar for platform code that many teams depend on.</t>
         </is>
       </c>
       <c r="G10" s="4" t="inlineStr">
         <is>
-          <t>Depth: Ships production-quality code independently - handles error paths, concurrency, and upgrade safety in platform code other teams depend on - and leaves code measurably better in the course of feature work without being asked. Scope: the components they own.</t>
+          <t>Depth: Writes functional, readable code; uses version control correctly; responds well to review. Evidenced by: Ships small, working changes that follow the codebase's conventions and pass review with minor feedback. Scope: task.</t>
         </is>
       </c>
       <c r="H10" s="4" t="inlineStr">
         <is>
-          <t>Depth: Writes the code others study to learn how it is done here - reference implementations, hardened shared libraries, tricky migration code - and holds the quality bar for a capability, judging when good-enough is correct and saying so. Scope: a capability's codebase, including its shared libraries.</t>
+          <t>Depth: Writes clean, documented, modular code; gives useful review feedback. Evidenced by: Ships production-quality code independently. Scope: component.</t>
         </is>
       </c>
       <c r="I10" s="4" t="inlineStr">
         <is>
-          <t>Depth: Raises the code-health baseline across teams - shared linting, library patterns, exemplar code others copy - measured by falling defect and review-cycle trends, and personally unblocks the hardest technical problems wherever they sit. Scope: multiple teams' codebases.</t>
+          <t>Depth: Designs for maintainability; leads refactors of problem areas; review feedback teaches. Evidenced by: Writes the code others study to learn how it is done here. Scope: capability / domain (terminal level).</t>
         </is>
       </c>
       <c r="J10" s="4" t="inlineStr">
         <is>
-          <t>Depth: Defines what code quality means for the organization - the standards, tooling, and paved-road defaults that make the good way the easy way - and shows the results in delivery data. Scope: organization-wide engineering quality.</t>
+          <t>Depth: Expert in code health at scale (shared libraries, deprecations, large migrations). Evidenced by: Raises the code-health baseline across teams. Scope: multiple teams.</t>
         </is>
       </c>
       <c r="K10" s="4" t="inlineStr">
         <is>
-          <t>Depth: Holds the company's long-horizon code health against short-term pressure, publicly making the economic case for maintenance investment, and still writes code in the highest-leverage places. Scope: company code health.</t>
+          <t>Depth: Shapes org-wide engineering standards for long-lived codebases. Evidenced by: Defines what code quality means for the organization. Scope: organization.</t>
+        </is>
+      </c>
+      <c r="L10" s="4" t="inlineStr">
+        <is>
+          <t>Depth: Defines what good engineering looks like company-wide; externally recognized. Evidenced by: Holds the company's long-horizon code health against short-term pressure. Scope: company.</t>
         </is>
       </c>
     </row>
@@ -1305,37 +1356,42 @@
       </c>
       <c r="E11" s="4" t="inlineStr">
         <is>
-          <t>Sadowski et al., "Modern Code Review: A Case Study at Google" (ICSE-SEIP, 2018)</t>
+          <t>Reads, reasons about and reviews others' code.</t>
         </is>
       </c>
       <c r="F11" s="4" t="inlineStr">
         <is>
-          <t>Depth: Reviews peers' changes for readability and test coverage and asks genuine questions; responds to feedback on their own changes without defensiveness. Scope: changes within their team.</t>
+          <t>Google, Engineering Practices Documentation: How to Do a Code Review (accessed 2026-07) — grounds the progression from catching defects to calibrating review culture.</t>
         </is>
       </c>
       <c r="G11" s="4" t="inlineStr">
         <is>
-          <t>Depth: Gives reviews that catch real defects - correctness, error handling, compatibility - in actionable, kind comments, and distinguishes blocking issues from preferences explicitly. Scope: their component and its neighbors.</t>
+          <t>Depth: Navigates the codebase and understands code shown; reviews small changes. Evidenced by: Reviews peers' changes for readability and test coverage and asks genuine questions. Scope: task.</t>
         </is>
       </c>
       <c r="H11" s="4" t="inlineStr">
         <is>
-          <t>Depth: Reviews for systemic risk, not just correctness - catches designs-in-disguise, breaking changes to platform users, and operational hazards - and their comments teach the principle behind the correction; engineers seek their review by choice. Scope: review authority across a capability.</t>
+          <t>Depth: Independently understands unfamiliar code; gives timely, specific review feedback. Evidenced by: Gives reviews that catch real defects. Scope: component.</t>
         </is>
       </c>
       <c r="I11" s="4" t="inlineStr">
         <is>
-          <t>Depth: Calibrates review culture across teams - sets what blocks a merge platform-wide, coaches reviewers, and steps into contentious reviews as the tiebreaker whose reasoning both sides accept. Scope: multiple teams' review culture.</t>
+          <t>Depth: Quickly grasps complex/legacy systems; reviews raise the bar across a domain. Evidenced by: Reviews for systemic risk, not just correctness. Scope: capability / domain (terminal level).</t>
         </is>
       </c>
       <c r="J11" s="4" t="inlineStr">
         <is>
-          <t>Depth: Designs the organization's quality gates - decides where human review, automation, and ownership boundaries sit so review load scales with the organization. Scope: organization.</t>
+          <t>Depth: Expert at reviewing high-risk changes; review standards spread across teams. Evidenced by: Calibrates review culture across teams. Scope: multiple teams.</t>
         </is>
       </c>
       <c r="K11" s="4" t="inlineStr">
         <is>
-          <t>Depth: Reviews the changes that change the company - the riskiest cross-cutting designs and migrations route to them by reputation, and their judgment is treated as the final technical check. Scope: company.</t>
+          <t>Depth: Authority on review practice org-wide. Evidenced by: Designs the organization's quality gates. Scope: organization.</t>
+        </is>
+      </c>
+      <c r="L11" s="4" t="inlineStr">
+        <is>
+          <t>Depth: Defines what good review looks like; shapes industry-facing practice. Evidenced by: Reviews the changes that change the company. Scope: company.</t>
         </is>
       </c>
     </row>
@@ -1362,37 +1418,42 @@
       </c>
       <c r="E12" s="4" t="inlineStr">
         <is>
-          <t>Cohn (2009) as refined by Vocke, "The Practical Test Pyramid" (2018)</t>
+          <t>Designs tests that give real confidence to ship.</t>
         </is>
       </c>
       <c r="F12" s="4" t="inlineStr">
         <is>
-          <t>Depth: Writes unit tests that pin the behavior of their change, including the failure path, and runs the affected suite before requesting review; reproduces a bug with a failing test before fixing it. Scope: tests for their own tasks.</t>
+          <t>Cohn, Succeeding with Agile: Software Development Using Scrum (Addison-Wesley, 2009) — gives the coverage-balance and contract-testing discipline platform release confidence rests on.</t>
         </is>
       </c>
       <c r="G12" s="4" t="inlineStr">
         <is>
-          <t>Depth: Balances unit, integration, and end-to-end coverage for their component and fixes flaky tests instead of retrying them, keeping the suite fast and trustworthy. Scope: one component's test strategy.</t>
+          <t>Depth: Writes unit tests with guidance; tests own changes before merging. Evidenced by: Writes unit tests that pin the behavior of their change, including the failure path. Scope: task.</t>
         </is>
       </c>
       <c r="H12" s="4" t="inlineStr">
         <is>
-          <t>Depth: Designs the verification strategy for a capability - contract tests on its API, upgrade and rollback tests, failure injection where users would feel it - and blocks releases the strategy does not cover, deleting low-value tests as readily as adding good ones. Scope: a capability's release confidence.</t>
+          <t>Depth: Applies the testing pyramid; everything shipped arrives tested; mocks dependencies sensibly. Evidenced by: Balances unit, integration, and end-to-end coverage for their component. Scope: component.</t>
         </is>
       </c>
       <c r="I12" s="4" t="inlineStr">
         <is>
-          <t>Depth: Builds test infrastructure several teams rely on - shared harnesses, ephemeral environments, contract-test brokers - and drives down cross-team integration escapes and flake rates. Scope: verification across multiple teams.</t>
+          <t>Depth: Designs testable systems (contract, property-based, replay from prod); owns a test strategy. Evidenced by: Designs the verification strategy for a capability. Scope: capability / domain (terminal level).</t>
         </is>
       </c>
       <c r="J12" s="4" t="inlineStr">
         <is>
-          <t>Depth: Sets the organization's testing standards and invests where escaped defects cluster, visible in trend lines leadership reviews. Scope: organization-wide verification practice.</t>
+          <t>Depth: Expert in test strategy at scale (test data, environments, deployment safety). Evidenced by: Builds test infrastructure several teams rely on. Scope: multiple teams.</t>
         </is>
       </c>
       <c r="K12" s="4" t="inlineStr">
         <is>
-          <t>Depth: Frames verification as company risk management, deciding where the company buys confidence with testing versus operational safeguards. Scope: company risk posture.</t>
+          <t>Depth: Sets testing/verification discipline across the org. Evidenced by: Sets the organization's testing standards. Scope: organization.</t>
+        </is>
+      </c>
+      <c r="L12" s="4" t="inlineStr">
+        <is>
+          <t>Depth: Shapes the company-wide quality culture; advances verification practice. Evidenced by: Frames verification as company risk management. Scope: company.</t>
         </is>
       </c>
     </row>
@@ -1419,37 +1480,42 @@
       </c>
       <c r="E13" s="4" t="inlineStr">
         <is>
-          <t>Humble &amp; Farley, *Continuous Delivery* (2010)</t>
+          <t>Builds the build, test, release and deploy pipeline.</t>
         </is>
       </c>
       <c r="F13" s="4" t="inlineStr">
         <is>
-          <t>Depth: Ships through the pipeline correctly - green builds, small batches - and reads pipeline failures to their cause before asking for help. Scope: their own changes.</t>
+          <t>Humble &amp; Farley, Continuous Delivery: Reliable Software Releases through Build Test and Deployment Automation (Addison-Wesley, 2010) — defines the deployment pipeline behind pipeline-as-product and making the safe path the easy path.</t>
         </is>
       </c>
       <c r="G13" s="4" t="inlineStr">
         <is>
-          <t>Depth: Owns their component's pipeline - faster feedback, deterministic builds, automated rollback - and treats a red main branch as the team's top interrupt. Scope: one component's delivery path.</t>
+          <t>Depth: Uses and makes guided fixes to existing pipelines. Evidenced by: Ships through the pipeline correctly. Scope: task.</t>
         </is>
       </c>
       <c r="H13" s="4" t="inlineStr">
         <is>
-          <t>Depth: Designs CI/CD as a product for a capability's users - reusable pipeline templates, progressive delivery with canaries and feature flags, automated rollback triggers - so risky changes ship safely by default, and tracks its DORA metrics as product metrics. Scope: the delivery system for a capability and its users.</t>
+          <t>Depth: Independently builds and improves pipelines for their area. Evidenced by: Owns their component's pipeline. Scope: component.</t>
         </is>
       </c>
       <c r="I13" s="4" t="inlineStr">
         <is>
-          <t>Depth: Builds delivery infrastructure multiple teams ship through and improves their aggregate lead time and change-failure rate, with the before/after measured. Scope: delivery across multiple teams.</t>
+          <t>Depth: Designs deployment safety (progressive delivery, rollback) for a domain. Evidenced by: Designs CI/CD as a product for a capability's users. Scope: capability / domain (terminal level).</t>
         </is>
       </c>
       <c r="J13" s="4" t="inlineStr">
         <is>
-          <t>Depth: Owns the organization's delivery architecture - pipeline standards, environment strategy, release policy - and the metrics program that shows it working. Scope: organization-wide delivery performance.</t>
+          <t>Depth: Expert in delivery engineering at scale; sets standards across teams. Evidenced by: Builds delivery infrastructure multiple teams ship through. Scope: multiple teams.</t>
         </is>
       </c>
       <c r="K13" s="4" t="inlineStr">
         <is>
-          <t>Depth: Sets company delivery strategy - the company's tolerance for speed versus control, and the investments that move both. Scope: company-wide delivery.</t>
+          <t>Depth: Defines the org's delivery/release philosophy. Evidenced by: Owns the organization's delivery architecture. Scope: organization.</t>
+        </is>
+      </c>
+      <c r="L13" s="4" t="inlineStr">
+        <is>
+          <t>Depth: Advances release engineering practice company-wide. Evidenced by: Sets company delivery strategy. Scope: company.</t>
         </is>
       </c>
     </row>
@@ -1476,37 +1542,42 @@
       </c>
       <c r="E14" s="4" t="inlineStr">
         <is>
-          <t>Winters, Manshreck &amp; Wright, *Software Engineering at Google* (2020), deprecation chapter</t>
+          <t>Manages how change reaches production safely — decoupling deploy from release with feature flags, staged and canary rollouts, rollback readiness, and migration sequencing that bounds the blast radius of every change.</t>
         </is>
       </c>
       <c r="F14" s="4" t="inlineStr">
         <is>
-          <t>Depth: Executes migration and release steps from a runbook accurately and reports blockers with reproduction detail. Scope: assigned migration tasks and individual releases.</t>
+          <t>Winters, Manshreck &amp; Wright, Software Engineering at Google: Lessons Learned from Programming Over Time (O'Reilly, 2020) — treats deprecation as planned, resourced engineering work with migration paths, not neglect.</t>
         </is>
       </c>
       <c r="G14" s="4" t="inlineStr">
         <is>
-          <t>Depth: Migrates their component's consumers off an old interface - versioned releases, working codemods or clear guides, targeted notices, stragglers tracked to zero - with rollback paths they have actually exercised. Scope: one component's releases and migrations.</t>
+          <t>Depth: Follows the release process exactly — flags, staged rollout steps, verification checklists — verifies their change in production, and rolls back with guidance. Evidenced by: Executes migration and release steps from a runbook accurately. Scope: task.</t>
         </is>
       </c>
       <c r="H14" s="4" t="inlineStr">
         <is>
-          <t>Depth: Plans and runs a capability-level deprecation as a managed migration - usage census, automated tooling for the common case, published timelines with dual-support windows, staged shutoffs with real dates, and support for the hard cases - landing it without surprise breakage or executive escalation. Scope: a capability's lifecycle end to end.</t>
+          <t>Depth: Ships behind flags with a rollback plan by default, monitors rollouts and reverts on their own judgment when signals degrade, and writes changes that tolerate both versions running during rollout. Evidenced by: Migrates their component's consumers off an old interface. Scope: component.</t>
         </is>
       </c>
       <c r="I14" s="4" t="inlineStr">
         <is>
-          <t>Depth: Coordinates migrations that cross team boundaries - sequencing dependencies, building shared tooling, keeping a public burn-down - so no team is stranded. Scope: multi-team migrations.</t>
+          <t>Depth: Designs the rollout for risky changes — canary criteria, migration sequencing, flag lifecycle, kill switches — and reviews others' rollout plans for blast radius; the person teams ask how to ship something safely. Evidenced by: Plans and runs a capability-level deprecation as a managed migration. Scope: capability / domain (terminal level).</t>
         </is>
       </c>
       <c r="J14" s="4" t="inlineStr">
         <is>
-          <t>Depth: Sets the organization's deprecation policy - support windows, migration funding rules, sunset criteria - so retirement is routine rather than heroic, and drives org-scale migrations to completion. Scope: organization-wide lifecycle management.</t>
+          <t>Depth: Builds progressive-delivery machinery multiple teams release through (flag platforms, automated canary analysis, automated rollback), retiring deploy patterns that cause repeat incidents and measurably raising deploy frequency. Evidenced by: Coordinates migrations that cross team boundaries. Scope: multiple teams.</t>
         </is>
       </c>
       <c r="K14" s="4" t="inlineStr">
         <is>
-          <t>Depth: Sets the company's compatibility promise - how long things stay supported, what stability means, and when the company breaks its own users - and drives company-scale technology transitions with multi-year plans that survive reorgs. Scope: company technology lifecycle.</t>
+          <t>Depth: Owns release policy for an organization and its delivery metrics — rollout standards, freeze rules, environment strategy — dismantling ceremony that adds no safety. Evidenced by: Sets the organization's deprecation policy. Scope: organization.</t>
+        </is>
+      </c>
+      <c r="L14" s="4" t="inlineStr">
+        <is>
+          <t>Depth: Sets how an entire company's software reaches customers — the risk posture products ship under — and defends it to executives, auditors, and regulators. Evidenced by: Sets the company's compatibility promise. Scope: company.</t>
         </is>
       </c>
     </row>
@@ -1533,37 +1604,42 @@
       </c>
       <c r="E15" s="4" t="inlineStr">
         <is>
-          <t>Amazon Web Services, *Well-Architected Framework* (2015-)</t>
+          <t>Engineers compute, network, storage and IaC.</t>
         </is>
       </c>
       <c r="F15" s="4" t="inlineStr">
         <is>
-          <t>Depth: Provisions and modifies cloud resources from documented patterns, explaining what each resource in their change is for and checking cost implications before creating it. Scope: task-level resources in an existing account structure.</t>
+          <t>Amazon Web Services, AWS Well-Architected Framework (AWS, accessed 2026-07) — the industry-standard rubric for the cloud trade-offs this competency makes and reviews.</t>
         </is>
       </c>
       <c r="G15" s="4" t="inlineStr">
         <is>
-          <t>Depth: Designs the cloud footprint for a component - networking, storage, compute choices - with a written note on cost and failure-mode trade-offs. Scope: one component's infrastructure.</t>
+          <t>Depth: Makes guided changes to existing infra; understands core cloud services. Evidenced by: Provisions and modifies cloud resources from documented patterns. Scope: task.</t>
         </is>
       </c>
       <c r="H15" s="4" t="inlineStr">
         <is>
-          <t>Depth: Architects a capability's infrastructure for the failure domains that matter - zones, regions, quotas, tenancy isolation, dependencies - and defends the design in review against well-architected-style criteria, including cost. Catches single points of failure and blast-radius problems in others' designs. Scope: a capability's cloud architecture.</t>
+          <t>Depth: Independently builds and manages standard resources using IaC. Evidenced by: Designs the cloud footprint for a component. Scope: component.</t>
         </is>
       </c>
       <c r="I15" s="4" t="inlineStr">
         <is>
-          <t>Depth: Designs shared infrastructure patterns - landing zones, network topology, account strategy - that multiple teams inherit rather than reinvent. Scope: infrastructure spanning multiple teams.</t>
+          <t>Depth: Designs infra for scale, cost and resilience across a domain. Evidenced by: Architects a capability's infrastructure for the failure domains that matter. Scope: capability / domain (terminal level).</t>
         </is>
       </c>
       <c r="J15" s="4" t="inlineStr">
         <is>
-          <t>Depth: Sets the organization's cloud strategy - provider posture, region strategy, cost governance - and reviews major designs against it, owning the trade-offs in front of finance and vendors. Scope: organization-wide cloud estate.</t>
+          <t>Depth: Expert in infra platforms used by many teams; owns major cost strategy. Evidenced by: Designs shared infrastructure patterns. Scope: multiple teams.</t>
         </is>
       </c>
       <c r="K15" s="4" t="inlineStr">
         <is>
-          <t>Depth: Owns company-level infrastructure bets - multi-cloud versus single, build versus buy at the platform layer, decade-scale commitments - and negotiates the vendor relationships behind them. Scope: company infrastructure strategy.</t>
+          <t>Depth: Sets org infrastructure direction. Evidenced by: Sets the organization's cloud strategy. Scope: organization.</t>
+        </is>
+      </c>
+      <c r="L15" s="4" t="inlineStr">
+        <is>
+          <t>Depth: Trusted with company-level platform bets; defines infra strategy. Evidenced by: Owns company-level infrastructure bets. Scope: company.</t>
         </is>
       </c>
     </row>
@@ -1590,37 +1666,42 @@
       </c>
       <c r="E16" s="4" t="inlineStr">
         <is>
-          <t>Burns, Grant, Oppenheimer, Brewer &amp; Wilkes, "Borg, Omega, and Kubernetes" (ACM Queue, 2016)</t>
+          <t>Schedule, place, and manage containerized workloads across a cluster of compute nodes.</t>
         </is>
       </c>
       <c r="F16" s="4" t="inlineStr">
         <is>
-          <t>Depth: Deploys and debugs workloads on the orchestrator with guidance - reads events, logs, and resource limits to explain why a workload is not running. Scope: task-level workloads.</t>
+          <t>Burns, Beda, Hightower &amp; Evenson, Kubernetes: Up and Running, 3rd Edition (O'Reilly, 2022) — explains why orchestration is platform machinery -- controllers and declarative desired state -- not just deployment tooling.</t>
         </is>
       </c>
       <c r="G16" s="4" t="inlineStr">
         <is>
-          <t>Depth: Owns their component's runtime configuration - requests and limits, probes, disruption budgets, autoscaling - and tunes it from observed behavior. Scope: one component's runtime.</t>
+          <t>Depth: Deploys workloads to an existing orchestrator under review, adjusting basic scheduling settings from examples. Evidenced by: Deploys and debugs workloads on the orchestrator with guidance. Scope: task.</t>
         </is>
       </c>
       <c r="H16" s="4" t="inlineStr">
         <is>
-          <t>Depth: Designs and operates cluster-level platform machinery - operators and controllers, admission rules, tenancy and isolation boundaries, upgrade strategies - and debugs the control plane itself when abstractions leak. Scope: the runtime backing a capability and its tenants.</t>
+          <t>Depth: Independently operates orchestrated workloads, manages routine scaling, placement, and health checks with normal review. Evidenced by: Owns their component's runtime configuration. Scope: component.</t>
         </is>
       </c>
       <c r="I16" s="4" t="inlineStr">
         <is>
-          <t>Depth: Sets workload standards multiple teams schedule against - cluster topology, upgrade cadence, multi-tenancy rules - and runs orchestrator upgrades without user-visible disruption. Scope: shared clusters across multiple teams.</t>
+          <t>Depth: Designs scheduling, affinity, and resource policies for ambiguous workloads and resolves hard orchestration failures. Evidenced by: Designs and operates cluster-level platform machinery. Scope: capability / domain (terminal level).</t>
         </is>
       </c>
       <c r="J16" s="4" t="inlineStr">
         <is>
-          <t>Depth: Owns the organization's runtime strategy - cluster fleet architecture, workload placement policy, the abstraction level exposed over raw orchestration. Scope: organization-wide runtime estate.</t>
+          <t>Depth: Defines cluster topology and scheduling patterns others adopt, solving deep placement, contention, and lifecycle problems. Evidenced by: Sets workload standards multiple teams schedule against. Scope: multiple teams.</t>
         </is>
       </c>
       <c r="K16" s="4" t="inlineStr">
         <is>
-          <t>Depth: Decides company-level runtime direction - when to adopt, skip, or exit a foundational compute technology - with published reasoning others cite. Scope: company compute strategy.</t>
+          <t>Depth: Sets organization-wide orchestration strategy and standards, anticipating where workload scheduling is heading. Evidenced by: Owns the organization's runtime strategy. Scope: organization.</t>
+        </is>
+      </c>
+      <c r="L16" s="4" t="inlineStr">
+        <is>
+          <t>Depth: Defines what effective orchestration means for the discipline, externally credible in shaping scheduling practice. Evidenced by: Decides company-level runtime direction. Scope: company.</t>
         </is>
       </c>
     </row>
@@ -1647,37 +1728,42 @@
       </c>
       <c r="E17" s="4" t="inlineStr">
         <is>
-          <t>Kurose &amp; Ross, *Computer Networking: A Top-Down Approach* (8th ed., 2021)</t>
+          <t>Architect network topologies, subnets, and routing for connectivity and segmentation.</t>
         </is>
       </c>
       <c r="F17" s="4" t="inlineStr">
         <is>
-          <t>Depth: Traces a request through DNS, load balancer, and service to locate a failure, narrating the path as they go. Scope: single-workload troubleshooting.</t>
+          <t>Kurose &amp; Ross, Computer Networking: A Top-Down Approach, 8th ed. (Pearson, 2020) — the standard layered model behind tracing requests and designing topologies across abstraction layers.</t>
         </is>
       </c>
       <c r="G17" s="4" t="inlineStr">
         <is>
-          <t>Depth: Configures the networking and compute for their component - routing, transport security, capacity class - and explains each choice. Scope: one component's foundations.</t>
+          <t>Depth: Configures basic network segments and routes from designs under review, verifying connectivity. Evidenced by: Traces a request through DNS, load balancer, and service to locate a failure. Scope: task.</t>
         </is>
       </c>
       <c r="H17" s="4" t="inlineStr">
         <is>
-          <t>Depth: Designs network and compute topology for a capability - segmentation, ingress and egress, cross-region traffic - and debugs the problems that cross abstraction layers. Scope: a capability's foundation layer.</t>
+          <t>Depth: Independently builds standard network topologies, manages routing and segmentation for routine needs with review. Evidenced by: Configures the networking and compute for their component. Scope: component.</t>
         </is>
       </c>
       <c r="I17" s="4" t="inlineStr">
         <is>
-          <t>Depth: Owns shared foundations several teams depend on and leads the gnarliest cross-layer incident investigations. Scope: multi-team shared infrastructure.</t>
+          <t>Depth: Designs routing and addressing schemes for ambiguous topologies and diagnoses hard reachability and routing failures. Evidenced by: Designs network and compute topology for a capability. Scope: capability / domain (terminal level).</t>
         </is>
       </c>
       <c r="J17" s="4" t="inlineStr">
         <is>
-          <t>Depth: Sets organization standards for network architecture and compute platforms and drives the consolidation migrations they imply. Scope: organization.</t>
+          <t>Depth: Defines network architecture and routing patterns others adopt, solving deep segmentation, scale, and convergence problems. Evidenced by: Owns shared foundations several teams depend on. Scope: multiple teams.</t>
         </is>
       </c>
       <c r="K17" s="4" t="inlineStr">
         <is>
-          <t>Depth: Owns company-scale foundation decisions - backbone, edge, data-center and cloud boundary - with a written multi-year plan. Scope: company.</t>
+          <t>Depth: Sets organization-wide network strategy and standards, anticipating shifts in network design and routing. Evidenced by: Sets organization standards for network architecture and compute platforms. Scope: organization.</t>
+        </is>
+      </c>
+      <c r="L17" s="4" t="inlineStr">
+        <is>
+          <t>Depth: Defines what good network design means for the field, externally credible in shaping routing practice. Evidenced by: Owns company-scale foundation decisions. Scope: company.</t>
         </is>
       </c>
     </row>
@@ -1704,37 +1790,42 @@
       </c>
       <c r="E18" s="4" t="inlineStr">
         <is>
-          <t>Morris, *Infrastructure as Code* (O'Reilly, 2016)</t>
+          <t>Define and version infrastructure declaratively to provision repeatable environments.</t>
         </is>
       </c>
       <c r="F18" s="4" t="inlineStr">
         <is>
-          <t>Depth: Makes changes through the IaC workflow rather than the console, reading plans and diffs to predict what will change before applying. Scope: task-level changes in existing modules.</t>
+          <t>Morris, Infrastructure as Code: Dynamic Systems for the Cloud Age, 2nd Edition (O'Reilly, 2021) — the discipline behind every plan-review-apply and drift-detection behavior at each level.</t>
         </is>
       </c>
       <c r="G18" s="4" t="inlineStr">
         <is>
-          <t>Depth: Writes reusable, parameterized modules for their component with sensible defaults and validation, and untangles state problems - drift, imports - safely. Scope: one component's infrastructure code.</t>
+          <t>Depth: Writes simple declarative resource definitions from templates, applying them under review in non-production environments. Evidenced by: Makes changes through the IaC workflow rather than the console. Scope: task.</t>
         </is>
       </c>
       <c r="H18" s="4" t="inlineStr">
         <is>
-          <t>Depth: Designs the IaC architecture for a capability - module boundaries, state topology, environment promotion, policy checks in the pipeline - so console drift is the exception that pages someone. Reviews others' infrastructure code for blast radius and reversibility. Scope: a capability's infrastructure codebase.</t>
+          <t>Depth: Independently provisions standard infrastructure stacks, manages state and variables, and handles routine drift with normal review. Evidenced by: Writes reusable, parameterized modules for their component. Scope: component.</t>
         </is>
       </c>
       <c r="I18" s="4" t="inlineStr">
         <is>
-          <t>Depth: Publishes module libraries and IaC conventions multiple teams build on, and runs breaking upgrades of shared modules without stranding consumers. Scope: shared infrastructure code across multiple teams.</t>
+          <t>Depth: Designs reusable modules for ambiguous needs, structures state safely, and is the go-to for tricky provisioning failures. Evidenced by: Designs the IaC architecture for a capability. Scope: capability / domain (terminal level).</t>
         </is>
       </c>
       <c r="J18" s="4" t="inlineStr">
         <is>
-          <t>Depth: Sets the organization's IaC standards - tooling, structure, testing, drift policy - and retires the exceptions and legacy hand-managed estates. Scope: organization-wide infrastructure codebase.</t>
+          <t>Depth: Defines the provisioning patterns and module conventions others adopt, solving thorny dependency and idempotency problems. Evidenced by: Publishes module libraries and IaC conventions multiple teams build on. Scope: multiple teams.</t>
         </is>
       </c>
       <c r="K18" s="4" t="inlineStr">
         <is>
-          <t>Depth: Treats the company's infrastructure definition as a strategic asset - portability, auditability, disaster recovery - and directs investment accordingly. Scope: company infrastructure posture.</t>
+          <t>Depth: Sets the organization-wide IaC strategy, governance, and standards, anticipating shifts in declarative provisioning practice. Evidenced by: Sets the organization's IaC standards. Scope: organization.</t>
+        </is>
+      </c>
+      <c r="L18" s="4" t="inlineStr">
+        <is>
+          <t>Depth: Defines what good infrastructure-as-code means for the field, shaping provisioning practices recognized across the industry. Evidenced by: Treats the company's infrastructure definition as a strategic asset. Scope: company.</t>
         </is>
       </c>
     </row>
@@ -1761,37 +1852,42 @@
       </c>
       <c r="E19" s="4" t="inlineStr">
         <is>
-          <t>Bottcher, "What I Talk About When I Talk About Platforms" (martinfowler.com, 2018)</t>
+          <t>Build self-service internal platforms and paved paths that streamline delivery.</t>
         </is>
       </c>
       <c r="F19" s="4" t="inlineStr">
         <is>
-          <t>Depth: Uses the self-service tooling as users do and documents the gaps that forced manual steps - doc corrections, template fixes, clearer prompts. Scope: individual requests.</t>
+          <t>Bottcher, What I Talk About When I Talk About Platforms (martinfowler.com, 2018) — the definitional source for removing humans from the request path.</t>
         </is>
       </c>
       <c r="G19" s="4" t="inlineStr">
         <is>
-          <t>Depth: Automates a manual provisioning flow for their component into a self-service action with validation and sane defaults, and measures the tickets it eliminates. Scope: one component's provisioning.</t>
+          <t>Depth: Maintains existing self-service platform components under review, addressing documented user requests. Evidenced by: Uses the self-service tooling as users do and documents the gaps that forced manual steps. Scope: task.</t>
         </is>
       </c>
       <c r="H19" s="4" t="inlineStr">
         <is>
-          <t>Depth: Designs self-service for a capability end to end - request, policy checks, provisioning, and day-2 operations like resize and teardown - with guardrails so self-service cannot create unsafe states, driving the ticket queue toward zero and time-to-provision down. Scope: a capability's full self-service lifecycle.</t>
+          <t>Depth: Independently builds and supports standard platform capabilities and templates for routine developer needs with review. Evidenced by: Automates a manual provisioning flow for their component into a self-service action. Scope: component.</t>
         </is>
       </c>
       <c r="I19" s="4" t="inlineStr">
         <is>
-          <t>Depth: Unifies self-service across teams behind one coherent interface - portal, CLI, or API - with a consistent request-to-ready experience, and holds the bar that new platform features ship self-service by default. Scope: self-service spanning multiple teams' offerings.</t>
+          <t>Depth: Designs self-service workflows for ambiguous needs, reducing friction and resolving hard abstraction and adoption issues. Evidenced by: Designs self-service for a capability end to end. Scope: capability / domain (terminal level).</t>
         </is>
       </c>
       <c r="J19" s="4" t="inlineStr">
         <is>
-          <t>Depth: Drives the organization to a self-service operating model, reporting ticket-elimination and time-to-ready trends to leadership. Scope: organization-wide provisioning experience.</t>
+          <t>Depth: Defines platform architecture and golden paths others adopt, solving deep developer-experience and leverage problems. Evidenced by: Unifies self-service across teams behind one coherent interface. Scope: multiple teams.</t>
         </is>
       </c>
       <c r="K19" s="4" t="inlineStr">
         <is>
-          <t>Depth: Makes self-service the company's default operating model for infrastructure, with manual provisioning reduced to signed-off exceptions. Scope: company operating model.</t>
+          <t>Depth: Sets organization-wide platform strategy, anticipating how developer-experience engineering should evolve. Evidenced by: Drives the organization to a self-service operating model. Scope: organization.</t>
+        </is>
+      </c>
+      <c r="L19" s="4" t="inlineStr">
+        <is>
+          <t>Depth: Defines what excellent platform engineering means for the field, shaping industry developer-experience practice. Evidenced by: Makes self-service the company's default operating model for infrastructure. Scope: company.</t>
         </is>
       </c>
     </row>
@@ -1818,37 +1914,42 @@
       </c>
       <c r="E20" s="4" t="inlineStr">
         <is>
-          <t>Majors, Fong-Jones &amp; Miranda, *Observability Engineering* (O'Reilly, 2022)</t>
+          <t>Makes system behavior visible.</t>
         </is>
       </c>
       <c r="F20" s="4" t="inlineStr">
         <is>
-          <t>Depth: Reads existing dashboards, logs, and traces to locate a fault, and adds log lines and metrics to their own changes as a matter of course. Scope: debugging their own tasks.</t>
+          <t>Majors, Fong-Jones &amp; Miranda, Observability Engineering: Achieving Production Excellence (O'Reilly, 2022) — sets the bar the telemetry offering at each level is measured against.</t>
         </is>
       </c>
       <c r="G20" s="4" t="inlineStr">
         <is>
-          <t>Depth: Instruments their component so strangers can debug it - structured events, useful trace spans, dashboards tied to user symptoms - answering 'what changed and who is affected' without adding code. Scope: one component's telemetry.</t>
+          <t>Depth: Understands logs/metrics/traces; reads existing dashboards. Evidenced by: Traces a failing deploy to a specific pod's OOM-kill using the team's existing dashboard, without needing a teammate to point them to it. Scope: task.</t>
         </is>
       </c>
       <c r="H20" s="4" t="inlineStr">
         <is>
-          <t>Depth: Designs the observability offering for a capability - cardinality and cost trade-offs, sampling, correlation across services, out-of-the-box dashboards users get without configuration - and debugs novel production questions from telemetry alone. Makes platform telemetry consumable by users debugging their own workloads. Scope: a capability's observability, including its user-facing telemetry.</t>
+          <t>Depth: Instruments their services; builds dashboards; tunes alerts to limit noise. Evidenced by: Instruments their component so strangers can debug it. Scope: component.</t>
         </is>
       </c>
       <c r="I20" s="4" t="inlineStr">
         <is>
-          <t>Depth: Builds observability infrastructure multiple teams instrument against - shared pipelines, conventions, cost governance - and raises the floor of what every team can see. Scope: telemetry across multiple teams.</t>
+          <t>Depth: Designs observability for complex systems (end-to-end traces, quality signals, cost attribution). Evidenced by: Designs the observability offering for a capability. Scope: capability / domain (terminal level).</t>
         </is>
       </c>
       <c r="J20" s="4" t="inlineStr">
         <is>
-          <t>Depth: Sets the organization's observability strategy and standards, retiring tool sprawl, owning the cost curve, and making cross-system debugging routine. Scope: organization-wide observability.</t>
+          <t>Depth: Expert in instrumentation trade-offs at scale, incl. privacy-safe logging. Evidenced by: Builds observability infrastructure multiple teams instrument against. Scope: multiple teams.</t>
         </is>
       </c>
       <c r="K20" s="4" t="inlineStr">
         <is>
-          <t>Depth: Frames observability as company capability - what the business can and cannot see about its own operation - and directs investment at the blind spots with the largest risk. Scope: company-level visibility.</t>
+          <t>Depth: Defines org observability strategy. Evidenced by: Sets the organization's observability strategy and standards. Scope: organization.</t>
+        </is>
+      </c>
+      <c r="L20" s="4" t="inlineStr">
+        <is>
+          <t>Depth: Shapes company-wide operational visibility; advances practice. Evidenced by: Frames observability as company capability. Scope: company.</t>
         </is>
       </c>
     </row>
@@ -1875,37 +1976,42 @@
       </c>
       <c r="E21" s="4" t="inlineStr">
         <is>
-          <t>Beyer, Jones, Petoff &amp; Murphy (eds.), *Site Reliability Engineering* (O'Reilly, 2016)</t>
+          <t>Keeps services healthy; designs for failure.</t>
         </is>
       </c>
       <c r="F21" s="4" t="inlineStr">
         <is>
-          <t>Depth: Explains their service's SLOs and reads burn-rate dashboards correctly, escalating when budget burn is abnormal and responding to alerts on their own work by the runbook. Scope: awareness on the services they touch.</t>
+          <t>Beyer, Jones, Petoff &amp; Murphy (eds.), Site Reliability Engineering: How Google Runs Production Systems (O'Reilly/Google, 2016) — establishes SLOs, error budgets, and symptom-based alerting as the reliability contract.</t>
         </is>
       </c>
       <c r="G21" s="4" t="inlineStr">
         <is>
-          <t>Depth: Defines SLIs that reflect user experience for their component - alert thresholds tied to symptoms rather than causes, runbooks a first-time responder can execute - and prunes noisy alerts. Scope: one component's service levels.</t>
+          <t>Depth: Understands SLOs and common failure modes; keeps components healthy with guidance. Evidenced by: Explains their service's SLOs and reads burn-rate dashboards correctly. Scope: task.</t>
         </is>
       </c>
       <c r="H21" s="4" t="inlineStr">
         <is>
-          <t>Depth: Negotiates SLOs for a capability with its internal customers, sets error-budget policy, wires budgets into release decisions, and visibly changes priorities when the budget is exhausted - feature work stops, reliability work starts. Audits alert quality so pages are actionable and rare. Scope: a capability's reliability contract.</t>
+          <t>Depth: Builds retries, timeouts and fallbacks; understands blast radius. Evidenced by: Adds a retry-with-backoff and a fallback path to a flaky downstream call so that dependency's failure doesn't cascade into their own component. Scope: component.</t>
         </is>
       </c>
       <c r="I21" s="4" t="inlineStr">
         <is>
-          <t>Depth: Aligns SLOs across dependent services so promises compose - no service promising more than its dependencies allow - and arbitrates budget disputes between teams. Scope: reliability contracts across multiple teams.</t>
+          <t>Depth: Designs for graceful degradation; defines SLOs; accountable for a domain's reliability. Evidenced by: Negotiates SLOs for a capability with its internal customers. Scope: capability / domain (terminal level).</t>
         </is>
       </c>
       <c r="J21" s="4" t="inlineStr">
         <is>
-          <t>Depth: Owns the organization's SLO framework and review cadence, making error budgets the shared currency of reliability decisions in planning. Scope: organization-wide reliability governance.</t>
+          <t>Depth: Expert in resilience and capacity planning at scale; drives down incidents systemically. Evidenced by: Aligns SLOs across dependent services so promises compose. Scope: multiple teams.</t>
         </is>
       </c>
       <c r="K21" s="4" t="inlineStr">
         <is>
-          <t>Depth: Sets company reliability targets against business risk and cost, deciding where the company deliberately buys less than five nines. Scope: company reliability posture.</t>
+          <t>Depth: Owns org-level reliability; fixes risk in process and org design. Evidenced by: Owns the organization's SLO framework and review cadence. Scope: organization.</t>
+        </is>
+      </c>
+      <c r="L21" s="4" t="inlineStr">
+        <is>
+          <t>Depth: Sets the company's reliability philosophy. Evidenced by: Sets company reliability targets against business risk and cost. Scope: company.</t>
         </is>
       </c>
     </row>
@@ -1932,37 +2038,42 @@
       </c>
       <c r="E22" s="4" t="inlineStr">
         <is>
-          <t>PagerDuty, *Incident Response Guide* (2017)</t>
+          <t>Responds to and learns from production incidents.</t>
         </is>
       </c>
       <c r="F22" s="4" t="inlineStr">
         <is>
-          <t>Depth: Executes runbook steps accurately during incidents under supervision - joins the channel, keeps a timeline, and speaks up when reality diverges from the runbook. Scope: assisting on incidents touching their tasks.</t>
+          <t>PagerDuty, Incident Response Documentation (accessed 2026-07) — grounds the progression from executing runbooks to designing the response system itself.</t>
         </is>
       </c>
       <c r="G22" s="4" t="inlineStr">
         <is>
-          <t>Depth: Serves as primary on-call for their component - triages, mitigates first, communicates status on a cadence, and escalates with a clear handoff when out of depth. Scope: one component's rotation.</t>
+          <t>Depth: Responds to alerts with support; follows runbooks; escalates appropriately. Evidenced by: Executes runbook steps accurately during incidents under supervision. Scope: task.</t>
         </is>
       </c>
       <c r="H22" s="4" t="inlineStr">
         <is>
-          <t>Depth: Commands complex multi-team incidents - structures the response, delegates workstreams, makes mitigation calls under uncertainty, and runs the user-facing communications; responders describe the room getting calmer when they join. Scope: incidents spanning a capability and its dependent teams.</t>
+          <t>Depth: Triages and resolves routine incidents; clear notes; takes on-call. Evidenced by: Serves as primary on-call for their component. Scope: component.</t>
         </is>
       </c>
       <c r="I22" s="4" t="inlineStr">
         <is>
-          <t>Depth: Designs the incident-management system itself - severity schemes, escalation paths, tooling, and on-call health across teams - and steps in as commander for the worst cases. Scope: multiple teams' response system.</t>
+          <t>Depth: Leads response to complex failures; blameless postmortems; same failure never recurs. Evidenced by: Commands complex multi-team incidents. Scope: capability / domain (terminal level).</t>
         </is>
       </c>
       <c r="J22" s="4" t="inlineStr">
         <is>
-          <t>Depth: Owns the organization's major-incident readiness - drives cross-org drills and game days and is the technical authority leadership expects on the bridge in a crisis. Scope: organization.</t>
+          <t>Depth: Expert in incident-management design (rotations, severity, escalation). Evidenced by: Designs the incident-management system itself. Scope: multiple teams.</t>
         </is>
       </c>
       <c r="K22" s="4" t="inlineStr">
         <is>
-          <t>Depth: Leads the company's existential incidents and the reforms after them - the response to company-threatening events, and the structural changes that follow, are theirs to drive. Scope: company.</t>
+          <t>Depth: Commands the highest-severity incidents; sets incident process org-wide. Evidenced by: Owns the organization's major-incident readiness. Scope: organization.</t>
+        </is>
+      </c>
+      <c r="L22" s="4" t="inlineStr">
+        <is>
+          <t>Depth: Sets the company's incident philosophy; calm authority in the worst moments. Evidenced by: Leads the company's existential incidents and the reforms after them. Scope: company.</t>
         </is>
       </c>
     </row>
@@ -1989,37 +2100,42 @@
       </c>
       <c r="E23" s="4" t="inlineStr">
         <is>
-          <t>Allspaw, "Blameless PostMortems and a Just Culture" (Etsy Code as Craft, 2012)</t>
+          <t>Responds to and learns from production incidents.</t>
         </is>
       </c>
       <c r="F23" s="4" t="inlineStr">
         <is>
-          <t>Depth: Contributes accurate timelines and observations to incident reviews and completes the follow-up actions assigned to them on time. Scope: incidents they took part in.</t>
+          <t>Allspaw, Blameless PostMortems and a Just Culture, Code as Craft (Etsy Engineering Blog, 2012) — establishes blameless analysis focused on systemic contributors over human error.</t>
         </is>
       </c>
       <c r="G23" s="4" t="inlineStr">
         <is>
-          <t>Depth: Writes blameless postmortems for their component's incidents - timelines, contributing factors beyond the trigger, and actions that get done rather than logged. Scope: one component.</t>
+          <t>Depth: Responds to alerts with support; follows runbooks; escalates appropriately. Evidenced by: Contributes accurate timelines and observations to incident reviews. Scope: task.</t>
         </is>
       </c>
       <c r="H23" s="4" t="inlineStr">
         <is>
-          <t>Depth: Facilitates incident reviews others attend voluntarily - surfaces systemic and organizational contributors, extracts themes across incidents, and converts them into platform work that measurably reduces repeats. Scope: a capability's incident record.</t>
+          <t>Depth: Triages and resolves routine incidents; clear notes; takes on-call. Evidenced by: Writes blameless postmortems for their component's incidents. Scope: component.</t>
         </is>
       </c>
       <c r="I23" s="4" t="inlineStr">
         <is>
-          <t>Depth: Builds the learning system across teams - review standards, cross-team pattern analysis, the feedback loop from incidents into roadmaps - and spots the org-level pattern behind separate teams' incidents. Scope: multiple teams.</t>
+          <t>Depth: Leads response to complex failures; blameless postmortems; same failure never recurs. Evidenced by: Facilitates incident reviews others attend voluntarily. Scope: capability / domain (terminal level).</t>
         </is>
       </c>
       <c r="J23" s="4" t="inlineStr">
         <is>
-          <t>Depth: Drives org-level resilience investment from incident evidence - the organization's biggest reliability bets cite analysis they produced. Scope: organization.</t>
+          <t>Depth: Expert in incident-management design (rotations, severity, escalation). Evidenced by: Builds the learning system across teams. Scope: multiple teams.</t>
         </is>
       </c>
       <c r="K23" s="4" t="inlineStr">
         <is>
-          <t>Depth: Shapes the company's safety culture - how the company talks about failure, and what it changes after failure, reflects norms they set. Scope: company.</t>
+          <t>Depth: Commands the highest-severity incidents; sets incident process org-wide. Evidenced by: Drives org-level resilience investment from incident evidence. Scope: organization.</t>
+        </is>
+      </c>
+      <c r="L23" s="4" t="inlineStr">
+        <is>
+          <t>Depth: Sets the company's incident philosophy; calm authority in the worst moments. Evidenced by: Shapes the company's safety culture. Scope: company.</t>
         </is>
       </c>
     </row>
@@ -2046,37 +2162,42 @@
       </c>
       <c r="E24" s="4" t="inlineStr">
         <is>
-          <t>Gregg, *Systems Performance* (2nd ed., 2020)</t>
+          <t>Keeps systems fast and economical.</t>
         </is>
       </c>
       <c r="F24" s="4" t="inlineStr">
         <is>
-          <t>Depth: Reads utilization and saturation dashboards correctly and flags approaching limits with evidence, checking the resource impact of their own changes before merge. Scope: resources their tasks touch.</t>
+          <t>Gregg, Systems Performance: Enterprise and the Cloud, 2nd ed. (Addison-Wesley, 2020) — grounds profiling-not-guessing and data-driven capacity planning at every level.</t>
         </is>
       </c>
       <c r="G24" s="4" t="inlineStr">
         <is>
-          <t>Depth: Load-tests their component and sizes it from measured headroom rather than guesswork, profiling the hot path before optimizing and tracking its spend. Scope: one component's capacity and performance.</t>
+          <t>Depth: Understands cost/latency drivers of what they build. Evidenced by: Reads utilization and saturation dashboards correctly and flags approaching limits with evidence. Scope: task.</t>
         </is>
       </c>
       <c r="H24" s="4" t="inlineStr">
         <is>
-          <t>Depth: Owns capacity planning for a capability - forecasts demand ahead of organic and launch-driven growth, sets headroom policy, manages tenant quotas so one user cannot starve the rest, and keeps cost-per-tenant visible so demand self-corrects. Catches the scaling cliff before users hit it. Scope: a capability's capacity, performance, and spend.</t>
+          <t>Depth: Applies standard optimizations; stays within cost/latency budgets. Evidenced by: Load-tests their component and sizes it from measured headroom rather than guesswork. Scope: component.</t>
         </is>
       </c>
       <c r="I24" s="4" t="inlineStr">
         <is>
-          <t>Depth: Runs capacity planning across shared pools that multiple teams draw from, arbitrating contention with data and driving the efficiency work with the largest aggregate payoff. Scope: shared capacity across multiple teams.</t>
+          <t>Depth: Designs cost-aware architectures; defines and tracks unit economics for a domain. Evidenced by: Owns capacity planning for a capability. Scope: capability / domain (terminal level).</t>
         </is>
       </c>
       <c r="J24" s="4" t="inlineStr">
         <is>
-          <t>Depth: Owns the organization's capacity and efficiency program - forecasting discipline, unit economics, commitment strategy with providers - with a forecast finance trusts. Scope: organization-wide capacity and cost.</t>
+          <t>Depth: Expert in economics at scale (fleet optimization, build-vs-buy). Evidenced by: Runs capacity planning across shared pools that multiple teams draw from. Scope: multiple teams.</t>
         </is>
       </c>
       <c r="K24" s="4" t="inlineStr">
         <is>
-          <t>Depth: Treats infrastructure economics as company strategy - negotiating commitments, setting efficiency targets, deciding when scale justifies structural change. Scope: company infrastructure economics.</t>
+          <t>Depth: Owns org-level spend strategy; cost decisions change margins. Evidenced by: Owns the organization's capacity and efficiency program. Scope: organization.</t>
+        </is>
+      </c>
+      <c r="L24" s="4" t="inlineStr">
+        <is>
+          <t>Depth: Shapes the company economics of the products. Evidenced by: Treats infrastructure economics as company strategy. Scope: company.</t>
         </is>
       </c>
     </row>
@@ -2103,37 +2224,42 @@
       </c>
       <c r="E25" s="4" t="inlineStr">
         <is>
-          <t>Beyer, Jones, Petoff &amp; Murphy (eds.), *Site Reliability Engineering* (O'Reilly, 2016), toil chapter</t>
+          <t>Default to eliminating toil by automating repetitive operational work.</t>
         </is>
       </c>
       <c r="F25" s="4" t="inlineStr">
         <is>
-          <t>Depth: Executes operational runbooks accurately and improves the runbook when a step is wrong or missing, scripting away repetitive steps in their own work and sharing the script. Scope: assigned operational tasks.</t>
+          <t>Beyer, Jones, Petoff &amp; Murphy (eds.), Site Reliability Engineering: How Google Runs Production Systems (O'Reilly/Google, 2016) — provides the definition and budget ceiling this competency tracks against.</t>
         </is>
       </c>
       <c r="G25" s="4" t="inlineStr">
         <is>
-          <t>Depth: Automates the recurring manual work in their component - scripted, scheduled, or eliminated - and shows the hours reclaimed. Scope: one component's operational load.</t>
+          <t>Depth: Runs and lightly edits existing automation under review, flagging tasks that remain manual. Evidenced by: Executes operational runbooks accurately and improves the runbook when a step is wrong or missing. Scope: task.</t>
         </is>
       </c>
       <c r="H25" s="4" t="inlineStr">
         <is>
-          <t>Depth: Measures toil for a capability and holds it under an explicit budget, designing the operational work out - self-healing, auto-remediation, removing the need entirely - rather than scripting it faster. Scope: a capability's operational model.</t>
+          <t>Depth: Independently automates routine operational tasks and integrates them into standard workflows with normal review. Evidenced by: Automates the recurring manual work in their component. Scope: component.</t>
         </is>
       </c>
       <c r="I25" s="4" t="inlineStr">
         <is>
-          <t>Depth: Builds automation multiple teams reuse for their operational work and drives down the organization's aggregate on-call load, with the trend visible. Scope: operational load across multiple teams.</t>
+          <t>Depth: Designs automation for ambiguous, error-prone toil and resolves hard reliability and orchestration issues in pipelines. Evidenced by: Measures toil for a capability and holds it under an explicit budget. Scope: capability / domain (terminal level).</t>
         </is>
       </c>
       <c r="J25" s="4" t="inlineStr">
         <is>
-          <t>Depth: Sets the organization's toil policy - measurement, budgets, and the planning rule that reclaims time for engineering work. Scope: organization-wide operational efficiency.</t>
+          <t>Depth: Defines automation patterns and toil-elimination practices others adopt, solving deep workflow and safety problems. Evidenced by: Builds automation multiple teams reuse for their operational work. Scope: multiple teams.</t>
         </is>
       </c>
       <c r="K25" s="4" t="inlineStr">
         <is>
-          <t>Depth: Makes operational leverage a company-level argument - headcount that scales sublinearly with growth - and directs automation investment accordingly. Scope: company operational economics.</t>
+          <t>Depth: Sets organization-wide automation strategy, anticipating where automation-first operations should head. Evidenced by: Sets the organization's toil policy. Scope: organization.</t>
+        </is>
+      </c>
+      <c r="L25" s="4" t="inlineStr">
+        <is>
+          <t>Depth: Defines what automation-first operations means for the discipline, externally credible in shaping the practice. Evidenced by: Makes operational leverage a company-level argument. Scope: company.</t>
         </is>
       </c>
     </row>
@@ -2160,37 +2286,42 @@
       </c>
       <c r="E26" s="4" t="inlineStr">
         <is>
-          <t>OWASP, *Application Security Verification Standard* (v4, 2019)</t>
+          <t>Encodes preventive controls as versioned, tested, automatically enforced policy - admission checks, pipeline gates, configuration rules - with actionable violation messages and governed exception paths, so the safe way is the default way.</t>
         </is>
       </c>
       <c r="F26" s="4" t="inlineStr">
         <is>
-          <t>Depth: Works within existing guardrails and reads policy failures to their cause instead of asking for exemptions, and explains what each guardrail protects against. Scope: their own changes.</t>
+          <t>OWASP Foundation, OWASP Application Security Verification Standard (accessed 2026-07) — gives guardrail and policy rules an external, auditable bar instead of home-grown opinion.</t>
         </is>
       </c>
       <c r="G26" s="4" t="inlineStr">
         <is>
-          <t>Depth: Writes and tests policy rules for their component - admission checks, pipeline gates - with low false-positive rates and violation messages that say how to fix the problem. Scope: one component's policy surface.</t>
+          <t>Depth: Works within existing guardrails, reads a policy violation to its cause instead of requesting an exception, and explains what each guardrail protects against. Evidenced by: Traces a blocked deploy to a missing resource-limit field in the manifest instead of filing an exception request, and fixes it. Scope: task.</t>
         </is>
       </c>
       <c r="H26" s="4" t="inlineStr">
         <is>
-          <t>Depth: Designs the guardrail architecture for a capability - what is blocked, warned, or audited, with documented threat reasoning - and tunes it so the safe path is the fast path, measured by exemption-request rates falling; runs the exception workflow without becoming the bottleneck. Scope: a capability's preventive controls.</t>
+          <t>Depth: Writes and tests policy rules for a component - admission checks, pipeline gates - with low false-positive rates and violation messages that tell the user how to comply. Evidenced by: Writes an admission-control rule for their component that catches unencrypted volumes with a message that tells the requester exactly which field to change. Scope: component.</t>
         </is>
       </c>
       <c r="I26" s="4" t="inlineStr">
         <is>
-          <t>Depth: Harmonizes policy across teams into a coherent, versioned policy library with a real exception process - time-boxed, owned, reviewed - and adjudicates the security-versus-velocity disputes teams escalate. Scope: guardrails spanning multiple teams.</t>
+          <t>Depth: Designs the guardrail architecture for a capability - what is blocked, warned, or audited, with documented threat reasoning - tuned so the safe path is the fast path, and runs an audited exception workflow without becoming the bottleneck. Evidenced by: Designs a capability's guardrail set -- what blocks, what warns, what only audits -- with the threat each rule defends against written down, and runs the exception process without becoming its bottleneck. Scope: capability / domain (terminal level).</t>
         </is>
       </c>
       <c r="J26" s="4" t="inlineStr">
         <is>
-          <t>Depth: Owns the organization's guardrail strategy with security partners - the control catalog, its coverage, and the evidence it works, moving security from review-time to platform-time. Scope: organization-wide preventive posture.</t>
+          <t>Depth: Harmonizes policy across teams into a coherent, versioned policy library with a governed exception process, and adjudicates escalated safety-versus-velocity disputes. Evidenced by: Merges three teams' near-duplicate policy libraries into one versioned set and adjudicates which team's stricter rule wins. Scope: multiple teams.</t>
         </is>
       </c>
       <c r="K26" s="4" t="inlineStr">
         <is>
-          <t>Depth: Sets the company's balance of enablement and control, accountable for guardrails that hold under audit and under attack without strangling delivery. Scope: company control posture.</t>
+          <t>Depth: Owns an organization's preventive-control strategy with security partners - the control catalog, its coverage, and the evidence it works - moving enforcement from review-time to platform-time. Evidenced by: Owns the guardrail catalog with the security team, moving a manual pre-launch review into an automated pipeline gate. Scope: organization.</t>
+        </is>
+      </c>
+      <c r="L26" s="4" t="inlineStr">
+        <is>
+          <t>Depth: Sets an organization-defining balance of enablement and control, accountable for guardrails that hold under audit and attack without throttling delivery. Evidenced by: Sets the company's default posture on where automation blocks versus warns, and defends it to auditors after an incident nearly reopens the debate. Scope: company.</t>
         </is>
       </c>
     </row>
@@ -2217,37 +2348,42 @@
       </c>
       <c r="E27" s="4" t="inlineStr">
         <is>
-          <t>Ward &amp; Beyer, "BeyondCorp: A New Approach to Enterprise Security" (;login:, 2014)</t>
+          <t>Govern identities, authentication, and least-privilege authorization across systems.</t>
         </is>
       </c>
       <c r="F27" s="4" t="inlineStr">
         <is>
-          <t>Depth: Requests and uses credentials through the sanctioned workflow, never hard-codes a secret, and reports exposed credentials immediately - and spots one in review. Scope: their own access hygiene.</t>
+          <t>Ward &amp; Beyer, BeyondCorp: A New Approach to Enterprise Security, ;login: 39(6), 6-11 (USENIX, 2014) — the identity-centric model behind least privilege, workload identity, and short-lived credentials.</t>
         </is>
       </c>
       <c r="G27" s="4" t="inlineStr">
         <is>
-          <t>Depth: Configures workload identity, scoped roles, and secret rotation for their component, removing standing permissions it no longer needs. Scope: one component's identity surface.</t>
+          <t>Depth: Provisions and deprovisions accounts from documented procedures, with approvals and access reviewed before activation. Evidenced by: Requests and uses credentials through the sanctioned workflow. Scope: task.</t>
         </is>
       </c>
       <c r="H27" s="4" t="inlineStr">
         <is>
-          <t>Depth: Designs the identity model for a capability - workload identity, short-lived credentials, least-privilege role structure, break-glass with audit - and reviews access designs for privilege-escalation paths before they ship. Scope: a capability's identity and secrets architecture.</t>
+          <t>Depth: Configures roles, group membership, and authentication factors independently for standard joiners, movers, and leavers. Evidenced by: Configures workload identity, scoped roles, and secret rotation for their component. Scope: component.</t>
         </is>
       </c>
       <c r="I27" s="4" t="inlineStr">
         <is>
-          <t>Depth: Builds identity infrastructure multiple teams authenticate through, and runs credential-model migrations - long-lived to short-lived, shared to workload identity - without breaking users. Scope: identity across multiple teams.</t>
+          <t>Depth: Resolves complex entitlement conflicts and designs least-privilege role models for ambiguous, cross-system access needs. Evidenced by: Designs the identity model for a capability. Scope: capability / domain (terminal level).</t>
         </is>
       </c>
       <c r="J27" s="4" t="inlineStr">
         <is>
-          <t>Depth: Owns the organization's identity architecture and its zero-trust roadmap, retiring standing privilege and shared secrets as measurable programs. Scope: organization-wide identity.</t>
+          <t>Depth: Defines the identity lifecycle and authorization architecture that other engineers adopt across the organization. Evidenced by: Builds identity infrastructure multiple teams authenticate through. Scope: multiple teams.</t>
         </is>
       </c>
       <c r="K27" s="4" t="inlineStr">
         <is>
-          <t>Depth: Sets company identity strategy across employee, workload, and customer boundaries, and represents it to auditors, partners, and executives. Scope: company identity posture.</t>
+          <t>Depth: Sets identity strategy, governs federation and privileged-access standards, and anticipates emerging access risks. Evidenced by: Owns the organization's identity architecture and its zero-trust roadmap. Scope: organization.</t>
+        </is>
+      </c>
+      <c r="L27" s="4" t="inlineStr">
+        <is>
+          <t>Depth: Defines what sound identity practice means for the field and shapes how others govern access. Evidenced by: Sets company identity strategy across employee, workload, and customer boundaries. Scope: company.</t>
         </is>
       </c>
     </row>
@@ -2274,37 +2410,42 @@
       </c>
       <c r="E28" s="4" t="inlineStr">
         <is>
-          <t>OpenSSF, *SLSA: Supply-chain Levels for Software Artifacts* (2021)</t>
+          <t>Verify provenance and integrity of dependencies, builds, and deployed artifacts.</t>
         </is>
       </c>
       <c r="F28" s="4" t="inlineStr">
         <is>
-          <t>Depth: Keeps dependencies current on their tasks and acts on vulnerability-scanner findings with guidance, distinguishing exploitable from noise with help. Scope: dependencies in their own changes.</t>
+          <t>OpenSSF, SLSA (Supply-chain Levels for Software Artifacts), Version 1.0 (2023) — the graded build-integrity standard the signing, provenance, and admission controls here implement.</t>
         </is>
       </c>
       <c r="G28" s="4" t="inlineStr">
         <is>
-          <t>Depth: Maintains their component's supply-chain hygiene - pinning, update cadence, accurate software inventories, signed artifacts - and remediates vulnerabilities within the team's SLA. Scope: one component's supply chain.</t>
+          <t>Depth: Verifies artifact provenance and signatures following documented checks, escalating anomalies for review. Evidenced by: Keeps dependencies current on their tasks and acts on vulnerability-scanner findings with guidance. Scope: task.</t>
         </is>
       </c>
       <c r="H28" s="4" t="inlineStr">
         <is>
-          <t>Depth: Designs a capability's pipeline to a stated supply-chain integrity level - provenance generation, signed artifacts, isolated builds, admission verification - and can show the attestation chain for any production artifact; leads the response when a dependency compromise hits. Scope: a capability's build-to-deploy integrity.</t>
+          <t>Depth: Configures signing, dependency scanning, and provenance controls independently for standard pipelines. Evidenced by: Maintains their component's supply-chain hygiene. Scope: component.</t>
         </is>
       </c>
       <c r="I28" s="4" t="inlineStr">
         <is>
-          <t>Depth: Builds supply-chain controls into the shared pipeline so every team inherits provenance and scanning by default. Scope: supply-chain posture across multiple teams.</t>
+          <t>Depth: Designs artifact-integrity and dependency-trust controls for complex, ambiguous supply chains. Evidenced by: Designs a capability's pipeline to a stated supply-chain integrity level. Scope: capability / domain (terminal level).</t>
         </is>
       </c>
       <c r="J28" s="4" t="inlineStr">
         <is>
-          <t>Depth: Owns the organization's supply-chain security program - target levels, coverage, exception burn-down - reported against a public roadmap. Scope: organization-wide supply chain.</t>
+          <t>Depth: Defines the supply-chain security architecture and verification patterns others adopt. Evidenced by: Builds supply-chain controls into the shared pipeline so every team inherits provenance and scanning by default. Scope: multiple teams.</t>
         </is>
       </c>
       <c r="K28" s="4" t="inlineStr">
         <is>
-          <t>Depth: Sets company supply-chain policy including third-party and vendor software, and answers for it to customers and regulators. Scope: company supply-chain posture.</t>
+          <t>Depth: Sets supply-chain assurance strategy and anticipates emerging artifact and dependency threats. Evidenced by: Owns the organization's supply-chain security program. Scope: organization.</t>
+        </is>
+      </c>
+      <c r="L28" s="4" t="inlineStr">
+        <is>
+          <t>Depth: Defines authoritative supply-chain security practice that shapes industry expectations. Evidenced by: Sets company supply-chain policy including third-party and vendor software. Scope: company.</t>
         </is>
       </c>
     </row>
@@ -2331,37 +2472,42 @@
       </c>
       <c r="E29" s="4" t="inlineStr">
         <is>
-          <t>NIST, *OSCAL - Open Security Controls Assessment Language* (1.0, 2021)</t>
+          <t>Bakes privacy, audit and regulatory controls into systems.</t>
         </is>
       </c>
       <c r="F29" s="4" t="inlineStr">
         <is>
-          <t>Depth: Follows the platform's compliance procedures accurately - change records, access reviews - and asks why a control exists rather than routing around it. Scope: their own work's compliance hygiene.</t>
+          <t>NIST, The NIST Cybersecurity Framework (CSF) 2.0, NIST CSWP 29 (2024) — makes compliance-by-default and continuous evidence collection a tooled practice rather than paperwork.</t>
         </is>
       </c>
       <c r="G29" s="4" t="inlineStr">
         <is>
-          <t>Depth: Automates evidence collection for their component's controls so audit requests are answered from systems, not screenshots. Scope: one component's control evidence.</t>
+          <t>Depth: Knows data handling has privacy implications; follows rules. Evidenced by: Follows the platform's compliance procedures accurately. Scope: task.</t>
         </is>
       </c>
       <c r="H29" s="4" t="inlineStr">
         <is>
-          <t>Depth: Maps a capability's controls to the frameworks the company answers to and designs them to be inherited - teams building on the capability get the control satisfied by default - and walks auditors through the design credibly. Scope: a capability's compliance surface.</t>
+          <t>Depth: Applies PII handling, redaction, residency and retention correctly. Evidenced by: Automates evidence collection for their component's controls. Scope: component.</t>
         </is>
       </c>
       <c r="I29" s="4" t="inlineStr">
         <is>
-          <t>Depth: Rationalizes overlapping control implementations across teams into shared, platform-enforced controls, cutting per-team audit effort measurably. Scope: compliance across multiple teams.</t>
+          <t>Depth: Designs for compliance (consent, audit trails, regional rules); owns readiness for a domain. Evidenced by: Maps a capability's controls to the frameworks the company answers to and designs them to be inherited. Scope: capability / domain (terminal level).</t>
         </is>
       </c>
       <c r="J29" s="4" t="inlineStr">
         <is>
-          <t>Depth: Owns the organization's compliance-as-code strategy with legal and security partners - which frameworks, which inherited controls, what the audit story is. Scope: organization-wide compliance architecture.</t>
+          <t>Depth: Expert at translating regulation into controls; represents engineering in audits. Evidenced by: Rationalizes overlapping control implementations across teams into shared, platform-enforced controls. Scope: multiple teams.</t>
         </is>
       </c>
       <c r="K29" s="4" t="inlineStr">
         <is>
-          <t>Depth: Shapes company posture on regulatory strategy where infrastructure is implicated - data residency, certifications worth pursuing - as an input to market decisions. Scope: company regulatory posture.</t>
+          <t>Depth: Sets org compliance strategy; anticipates regulation. Evidenced by: Owns the organization's compliance-as-code strategy with legal and security partners. Scope: organization.</t>
+        </is>
+      </c>
+      <c r="L29" s="4" t="inlineStr">
+        <is>
+          <t>Depth: Authoritative on the landscape; trusted interface to regulators. Evidenced by: Shapes company posture on regulatory strategy where infrastructure is implicated. Scope: company.</t>
         </is>
       </c>
     </row>
@@ -2388,37 +2534,42 @@
       </c>
       <c r="E30" s="4" t="inlineStr">
         <is>
-          <t>Procida, *Diataxis* (2017-)</t>
+          <t>Structuring, writing, and organizing docs so information is findable and usable.</t>
         </is>
       </c>
       <c r="F30" s="4" t="inlineStr">
         <is>
-          <t>Depth: Fixes documentation errors they hit instead of working around them, and writes accurate task-level notes others can follow. Scope: docs for their own tasks.</t>
+          <t>Procida, Diataxis: A Systematic Framework for Technical Documentation (diataxis.fr, accessed 2026-07) — the framework behind docs organized by user need rather than system internals.</t>
         </is>
       </c>
       <c r="G30" s="4" t="inlineStr">
         <is>
-          <t>Depth: Keeps their component's docs shippable - a quickstart that works, reference that matches behavior - and treats doc bugs from users as real bugs. Scope: one component's documentation.</t>
+          <t>Depth: Writes and updates doc pages within an existing structure under guidance. Evidenced by: Fixes documentation errors they hit instead of working around them. Scope: task.</t>
         </is>
       </c>
       <c r="H30" s="4" t="inlineStr">
         <is>
-          <t>Depth: Designs a capability's documentation as part of the product - tutorial, how-to, reference, and explanation each doing their distinct job - instrumented for where readers fail, with recurring support questions treated as doc defects to fix at the source. Scope: a capability's doc set and information architecture.</t>
+          <t>Depth: Authors and organizes documentation for a product area with normal review. Evidenced by: Keeps their component's docs shippable. Scope: component.</t>
         </is>
       </c>
       <c r="I30" s="4" t="inlineStr">
         <is>
-          <t>Depth: Sets documentation conventions multiple teams follow and builds the docs infrastructure - templates, testable examples, freshness checks - that keeps them true. Scope: documentation across multiple teams.</t>
+          <t>Depth: Independently architects coherent doc structures for complex, evolving products. Evidenced by: Designs a capability's documentation as part of the product. Scope: capability / domain (terminal level).</t>
         </is>
       </c>
       <c r="J30" s="4" t="inlineStr">
         <is>
-          <t>Depth: Owns the organization's developer-facing knowledge strategy, making docs quality a reviewed, measured property of every platform launch. Scope: organization-wide platform documentation.</t>
+          <t>Depth: Defines information-architecture standards others adopt and restructures tangled doc sets. Evidenced by: Sets documentation conventions multiple teams follow. Scope: multiple teams.</t>
         </is>
       </c>
       <c r="K30" s="4" t="inlineStr">
         <is>
-          <t>Depth: Writes the canonical company documents - architecture primers, technology strategy - that onboard leaders and engineers alike for years. Scope: company-level canon.</t>
+          <t>Depth: Sets the org's documentation strategy and anticipates structural scaling needs. Evidenced by: Owns the organization's developer-facing knowledge strategy. Scope: organization.</t>
+        </is>
+      </c>
+      <c r="L30" s="4" t="inlineStr">
+        <is>
+          <t>Depth: Defines great developer documentation and information architecture for the field. Evidenced by: Writes the canonical company documents. Scope: company.</t>
         </is>
       </c>
     </row>
@@ -2445,37 +2596,42 @@
       </c>
       <c r="E31" s="4" t="inlineStr">
         <is>
-          <t>Winters, Manshreck &amp; Wright, *Software Engineering at Google* (2020), design-docs chapters</t>
+          <t>Conveys ideas clearly to the right audience.</t>
         </is>
       </c>
       <c r="F31" s="4" t="inlineStr">
         <is>
-          <t>Depth: Writes clear tickets, PR descriptions, and status updates that need no follow-up questions, and asks questions in review that improve their understanding. Scope: their own changes and task communication.</t>
+          <t>Winters, Manshreck &amp; Wright, Software Engineering at Google: Lessons Learned from Programming Over Time (O'Reilly, 2020) — grounds decision-oriented writing as the mechanism by which trade-offs get decided once and stick.</t>
         </is>
       </c>
       <c r="G31" s="4" t="inlineStr">
         <is>
-          <t>Depth: Writes short design docs that state the problem, options, and recommendation, readable by a non-expert teammate, and records the decision so others can revisit it. Scope: component decisions.</t>
+          <t>Depth: Communicates status clearly; documentation is accurate. Evidenced by: Writes clear tickets, PR descriptions, and status updates that need no follow-up questions. Scope: task.</t>
         </is>
       </c>
       <c r="H31" s="4" t="inlineStr">
         <is>
-          <t>Depth: Writes design docs that make complex trade-offs decidable by non-experts - alternatives honestly weighed, decision record kept - tailoring the same content for engineers, users, and leaders, and runs technical discussions that converge instead of circling. Scope: capability-level decisions.</t>
+          <t>Depth: Writes clear design notes, runbooks and PRs; explains trade-offs without overselling. Evidenced by: Writes short design docs that state the problem, options, and recommendation. Scope: component.</t>
         </is>
       </c>
       <c r="I31" s="4" t="inlineStr">
         <is>
-          <t>Depth: Writes the cross-team proposals that settle contested technical questions, absorbing objections into the doc rather than the hallway, so decisions are made once and stick. Scope: technical discourse across multiple teams.</t>
+          <t>Depth: Writes design docs that drive decisions; translates technical risk for non-technical stakeholders. Evidenced by: Writes design docs that make complex trade-offs decidable by non-experts. Scope: capability / domain (terminal level).</t>
         </is>
       </c>
       <c r="J31" s="4" t="inlineStr">
         <is>
-          <t>Depth: Sets the organization's bar for decision writing - templates, norms, decision records, review forums - and models it in documents others circulate as examples. Scope: organization-wide technical communication.</t>
+          <t>Depth: Expert at making complex capability/risk legible to executives without dumbing it down; RFCs align orgs. Evidenced by: Writes the cross-team proposals that settle contested technical questions. Scope: multiple teams.</t>
         </is>
       </c>
       <c r="K31" s="4" t="inlineStr">
         <is>
-          <t>Depth: Communicates deep technical trade-offs to executives in the language of business risk without losing correctness - company technical direction in writing both audiences act on. Scope: company-level technical communication.</t>
+          <t>Depth: Strategy memos leadership acts on; org-wide and external reach. Evidenced by: Sets the organization's bar for decision writing. Scope: organization.</t>
+        </is>
+      </c>
+      <c r="L31" s="4" t="inlineStr">
+        <is>
+          <t>Depth: A clarifying voice at company scale; externally recognized. Evidenced by: Communicates deep technical trade-offs to executives in the language of business risk without losing correctness. Scope: company.</t>
         </is>
       </c>
     </row>
@@ -2502,37 +2658,42 @@
       </c>
       <c r="E32" s="4" t="inlineStr">
         <is>
-          <t>CNCF TAG App Delivery, *Platform Engineering Maturity Model* (2023)</t>
+          <t>Growing and nurturing developer communities and representing their needs internally.</t>
         </is>
       </c>
       <c r="F32" s="4" t="inlineStr">
         <is>
-          <t>Depth: Answers user questions in support channels accurately or routes them fast, and demos their own work clearly to the team. Scope: individual users' questions.</t>
+          <t>CNCF TAG App Delivery, Platform Engineering Maturity Model (2023) — frames adoption-by-evangelism as a maturity outcome the platform earns, not a mandate.</t>
         </is>
       </c>
       <c r="G32" s="4" t="inlineStr">
         <is>
-          <t>Depth: Runs enablement for their component - demos, office hours, onboarding sessions, launch notes users actually read - and turns repeated questions into docs or fixes. Scope: one component's user community.</t>
+          <t>Depth: Engages community channels and answers routine questions under guidance. Evidenced by: Answers user questions in support channels accurately or routes them fast. Scope: task.</t>
         </is>
       </c>
       <c r="H32" s="4" t="inlineStr">
         <is>
-          <t>Depth: Drives adoption of a capability through evangelism rather than mandate - launch communications, migration workshops, early-adopter partnerships, champion networks inside customer teams - converting skeptical teams with working proof, not slideware; adoption curves move when they run a campaign. Scope: a capability's internal market.</t>
+          <t>Depth: Grows and supports a developer community segment with normal review. Evidenced by: Runs enablement for their component. Scope: component.</t>
         </is>
       </c>
       <c r="I32" s="4" t="inlineStr">
         <is>
-          <t>Depth: Builds the enablement machinery platform teams share - champions programs, internal conferences, onboarding curricula, launch playbooks - that outlive any one campaign. Scope: advocacy infrastructure across multiple teams.</t>
+          <t>Depth: Independently builds thriving communities and defuses tense community conflicts. Evidenced by: Drives adoption of a capability through evangelism rather than mandate. Scope: capability / domain (terminal level).</t>
         </is>
       </c>
       <c r="J32" s="4" t="inlineStr">
         <is>
-          <t>Depth: Owns the platform's internal brand and narrative - leaders and engineers describe what the platform is for in the platform team's own words, and internal satisfaction signals show it. Scope: organization-wide platform narrative.</t>
+          <t>Depth: Defines community-building practices others adopt and revives flagging communities. Evidenced by: Builds the enablement machinery platform teams share. Scope: multiple teams.</t>
         </is>
       </c>
       <c r="K32" s="4" t="inlineStr">
         <is>
-          <t>Depth: Represents the company's engineering platform externally - talks, publications, community leadership - in ways that visibly aid hiring and credibility; inside, their voice moves executive opinion. Scope: company reputation and industry.</t>
+          <t>Depth: Sets the org's community strategy and anticipates where developer interest is shifting. Evidenced by: Owns the platform's internal brand and narrative. Scope: organization.</t>
+        </is>
+      </c>
+      <c r="L32" s="4" t="inlineStr">
+        <is>
+          <t>Depth: Defines what great developer advocacy means and is externally recognized for it. Evidenced by: Represents the company's engineering platform externally. Scope: company.</t>
         </is>
       </c>
     </row>
@@ -2559,37 +2720,42 @@
       </c>
       <c r="E33" s="4" t="inlineStr">
         <is>
-          <t>Larson, *Staff Engineer: Leadership Beyond the Management Track* (2021)</t>
+          <t>Aligning leadership and cross-functional stakeholders around product direction and trade-offs.</t>
         </is>
       </c>
       <c r="F33" s="4" t="inlineStr">
         <is>
-          <t>Depth: Communicates status honestly and early - especially bad news - and asks stakeholders clarifying questions before building. Scope: their own tasks' stakeholders.</t>
+          <t>Larson, Staff Engineer: Leadership Beyond the Management Track (self-published, 2021) — grounds the progression from reporting status to advising leadership as a peer.</t>
         </is>
       </c>
       <c r="G33" s="4" t="inlineStr">
         <is>
-          <t>Depth: Manages expectations for their component with its consuming teams - what is supported, what is coming, what will not happen - in writing, closing the loop on every commitment made. Scope: one component's consumers.</t>
+          <t>Depth: Prepares updates and gathers input for stakeholders under direction. Evidenced by: Communicates status honestly and early - especially bad news. Scope: task.</t>
         </is>
       </c>
       <c r="H33" s="4" t="inlineStr">
         <is>
-          <t>Depth: Runs the stakeholder relationships for a capability - chooses and names the interaction mode for each relationship, renegotiates it when it stops fitting, and has the hard conversations about what the platform will not do; escalations from their stakeholders are rare and non-surprising. Scope: a capability's customer and leadership stakeholders.</t>
+          <t>Depth: Manages routine stakeholder relationships and communications with normal review. Evidenced by: Manages expectations for their component with its consuming teams. Scope: component.</t>
         </is>
       </c>
       <c r="I33" s="4" t="inlineStr">
         <is>
-          <t>Depth: Aligns competing demands from multiple teams into a roadmap each can live with, making the trade-offs and losers explicit rather than hidden, and steps into the conversations where trust between platform and a customer team has broken. Scope: stakeholders across multiple teams.</t>
+          <t>Depth: Independently aligns conflicting stakeholders and navigates tense executive conversations. Evidenced by: Runs the stakeholder relationships for a capability. Scope: capability / domain (terminal level).</t>
         </is>
       </c>
       <c r="J33" s="4" t="inlineStr">
         <is>
-          <t>Depth: Manages the platform's relationship with organization leadership - funding cases, expectation setting, honest reporting when bets miss. Scope: organization-level stakeholders.</t>
+          <t>Depth: Defines stakeholder-engagement approaches others adopt and brokers the hardest alignment. Evidenced by: Aligns competing demands from multiple teams into a roadmap each can live with. Scope: multiple teams.</t>
         </is>
       </c>
       <c r="K33" s="4" t="inlineStr">
         <is>
-          <t>Depth: Operates at executive level as the technical counterpart on company decisions that touch the platform - vendor deals, diligence, board-visible commitments. Scope: company-level stakeholders.</t>
+          <t>Depth: Sets executive-engagement strategy and anticipates leadership concerns before they arise. Evidenced by: Manages the platform's relationship with organization leadership. Scope: organization.</t>
+        </is>
+      </c>
+      <c r="L33" s="4" t="inlineStr">
+        <is>
+          <t>Depth: Defines exemplary stakeholder management for the discipline and is externally credible on it. Evidenced by: Operates at executive level as the technical counterpart on company decisions that touch the platform. Scope: company.</t>
         </is>
       </c>
     </row>
@@ -2616,37 +2782,42 @@
       </c>
       <c r="E34" s="4" t="inlineStr">
         <is>
-          <t>Skelton &amp; Pais, *Team Topologies* (2019) - team interaction modes</t>
+          <t>Works productively with others toward shared goals.</t>
         </is>
       </c>
       <c r="F34" s="4" t="inlineStr">
         <is>
-          <t>Depth: Works in the open - asks questions in public channels, asks for help before being stuck a full day, shares progress and blockers early, and follows through on commitments to teammates. Scope: within their team.</t>
+          <t>Skelton &amp; Pais, Team Topologies (IT Revolution, 2019) — gives platform-to-team relationships a deliberate design vocabulary rather than ad-hoc liaison work.</t>
         </is>
       </c>
       <c r="G34" s="4" t="inlineStr">
         <is>
-          <t>Depth: Partners directly with the teams that consume their component - joins their planning when changes affect them, embeds with a consuming team when needed, and brings what they learn back as platform improvements. Scope: neighboring teams.</t>
+          <t>Depth: Responsive to feedback; pairs willingly; asks for help appropriately. Evidenced by: Works in the open. Scope: task.</t>
         </is>
       </c>
       <c r="H34" s="4" t="inlineStr">
         <is>
-          <t>Depth: Builds the working relationships a capability depends on - negotiates interfaces and timelines with dependent teams, resolves cross-team disagreements by finding the shared goal and proposing options rather than positions - and is who other teams request by name. Scope: the web of teams around a capability.</t>
+          <t>Depth: Collaborates smoothly with adjacent functions; handles disagreement constructively. Evidenced by: Partners directly with the teams that consume their component. Scope: component.</t>
         </is>
       </c>
       <c r="I34" s="4" t="inlineStr">
         <is>
-          <t>Depth: Creates the collaboration structures that let teams decide without escalation - working groups, RFC forums, decision venues where cross-team platform issues actually get settled. Scope: multiple teams.</t>
+          <t>Depth: Builds strong cross-team relationships; resolves friction directly. Evidenced by: Builds the working relationships a capability depends on. Scope: capability / domain (terminal level).</t>
         </is>
       </c>
       <c r="J34" s="4" t="inlineStr">
         <is>
-          <t>Depth: Brokers alignment between organizations - platform, product, security, and finance leaders act on shared plans they assembled - and repairs broken inter-team relationships in the organization's most visible forums. Scope: across org boundaries.</t>
+          <t>Depth: Expert at aligning teams with competing priorities; mediates disputes between senior people. Evidenced by: Creates the collaboration structures that let teams decide without escalation. Scope: multiple teams.</t>
         </is>
       </c>
       <c r="K34" s="4" t="inlineStr">
         <is>
-          <t>Depth: Aligns the company's technical factions - the durable settlements between competing technical camps carry their fingerprints. Scope: company.</t>
+          <t>Depth: Creates the forums and processes through which collaboration happens. Evidenced by: Brokers alignment between organizations. Scope: organization.</t>
+        </is>
+      </c>
+      <c r="L34" s="4" t="inlineStr">
+        <is>
+          <t>Depth: Builds coalitions at company scale and externally. Evidenced by: Aligns the company's technical factions. Scope: company.</t>
         </is>
       </c>
     </row>
@@ -2673,37 +2844,42 @@
       </c>
       <c r="E35" s="4" t="inlineStr">
         <is>
-          <t>McConnell, *Software Estimation: Demystifying the Black Art* (2006)</t>
+          <t>Forecasts and plans work credibly.</t>
         </is>
       </c>
       <c r="F35" s="4" t="inlineStr">
         <is>
-          <t>Depth: Breaks an assigned task into steps, estimates them honestly, and flags slippage as soon as it is visible rather than at the deadline. Scope: their own task plans.</t>
+          <t>McConnell, Software Estimation: Demystifying the Black Art (Microsoft Press, 2006) — establishes estimates as probability ranges refined by decomposition and historical data.</t>
         </is>
       </c>
       <c r="G35" s="4" t="inlineStr">
         <is>
-          <t>Depth: Plans component-level work in increments that ship value early - milestones, dependencies, a definition of done - and re-plans openly when discovery changes the picture; their estimates are trusted inputs to team commitments. Scope: one component's plan.</t>
+          <t>Depth: Learns to estimate; surfaces blockers; plans own tasks with guidance. Evidenced by: Breaks an assigned task into steps, estimates them honestly, and flags slippage as soon as it is visible. Scope: task.</t>
         </is>
       </c>
       <c r="H35" s="4" t="inlineStr">
         <is>
-          <t>Depth: Plans a capability across quarters with explicit risk buffers - sequencing platform work against customer-team launch dates, reserving capacity for interrupts - and their dates are ones other teams schedule against; replans visibly when assumptions break. Scope: a capability's roadmap execution.</t>
+          <t>Depth: Estimates scoped work realistically; plans own 1-3 week projects. Evidenced by: Plans component-level work in increments that ship value early. Scope: component.</t>
         </is>
       </c>
       <c r="I35" s="4" t="inlineStr">
         <is>
-          <t>Depth: Builds plans that coordinate multiple teams' streams - dependencies mapped, integration points dated, slack placed where risk is - and keeps them credible through change. Scope: multi-team programs.</t>
+          <t>Depth: Plans quarter-scale, multi-workstream efforts including dependencies. Evidenced by: Plans a capability across quarters with explicit risk buffers. Scope: capability / domain (terminal level).</t>
         </is>
       </c>
       <c r="J35" s="4" t="inlineStr">
         <is>
-          <t>Depth: Runs the organization's platform planning cycle, reconciling bottom-up team plans with top-down strategy into commitments leadership can rely on. Scope: organization-wide planning.</t>
+          <t>Depth: Expert at planning large programs; anticipates risk early. Evidenced by: Builds plans that coordinate multiple teams' streams. Scope: multiple teams.</t>
         </is>
       </c>
       <c r="K35" s="4" t="inlineStr">
         <is>
-          <t>Depth: Plans in company horizons - multi-year technical programs whose sequencing survives reorgs and leadership changes. Scope: company planning horizon.</t>
+          <t>Depth: Plans org-level programs across quarters/years. Evidenced by: Runs the organization's platform planning cycle. Scope: organization.</t>
+        </is>
+      </c>
+      <c r="L35" s="4" t="inlineStr">
+        <is>
+          <t>Depth: Shapes how the company plans major technical change. Evidenced by: Sets the multi-year planning cycle major technical bets are sequenced against, and defends the sequencing to the executives funding it. Scope: company.</t>
         </is>
       </c>
     </row>
@@ -2730,37 +2906,42 @@
       </c>
       <c r="E36" s="4" t="inlineStr">
         <is>
-          <t>Reinertsen, *The Principles of Product Development Flow* (2009)</t>
+          <t>Weighs cost, value, risk and timing.</t>
         </is>
       </c>
       <c r="F36" s="4" t="inlineStr">
         <is>
-          <t>Depth: Works their queue in the agreed order and raises it explicitly when a new ask conflicts with committed work rather than silently absorbing it. Scope: their own queue.</t>
+          <t>Reinertsen, The Principles of Product Development Flow: Second Generation Lean Product Development (Celeritas, 2009) — gives trade-off and scope-cut decisions an economic footing instead of loudest-voice ordering.</t>
         </is>
       </c>
       <c r="G36" s="4" t="inlineStr">
         <is>
-          <t>Depth: Orders their component's backlog by user impact and cost of delay, defending the ordering when challenged and saying no with a reason and an alternative. Scope: one component's backlog.</t>
+          <t>Depth: Works highest-priority-first when told the priorities. Evidenced by: Works their queue in the agreed order and raises it explicitly when a new ask conflicts with committed work. Scope: task.</t>
         </is>
       </c>
       <c r="H36" s="4" t="inlineStr">
         <is>
-          <t>Depth: Sequences a capability's investment across feature work, reliability, migrations, and toil paydown using explicit cost-of-delay reasoning - cuts scope deliberately under pressure, publishes the not-doing list, and says no in writing with the reasoning attached. Scope: a capability's investment mix.</t>
+          <t>Depth: Makes sound priority calls within scope; time-boxes uncertain work. Evidenced by: Orders their component's backlog by user impact and cost of delay. Scope: component.</t>
         </is>
       </c>
       <c r="I36" s="4" t="inlineStr">
         <is>
-          <t>Depth: Arbitrates priority across teams competing for shared platform capacity, making the economic trade-offs visible so decisions survive the meeting. Scope: prioritization across multiple teams.</t>
+          <t>Depth: Balances cost/value/risk across a domain; resists hype; decisions hold up over months. Evidenced by: Sequences a capability's investment across feature work, reliability, migrations, and toil paydown using explicit cost-of-delay reasoning. Scope: capability / domain (terminal level).</t>
         </is>
       </c>
       <c r="J36" s="4" t="inlineStr">
         <is>
-          <t>Depth: Sets the organization's platform investment allocation - run versus grow versus transform - rebalancing it on evidence and killing zombie projects. Scope: organization-wide investment.</t>
+          <t>Depth: Expert at portfolio-level trade-offs; surfaces hidden assumptions; trusted tiebreaker. Evidenced by: Arbitrates priority across teams competing for shared platform capacity. Scope: multiple teams.</t>
         </is>
       </c>
       <c r="K36" s="4" t="inlineStr">
         <is>
-          <t>Depth: Advises company leadership on technology sequencing - what to do now, next, never - with reasoning that holds up years later. Scope: company sequencing.</t>
+          <t>Depth: Sets decision frameworks for the org. Evidenced by: Sets the organization's platform investment allocation. Scope: organization.</t>
+        </is>
+      </c>
+      <c r="L36" s="4" t="inlineStr">
+        <is>
+          <t>Depth: Influences company strategic direction through judgment. Evidenced by: Advises company leadership on technology sequencing. Scope: company.</t>
         </is>
       </c>
     </row>
@@ -2787,37 +2968,42 @@
       </c>
       <c r="E37" s="4" t="inlineStr">
         <is>
-          <t>Lave &amp; Wenger, *Situated Learning: Legitimate Peripheral Participation* (1991)</t>
+          <t>Grows other people's capability.</t>
         </is>
       </c>
       <c r="F37" s="4" t="inlineStr">
         <is>
-          <t>Depth: Asks for help effectively - showing what they tried - and passes on what they learn in docs and team channels where the next new person will find it. Scope: their own learning loop.</t>
+          <t>Wenger, Communities of Practice: Learning, Meaning, and Identity (Cambridge University Press, 1998) — expertise spreads through communities of practice, from peripheral participation inward.</t>
         </is>
       </c>
       <c r="G37" s="4" t="inlineStr">
         <is>
-          <t>Depth: Onboards new teammates with pairing and honest context, and gives specific, kind feedback in reviews that juniors visibly act on. Scope: individuals on their team.</t>
+          <t>Depth: Receptive to mentoring; shares what they learn. Evidenced by: Asks for help effectively - showing what they tried - and passes on what they learn. Scope: task.</t>
         </is>
       </c>
       <c r="H37" s="4" t="inlineStr">
         <is>
-          <t>Depth: Mentors engineers deliberately - stretch work matched to growth edges, questions before answers, honest feedback delivered kindly - and mentees' independence visibly increases; teaches internal users to self-serve rather than doing it for them, and runs the forums where knowledge crosses the team. Scope: engineers on their team and among their capability's users.</t>
+          <t>Depth: Helps onboard teammates; informally mentors juniors. Evidenced by: Onboards new teammates with pairing and honest context. Scope: component.</t>
         </is>
       </c>
       <c r="I37" s="4" t="inlineStr">
         <is>
-          <t>Depth: Grows senior engineers across teams toward staff scope - sponsoring visible work, delegating real ownership with backup, coaching design judgment - and is named in others' promotion cases as a reason. Scope: engineers across multiple teams.</t>
+          <t>Depth: Coaches engineers with growth-oriented feedback; measurably improves a team's skill. Evidenced by: Mentors engineers deliberately. Scope: capability / domain (terminal level).</t>
         </is>
       </c>
       <c r="J37" s="4" t="inlineStr">
         <is>
-          <t>Depth: Builds the organization's technical talent systems - mentoring structures, promotion calibration input, senior hiring bar - that develop engineers at scale. Scope: organization-wide talent development.</t>
+          <t>Depth: Develops future leads across teams; shapes hiring and onboarding. Evidenced by: Grows senior engineers across teams toward staff scope. Scope: multiple teams.</t>
         </is>
       </c>
       <c r="K37" s="4" t="inlineStr">
         <is>
-          <t>Depth: Develops the company's next generation of principal-level technical leaders and shapes the culture they inherit. Scope: company technical leadership pipeline.</t>
+          <t>Depth: Develops senior engineers and leaders; builds culture deliberately. Evidenced by: Builds the organization's technical talent systems. Scope: organization.</t>
+        </is>
+      </c>
+      <c r="L37" s="4" t="inlineStr">
+        <is>
+          <t>Depth: Develops the next generation of top talent; legacy outlasts tenure. Evidenced by: Develops the company's next generation of principal-level technical leaders. Scope: company.</t>
         </is>
       </c>
     </row>
@@ -2844,37 +3030,42 @@
       </c>
       <c r="E38" s="4" t="inlineStr">
         <is>
-          <t>Nygard, "Documenting Architecture Decisions" (2011)</t>
+          <t>Shapes technical direction beyond own work.</t>
         </is>
       </c>
       <c r="F38" s="4" t="inlineStr">
         <is>
-          <t>Depth: Forms and voices technical opinions in team discussions, connecting their tasks to the team's direction, and changes their mind visibly when shown better evidence. Scope: their team's decisions.</t>
+          <t>Nygard, Documenting Architecture Decisions (Cognitect blog, 2011) — the practice behind written, revisitable decisions from component decision records to company direction.</t>
         </is>
       </c>
       <c r="G38" s="4" t="inlineStr">
         <is>
-          <t>Depth: Proposes direction within their component - a refactor worth doing, a technology worth adopting - with a written case that weighs alternatives, and sees it through decision to done. Scope: one component's direction.</t>
+          <t>Depth: Contributes informed opinions in technical discussions. Evidenced by: Raises a concrete thundering-herd failure scenario against a proposed retry strategy in a design review, and the design changes because of it. Scope: task.</t>
         </is>
       </c>
       <c r="H38" s="4" t="inlineStr">
         <is>
-          <t>Depth: Sets technical direction for a capability - a written strategy naming the diagnosis, the bet, and what is deliberately not being done, decided through proposals that gather real dissent - revisiting it on evidence rather than sunk cost, and disagreeing-and-committing out loud when overruled. Scope: a capability's technical strategy.</t>
+          <t>Depth: Influences component-level decisions through credibility. Evidenced by: Proposes direction within their component. Scope: component.</t>
         </is>
       </c>
       <c r="I38" s="4" t="inlineStr">
         <is>
-          <t>Depth: Aligns multiple teams behind a shared technical direction without authority over them - the written proposal, the roadshow, the coalition, the early wins that make it real. Scope: direction across multiple teams.</t>
+          <t>Depth: Sets technical direction for a domain; others align to their calls. Evidenced by: Picks the message-queue technology a capability standardizes on for its next migration cycle, and engineers building on it align their designs to that call without relitigating it. Scope: capability / domain (terminal level).</t>
         </is>
       </c>
       <c r="J38" s="4" t="inlineStr">
         <is>
-          <t>Depth: Writes the organization's technical strategy and makes it operational - reflected in funding, staffing, and what teams say no to; teams cite it in their own planning. Scope: organization-wide technical strategy.</t>
+          <t>Depth: Shapes how multiple teams approach problems; trusted tiebreaker. Evidenced by: Aligns multiple teams behind a shared technical direction without authority over them. Scope: multiple teams.</t>
         </is>
       </c>
       <c r="K38" s="4" t="inlineStr">
         <is>
-          <t>Depth: Sets company-level technical direction - the few bets that define engineering for years - and is accountable for their outcome. Scope: company technical strategy.</t>
+          <t>Depth: Influences org-wide technical strategy. Evidenced by: Writes the organization's technical strategy and makes it operational. Scope: organization.</t>
+        </is>
+      </c>
+      <c r="L38" s="4" t="inlineStr">
+        <is>
+          <t>Depth: Influences company strategic direction through insight. Evidenced by: Sets company-level technical direction. Scope: company.</t>
         </is>
       </c>
     </row>
@@ -4712,277 +4903,1086 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A38"/>
+  <dimension ref="A1:D68"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="110" customWidth="1" min="1" max="1"/>
+    <col width="30" customWidth="1" min="1" max="1"/>
+    <col width="70" customWidth="1" min="2" max="2"/>
+    <col width="40" customWidth="1" min="3" max="3"/>
+    <col width="45" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Sources</t>
+          <t>Framework</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Source</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Grounds</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Link</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="4" t="inlineStr">
         <is>
-          <t>Allspaw, "Blameless PostMortems and a Just Culture" (Etsy Code as Craft, 2012)</t>
+          <t>Feedback loops, cognitive load, flow state as the measurable drivers of developer productivity</t>
+        </is>
+      </c>
+      <c r="B2" s="4" t="inlineStr">
+        <is>
+          <t>Noda, Storey, Forsgren &amp; Greiler, DevEx: What Actually Drives Productivity, ACM Queue 21(2) (2023)</t>
+        </is>
+      </c>
+      <c r="C2" s="4" t="inlineStr">
+        <is>
+          <t>Internal user research</t>
+        </is>
+      </c>
+      <c r="D2" s="4" t="inlineStr">
+        <is>
+          <t>https://queue.acm.org/detail.cfm?id=3595878</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="4" t="inlineStr">
         <is>
-          <t>Amazon Web Services, *Well-Architected Framework* (2015-)</t>
+          <t>Empirical linkage between deployment/release engineering maturity and organizational performance</t>
+        </is>
+      </c>
+      <c r="B3" s="4" t="inlineStr">
+        <is>
+          <t>Forsgren, Humble &amp; Kim, Accelerate: The Science of Lean Software and DevOps (IT Revolution Press, 2018)</t>
+        </is>
+      </c>
+      <c r="C3" s="4" t="inlineStr">
+        <is>
+          <t>Adoption &amp; success metrics</t>
+        </is>
+      </c>
+      <c r="D3" s="4" t="inlineStr">
+        <is>
+          <t>https://itrevolution.com/product/accelerate/</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="4" t="inlineStr">
         <is>
-          <t>Beyer, Jones, Petoff &amp; Murphy (eds.), *Site Reliability Engineering* (O'Reilly, 2016)</t>
-        </is>
-      </c>
+          <t>Team boundaries; org-level team formation patterns</t>
+        </is>
+      </c>
+      <c r="B4" s="4" t="inlineStr">
+        <is>
+          <t>Skelton &amp; Pais, Team Topologies (IT Revolution, 2019)</t>
+        </is>
+      </c>
+      <c r="C4" s="4" t="inlineStr">
+        <is>
+          <t>Thinnest viable platform</t>
+        </is>
+      </c>
+      <c r="D4" s="4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="4" t="inlineStr">
         <is>
-          <t>Beyer, Jones, Petoff &amp; Murphy (eds.), *Site Reliability Engineering* (O'Reilly, 2016), toil chapter</t>
+          <t>Org-level product strategy vs. output-shipping; grounds strategic/commercial leveling</t>
+        </is>
+      </c>
+      <c r="B5" s="4" t="inlineStr">
+        <is>
+          <t>Perri, Escaping the Build Trap: How Effective Product Management Creates Real Value (O'Reilly, 2018)</t>
+        </is>
+      </c>
+      <c r="C5" s="4" t="inlineStr">
+        <is>
+          <t>Platform roadmap &amp; prioritization</t>
+        </is>
+      </c>
+      <c r="D5" s="4" t="inlineStr">
+        <is>
+          <t>https://www.oreilly.com/library/view/escaping-the-build/9781491973783/</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="4" t="inlineStr">
         <is>
-          <t>Bottcher, "What I Talk About When I Talk About Platforms" (martinfowler.com, 2018)</t>
+          <t>Origin of the golden-path/paved-road pattern for internal platforms</t>
+        </is>
+      </c>
+      <c r="B6" s="4" t="inlineStr">
+        <is>
+          <t>Spotify Engineering, How We Use Golden Paths to Solve Fragmentation in Our Software Ecosystem (Spotify Engineering Blog, 2020)</t>
+        </is>
+      </c>
+      <c r="C6" s="4" t="inlineStr">
+        <is>
+          <t>Golden paths &amp; paved roads</t>
+        </is>
+      </c>
+      <c r="D6" s="4" t="inlineStr">
+        <is>
+          <t>https://engineering.atspotify.com/2020/08/how-we-use-golden-paths-to-solve-fragmentation-in-our-software-ecosystem/</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="4" t="inlineStr">
         <is>
-          <t>Burns, Grant, Oppenheimer, Brewer &amp; Wilkes, "Borg, Omega, and Kubernetes" (ACM Queue, 2016)</t>
+          <t>Foundational cognitive load theory; extraneous vs. intrinsic load -- DOI 403s to automated clients (Wiley) but title/journal/vol/pages confirmed by WebSearch</t>
+        </is>
+      </c>
+      <c r="B7" s="4" t="inlineStr">
+        <is>
+          <t>Sweller, Cognitive Load During Problem Solving: Effects on Learning, Cognitive Science 12(2), 257-285 (1988)</t>
+        </is>
+      </c>
+      <c r="C7" s="4" t="inlineStr">
+        <is>
+          <t>Cognitive load reduction</t>
+        </is>
+      </c>
+      <c r="D7" s="4" t="inlineStr">
+        <is>
+          <t>https://doi.org/10.1207/s15516709cog1202_4</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="4" t="inlineStr">
         <is>
-          <t>CNCF TAG App Delivery, *Platform Engineering Maturity Model* (2023)</t>
+          <t>Conway's Law: system design mirrors the communication structure of the organization that builds it</t>
+        </is>
+      </c>
+      <c r="B8" s="4" t="inlineStr">
+        <is>
+          <t>Conway, How Do Committees Invent?, Datamation 14(4), 28-31 (1968)</t>
+        </is>
+      </c>
+      <c r="C8" s="4" t="inlineStr">
+        <is>
+          <t>Platform system design</t>
+        </is>
+      </c>
+      <c r="D8" s="4" t="inlineStr">
+        <is>
+          <t>https://www.melconway.com/Home/Committees_Paper.html</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="4" t="inlineStr">
         <is>
-          <t>Cohn (2009) as refined by Vocke, "The Practical Test Pyramid" (2018)</t>
+          <t>Distinguishes programming from org-scale software engineering; anchors org-wide standard-setting levels</t>
+        </is>
+      </c>
+      <c r="B9" s="4" t="inlineStr">
+        <is>
+          <t>Winters, Manshreck &amp; Wright, Software Engineering at Google: Lessons Learned from Programming Over Time (O'Reilly, 2020)</t>
+        </is>
+      </c>
+      <c r="C9" s="4" t="inlineStr">
+        <is>
+          <t>API &amp; interface design</t>
+        </is>
+      </c>
+      <c r="D9" s="4" t="inlineStr">
+        <is>
+          <t>https://abseil.io/resources/swe-book</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="4" t="inlineStr">
         <is>
-          <t>Conway, "How Do Committees Invent?" (Datamation, 1968)</t>
+          <t>Refactoring discipline; anchors maintainability leveling</t>
+        </is>
+      </c>
+      <c r="B10" s="4" t="inlineStr">
+        <is>
+          <t>Fowler, Refactoring: Improving the Design of Existing Code, 2nd Edition (Addison-Wesley, 2018)</t>
+        </is>
+      </c>
+      <c r="C10" s="4" t="inlineStr">
+        <is>
+          <t>Coding &amp; implementation</t>
+        </is>
+      </c>
+      <c r="D10" s="4" t="inlineStr">
+        <is>
+          <t>https://martinfowler.com/books/refactoring.html</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="4" t="inlineStr">
         <is>
-          <t>Forsgren, Humble &amp; Kim, *Accelerate* (2018)</t>
+          <t>Published company code-review standard; anchors review-feedback and review-culture leveling</t>
+        </is>
+      </c>
+      <c r="B11" s="4" t="inlineStr">
+        <is>
+          <t>Google, Engineering Practices Documentation: How to Do a Code Review (accessed 2026-07)</t>
+        </is>
+      </c>
+      <c r="C11" s="4" t="inlineStr">
+        <is>
+          <t>Code review</t>
+        </is>
+      </c>
+      <c r="D11" s="4" t="inlineStr">
+        <is>
+          <t>https://google.github.io/eng-practices/review/</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="4" t="inlineStr">
         <is>
-          <t>Fowler, *Refactoring* (2nd ed., 2018)</t>
-        </is>
-      </c>
+          <t>Origin of the test automation pyramid; verified by web search, no stable canonical URL for a direct citation</t>
+        </is>
+      </c>
+      <c r="B12" s="4" t="inlineStr">
+        <is>
+          <t>Cohn, Succeeding with Agile: Software Development Using Scrum (Addison-Wesley, 2009)</t>
+        </is>
+      </c>
+      <c r="C12" s="4" t="inlineStr">
+        <is>
+          <t>Testing &amp; verification</t>
+        </is>
+      </c>
+      <c r="D12" s="4" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" s="4" t="inlineStr">
         <is>
-          <t>Gregg, *Systems Performance* (2nd ed., 2020)</t>
+          <t>Deployment pipeline environment-parity and release-automation discipline</t>
+        </is>
+      </c>
+      <c r="B13" s="4" t="inlineStr">
+        <is>
+          <t>Humble &amp; Farley, Continuous Delivery: Reliable Software Releases through Build Test and Deployment Automation (Addison-Wesley, 2010)</t>
+        </is>
+      </c>
+      <c r="C13" s="4" t="inlineStr">
+        <is>
+          <t>Delivery automation &amp; CI/CD</t>
+        </is>
+      </c>
+      <c r="D13" s="4" t="inlineStr">
+        <is>
+          <t>https://continuousdelivery.com/</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="4" t="inlineStr">
         <is>
-          <t>Humble &amp; Farley, *Continuous Delivery* (2010)</t>
+          <t>Six pillars (operational excellence, security, reliability, performance efficiency, cost optimization, sustainability) for cloud architecture maturity</t>
+        </is>
+      </c>
+      <c r="B14" s="4" t="inlineStr">
+        <is>
+          <t>Amazon Web Services, AWS Well-Architected Framework (AWS, accessed 2026-07)</t>
+        </is>
+      </c>
+      <c r="C14" s="4" t="inlineStr">
+        <is>
+          <t>Cloud architecture</t>
+        </is>
+      </c>
+      <c r="D14" s="4" t="inlineStr">
+        <is>
+          <t>https://docs.aws.amazon.com/wellarchitected/latest/framework/welcome.html</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="4" t="inlineStr">
         <is>
-          <t>Kurose &amp; Ross, *Computer Networking: A Top-Down Approach* (8th ed., 2021)</t>
+          <t>Written by Kubernetes co-founders; scheduling affinity resource policy and cluster topology patterns</t>
+        </is>
+      </c>
+      <c r="B15" s="4" t="inlineStr">
+        <is>
+          <t>Burns, Beda, Hightower &amp; Evenson, Kubernetes: Up and Running, 3rd Edition (O'Reilly, 2022)</t>
+        </is>
+      </c>
+      <c r="C15" s="4" t="inlineStr">
+        <is>
+          <t>Container orchestration &amp; runtime</t>
+        </is>
+      </c>
+      <c r="D15" s="4" t="inlineStr">
+        <is>
+          <t>https://www.oreilly.com/library/view/kubernetes-up-and/9781098110192/</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="4" t="inlineStr">
         <is>
-          <t>Larson, *Staff Engineer: Leadership Beyond the Management Track* (2021)</t>
+          <t>Layered networking</t>
+        </is>
+      </c>
+      <c r="B16" s="4" t="inlineStr">
+        <is>
+          <t>Kurose &amp; Ross, Computer Networking: A Top-Down Approach, 8th ed. (Pearson, 2020)</t>
+        </is>
+      </c>
+      <c r="C16" s="4" t="inlineStr">
+        <is>
+          <t>Networking &amp; compute foundations</t>
+        </is>
+      </c>
+      <c r="D16" s="4" t="inlineStr">
+        <is>
+          <t>https://www.pearson.com/en-us/subject-catalog/p/computer-networking/P200000003334/9780135928615</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="4" t="inlineStr">
         <is>
-          <t>Lave &amp; Wenger, *Situated Learning: Legitimate Peripheral Participation* (1991)</t>
+          <t>Declarative provisioning module design state management and idempotent infrastructure patterns</t>
+        </is>
+      </c>
+      <c r="B17" s="4" t="inlineStr">
+        <is>
+          <t>Morris, Infrastructure as Code: Dynamic Systems for the Cloud Age, 2nd Edition (O'Reilly, 2021)</t>
+        </is>
+      </c>
+      <c r="C17" s="4" t="inlineStr">
+        <is>
+          <t>Infrastructure as code</t>
+        </is>
+      </c>
+      <c r="D17" s="4" t="inlineStr">
+        <is>
+          <t>https://www.oreilly.com/library/view/infrastructure-as-code/9781098114664/</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="4" t="inlineStr">
         <is>
-          <t>Majors, Fong-Jones &amp; Miranda, *Observability Engineering* (O'Reilly, 2022)</t>
+          <t>Thinnest-viable-platform framing; a platform's job is to cut cognitive load through self-service interfaces</t>
+        </is>
+      </c>
+      <c r="B18" s="4" t="inlineStr">
+        <is>
+          <t>Bottcher, What I Talk About When I Talk About Platforms (martinfowler.com, 2018)</t>
+        </is>
+      </c>
+      <c r="C18" s="4" t="inlineStr">
+        <is>
+          <t>Self-service provisioning</t>
+        </is>
+      </c>
+      <c r="D18" s="4" t="inlineStr">
+        <is>
+          <t>https://martinfowler.com/articles/talk-about-platforms.html</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="4" t="inlineStr">
         <is>
-          <t>McConnell, *Software Estimation: Demystifying the Black Art* (2006)</t>
+          <t>High-cardinality, high-dimensionality telemetry vs. traditional monitoring</t>
+        </is>
+      </c>
+      <c r="B19" s="4" t="inlineStr">
+        <is>
+          <t>Majors, Fong-Jones &amp; Miranda, Observability Engineering: Achieving Production Excellence (O'Reilly, 2022)</t>
+        </is>
+      </c>
+      <c r="C19" s="4" t="inlineStr">
+        <is>
+          <t>Observability &amp; instrumentation</t>
+        </is>
+      </c>
+      <c r="D19" s="4" t="inlineStr">
+        <is>
+          <t>https://www.oreilly.com/library/view/observability-engineering/9781492076438/</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="4" t="inlineStr">
         <is>
-          <t>Morris, *Infrastructure as Code* (O'Reilly, 2016)</t>
+          <t>Google's published postmortem/root-cause and diagnostic-tooling practice; anchors debugging leveling</t>
+        </is>
+      </c>
+      <c r="B20" s="4" t="inlineStr">
+        <is>
+          <t>Beyer, Jones, Petoff &amp; Murphy (eds.), Site Reliability Engineering: How Google Runs Production Systems (O'Reilly/Google, 2016)</t>
+        </is>
+      </c>
+      <c r="C20" s="4" t="inlineStr">
+        <is>
+          <t>SLOs &amp; error budgets</t>
+        </is>
+      </c>
+      <c r="D20" s="4" t="inlineStr">
+        <is>
+          <t>https://sre.google/sre-book/table-of-contents/</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="4" t="inlineStr">
         <is>
-          <t>NIST, *OSCAL - Open Security Controls Assessment Language* (1.0, 2021)</t>
+          <t>Named incident-command roles severity classification and on-call rotation design practice guide</t>
+        </is>
+      </c>
+      <c r="B21" s="4" t="inlineStr">
+        <is>
+          <t>PagerDuty, Incident Response Documentation (accessed 2026-07)</t>
+        </is>
+      </c>
+      <c r="C21" s="4" t="inlineStr">
+        <is>
+          <t>Incident response</t>
+        </is>
+      </c>
+      <c r="D21" s="4" t="inlineStr">
+        <is>
+          <t>https://response.pagerduty.com/</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="4" t="inlineStr">
         <is>
-          <t>Noda, Storey, Forsgren &amp; Greiler, "DevEx: What Actually Drives Productivity" (ACM Queue, 2023)</t>
+          <t>Canonical articulation of blameless-postmortem practice grounded in Dekker's Just Culture -- link 403s to automated clients but title/author/venue confirmed by WebSearch</t>
+        </is>
+      </c>
+      <c r="B22" s="4" t="inlineStr">
+        <is>
+          <t>Allspaw, Blameless PostMortems and a Just Culture, Code as Craft (Etsy Engineering Blog, 2012)</t>
+        </is>
+      </c>
+      <c r="C22" s="4" t="inlineStr">
+        <is>
+          <t>Learning from incidents</t>
+        </is>
+      </c>
+      <c r="D22" s="4" t="inlineStr">
+        <is>
+          <t>https://www.etsy.com/codeascraft/blameless-postmortems</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="4" t="inlineStr">
         <is>
-          <t>Nygard, "Documenting Architecture Decisions" (2011)</t>
+          <t>USE method and capacity/performance methodology coupling cost, capacity and performance</t>
+        </is>
+      </c>
+      <c r="B23" s="4" t="inlineStr">
+        <is>
+          <t>Gregg, Systems Performance: Enterprise and the Cloud, 2nd ed. (Addison-Wesley, 2020)</t>
+        </is>
+      </c>
+      <c r="C23" s="4" t="inlineStr">
+        <is>
+          <t>Capacity, performance &amp; cost</t>
+        </is>
+      </c>
+      <c r="D23" s="4" t="inlineStr">
+        <is>
+          <t>https://www.brendangregg.com/systems-performance-2nd-edition-book.html</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="4" t="inlineStr">
         <is>
-          <t>OpenSSF, *SLSA: Supply-chain Levels for Software Artifacts* (2021)</t>
+          <t>Tiered verification levels (L1 baseline through L3 advanced) for defense-in-depth security controls</t>
+        </is>
+      </c>
+      <c r="B24" s="4" t="inlineStr">
+        <is>
+          <t>OWASP Foundation, OWASP Application Security Verification Standard (accessed 2026-07)</t>
+        </is>
+      </c>
+      <c r="C24" s="4" t="inlineStr">
+        <is>
+          <t>Guardrails &amp; policy as code</t>
+        </is>
+      </c>
+      <c r="D24" s="4" t="inlineStr">
+        <is>
+          <t>https://owasp.org/www-project-application-security-verification-standard/</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="4" t="inlineStr">
         <is>
-          <t>OWASP, *Application Security Verification Standard* (v4, 2019)</t>
+          <t>Google's device/identity-based perimeter-replacement architecture; origin of zero-trust practice later standardized in NIST SP 800-207; verified via WebSearch + curl (HTTP 200)</t>
+        </is>
+      </c>
+      <c r="B25" s="4" t="inlineStr">
+        <is>
+          <t>Ward &amp; Beyer, BeyondCorp: A New Approach to Enterprise Security, ;login: 39(6), 6-11 (USENIX, 2014)</t>
+        </is>
+      </c>
+      <c r="C25" s="4" t="inlineStr">
+        <is>
+          <t>Identity, secrets &amp; access</t>
+        </is>
+      </c>
+      <c r="D25" s="4" t="inlineStr">
+        <is>
+          <t>https://www.usenix.org/system/files/login/articles/login_dec14_02_ward.pdf</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="4" t="inlineStr">
         <is>
-          <t>PagerDuty, *Incident Response Guide* (2017)</t>
+          <t>Build-provenance maturity levels L0-L3 for artifact supply-chain integrity</t>
+        </is>
+      </c>
+      <c r="B26" s="4" t="inlineStr">
+        <is>
+          <t>OpenSSF, SLSA (Supply-chain Levels for Software Artifacts), Version 1.0 (2023)</t>
+        </is>
+      </c>
+      <c r="C26" s="4" t="inlineStr">
+        <is>
+          <t>Software supply chain security</t>
+        </is>
+      </c>
+      <c r="D26" s="4" t="inlineStr">
+        <is>
+          <t>https://slsa.dev/spec/v1.0/levels</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="4" t="inlineStr">
         <is>
-          <t>Perri, *Escaping the Build Trap* (2018)</t>
+          <t>Six-function (incl. Govern) taxonomy for organizing enterprise cybersecurity risk strategy</t>
+        </is>
+      </c>
+      <c r="B27" s="4" t="inlineStr">
+        <is>
+          <t>NIST, The NIST Cybersecurity Framework (CSF) 2.0, NIST CSWP 29 (2024)</t>
+        </is>
+      </c>
+      <c r="C27" s="4" t="inlineStr">
+        <is>
+          <t>Compliance &amp; audit readiness</t>
+        </is>
+      </c>
+      <c r="D27" s="4" t="inlineStr">
+        <is>
+          <t>https://csrc.nist.gov/pubs/cswp/29/the-nist-cybersecurity-framework-csf-20/final</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="4" t="inlineStr">
         <is>
-          <t>Procida, *Diataxis* (2017-)</t>
+          <t>Tutorials/how-to/reference/explanation framework; grounds documentation information-architecture leveling</t>
+        </is>
+      </c>
+      <c r="B28" s="4" t="inlineStr">
+        <is>
+          <t>Procida, Diataxis: A Systematic Framework for Technical Documentation (diataxis.fr, accessed 2026-07)</t>
+        </is>
+      </c>
+      <c r="C28" s="4" t="inlineStr">
+        <is>
+          <t>Technical documentation</t>
+        </is>
+      </c>
+      <c r="D28" s="4" t="inlineStr">
+        <is>
+          <t>https://diataxis.fr/</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="4" t="inlineStr">
         <is>
-          <t>Reinertsen, *The Principles of Product Development Flow* (2009)</t>
+          <t>Maturity tiers for platform-as-a-product investment across people/process/policy/technology; link verified 200</t>
+        </is>
+      </c>
+      <c r="B29" s="4" t="inlineStr">
+        <is>
+          <t>CNCF TAG App Delivery, Platform Engineering Maturity Model (2023)</t>
+        </is>
+      </c>
+      <c r="C29" s="4" t="inlineStr">
+        <is>
+          <t>Platform advocacy &amp; enablement</t>
+        </is>
+      </c>
+      <c r="D29" s="4" t="inlineStr">
+        <is>
+          <t>https://tag-app-delivery.cncf.io/whitepapers/platform-eng-maturity-model/</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="4" t="inlineStr">
         <is>
-          <t>Sadowski et al., "Modern Code Review: A Case Study at Google" (ICSE-SEIP, 2018)</t>
+          <t>Tech Lead / Solver / Architect / Right-Hand archetypes for senior IC technical leadership scope</t>
+        </is>
+      </c>
+      <c r="B30" s="4" t="inlineStr">
+        <is>
+          <t>Larson, Staff Engineer: Leadership Beyond the Management Track (self-published, 2021)</t>
+        </is>
+      </c>
+      <c r="C30" s="4" t="inlineStr">
+        <is>
+          <t>Stakeholder management</t>
+        </is>
+      </c>
+      <c r="D30" s="4" t="inlineStr">
+        <is>
+          <t>https://staffeng.com/book/</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="4" t="inlineStr">
         <is>
-          <t>Skelton &amp; Pais, *Team Topologies* (2019)</t>
+          <t>Estimation as a probabilistic forecast to calibrate, distinct from Code Complete</t>
+        </is>
+      </c>
+      <c r="B31" s="4" t="inlineStr">
+        <is>
+          <t>McConnell, Software Estimation: Demystifying the Black Art (Microsoft Press, 2006)</t>
+        </is>
+      </c>
+      <c r="C31" s="4" t="inlineStr">
+        <is>
+          <t>Planning &amp; estimation</t>
+        </is>
+      </c>
+      <c r="D31" s="4" t="inlineStr">
+        <is>
+          <t>https://www.construx.com/store/software-estimation-demystifying-the-black-art/</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="4" t="inlineStr">
         <is>
-          <t>Skelton &amp; Pais, *Team Topologies* (2019) - team interaction modes</t>
-        </is>
-      </c>
+          <t>Cost-of-delay and queueing-theory economics for prioritization decisions; verified via web search</t>
+        </is>
+      </c>
+      <c r="B32" s="4" t="inlineStr">
+        <is>
+          <t>Reinertsen, The Principles of Product Development Flow: Second Generation Lean Product Development (Celeritas, 2009)</t>
+        </is>
+      </c>
+      <c r="C32" s="4" t="inlineStr">
+        <is>
+          <t>Prioritization &amp; trade-off judgment</t>
+        </is>
+      </c>
+      <c r="D32" s="4" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" s="4" t="inlineStr">
         <is>
-          <t>Skelton &amp; Pais, *Team Topologies* (2019), applying Sweller's cognitive load theory (1988)</t>
-        </is>
-      </c>
+          <t>Legitimate peripheral participation and community-of-practice theory</t>
+        </is>
+      </c>
+      <c r="B33" s="4" t="inlineStr">
+        <is>
+          <t>Wenger, Communities of Practice: Learning, Meaning, and Identity (Cambridge University Press, 1998)</t>
+        </is>
+      </c>
+      <c r="C33" s="4" t="inlineStr">
+        <is>
+          <t>Mentorship &amp; knowledge sharing</t>
+        </is>
+      </c>
+      <c r="D33" s="4" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" s="4" t="inlineStr">
         <is>
-          <t>Spotify Engineering, "How We Use Golden Paths to Solve Fragmentation in Our Software Ecosystem" (2020)</t>
+          <t>Origin of the Architecture Decision Record (ADR) pattern</t>
+        </is>
+      </c>
+      <c r="B34" s="4" t="inlineStr">
+        <is>
+          <t>Nygard, Documenting Architecture Decisions (Cognitect blog, 2011)</t>
+        </is>
+      </c>
+      <c r="C34" s="4" t="inlineStr">
+        <is>
+          <t>Technical direction &amp; influence</t>
+        </is>
+      </c>
+      <c r="D34" s="4" t="inlineStr">
+        <is>
+          <t>https://cognitect.com/blog/2011/11/15/documenting-architecture-decisions</t>
         </is>
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="4" t="inlineStr">
-        <is>
-          <t>Ward &amp; Beyer, "BeyondCorp: A New Approach to Enterprise Security" (;login:, 2014)</t>
-        </is>
-      </c>
+      <c r="A35" s="4" t="inlineStr"/>
+      <c r="B35" s="4" t="inlineStr">
+        <is>
+          <t>Noda, Storey, Forsgren &amp; Greiler, DevEx: What Actually Drives Productivity, ACM Queue 21(2) (2023) — https://queue.acm.org/detail.cfm?id=3595878</t>
+        </is>
+      </c>
+      <c r="C35" s="4" t="inlineStr"/>
+      <c r="D35" s="4" t="inlineStr"/>
     </row>
     <row r="36">
-      <c r="A36" s="4" t="inlineStr">
-        <is>
-          <t>Winters, Manshreck &amp; Wright, *Software Engineering at Google* (2020) - Hyrum's Law</t>
-        </is>
-      </c>
+      <c r="A36" s="4" t="inlineStr"/>
+      <c r="B36" s="4" t="inlineStr">
+        <is>
+          <t>SFIA Foundation, Skills Framework for the Information Age, version 9 (2024) — https://sfia-online.org/en/sfia-9</t>
+        </is>
+      </c>
+      <c r="C36" s="4" t="inlineStr"/>
+      <c r="D36" s="4" t="inlineStr"/>
     </row>
     <row r="37">
-      <c r="A37" s="4" t="inlineStr">
-        <is>
-          <t>Winters, Manshreck &amp; Wright, *Software Engineering at Google* (2020), deprecation chapter</t>
-        </is>
-      </c>
+      <c r="A37" s="4" t="inlineStr"/>
+      <c r="B37" s="4" t="inlineStr">
+        <is>
+          <t>Larson, Staff Engineer: Leadership Beyond the Management Track (self-published, 2021) — https://staffeng.com/book/</t>
+        </is>
+      </c>
+      <c r="C37" s="4" t="inlineStr"/>
+      <c r="D37" s="4" t="inlineStr"/>
     </row>
     <row r="38">
-      <c r="A38" s="4" t="inlineStr">
-        <is>
-          <t>Winters, Manshreck &amp; Wright, *Software Engineering at Google* (2020), design-docs chapters</t>
-        </is>
-      </c>
+      <c r="A38" s="4" t="inlineStr"/>
+      <c r="B38" s="4" t="inlineStr">
+        <is>
+          <t>Forsgren, Humble &amp; Kim, Accelerate: The Science of Lean Software and DevOps (IT Revolution Press, 2018) — https://itrevolution.com/product/accelerate/</t>
+        </is>
+      </c>
+      <c r="C38" s="4" t="inlineStr"/>
+      <c r="D38" s="4" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" s="4" t="inlineStr"/>
+      <c r="B39" s="4" t="inlineStr">
+        <is>
+          <t>Skelton &amp; Pais, Team Topologies (IT Revolution, 2019)</t>
+        </is>
+      </c>
+      <c r="C39" s="4" t="inlineStr"/>
+      <c r="D39" s="4" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="A40" s="4" t="inlineStr"/>
+      <c r="B40" s="4" t="inlineStr">
+        <is>
+          <t>Perri, Escaping the Build Trap: How Effective Product Management Creates Real Value (O'Reilly, 2018) — https://www.oreilly.com/library/view/escaping-the-build/9781491973783/</t>
+        </is>
+      </c>
+      <c r="C40" s="4" t="inlineStr"/>
+      <c r="D40" s="4" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" s="4" t="inlineStr"/>
+      <c r="B41" s="4" t="inlineStr">
+        <is>
+          <t>Spotify Engineering, How We Use Golden Paths to Solve Fragmentation in Our Software Ecosystem (Spotify Engineering Blog, 2020) — https://engineering.atspotify.com/2020/08/how-we-use-golden-paths-to-solve-fragmentation-in-our-software-ecosystem/</t>
+        </is>
+      </c>
+      <c r="C41" s="4" t="inlineStr"/>
+      <c r="D41" s="4" t="inlineStr"/>
+    </row>
+    <row r="42">
+      <c r="A42" s="4" t="inlineStr"/>
+      <c r="B42" s="4" t="inlineStr">
+        <is>
+          <t>Sweller, Cognitive Load During Problem Solving: Effects on Learning, Cognitive Science 12(2), 257-285 (1988) — https://doi.org/10.1207/s15516709cog1202_4</t>
+        </is>
+      </c>
+      <c r="C42" s="4" t="inlineStr"/>
+      <c r="D42" s="4" t="inlineStr"/>
+    </row>
+    <row r="43">
+      <c r="A43" s="4" t="inlineStr"/>
+      <c r="B43" s="4" t="inlineStr">
+        <is>
+          <t>Conway, How Do Committees Invent?, Datamation 14(4), 28-31 (1968) — https://www.melconway.com/Home/Committees_Paper.html</t>
+        </is>
+      </c>
+      <c r="C43" s="4" t="inlineStr"/>
+      <c r="D43" s="4" t="inlineStr"/>
+    </row>
+    <row r="44">
+      <c r="A44" s="4" t="inlineStr"/>
+      <c r="B44" s="4" t="inlineStr">
+        <is>
+          <t>Winters, Manshreck &amp; Wright, Software Engineering at Google: Lessons Learned from Programming Over Time (O'Reilly, 2020) — https://abseil.io/resources/swe-book</t>
+        </is>
+      </c>
+      <c r="C44" s="4" t="inlineStr"/>
+      <c r="D44" s="4" t="inlineStr"/>
+    </row>
+    <row r="45">
+      <c r="A45" s="4" t="inlineStr"/>
+      <c r="B45" s="4" t="inlineStr">
+        <is>
+          <t>Fowler, Refactoring: Improving the Design of Existing Code, 2nd Edition (Addison-Wesley, 2018) — https://martinfowler.com/books/refactoring.html</t>
+        </is>
+      </c>
+      <c r="C45" s="4" t="inlineStr"/>
+      <c r="D45" s="4" t="inlineStr"/>
+    </row>
+    <row r="46">
+      <c r="A46" s="4" t="inlineStr"/>
+      <c r="B46" s="4" t="inlineStr">
+        <is>
+          <t>Google, Engineering Practices Documentation: How to Do a Code Review (accessed 2026-07) — https://google.github.io/eng-practices/review/</t>
+        </is>
+      </c>
+      <c r="C46" s="4" t="inlineStr"/>
+      <c r="D46" s="4" t="inlineStr"/>
+    </row>
+    <row r="47">
+      <c r="A47" s="4" t="inlineStr"/>
+      <c r="B47" s="4" t="inlineStr">
+        <is>
+          <t>Cohn, Succeeding with Agile: Software Development Using Scrum (Addison-Wesley, 2009)</t>
+        </is>
+      </c>
+      <c r="C47" s="4" t="inlineStr"/>
+      <c r="D47" s="4" t="inlineStr"/>
+    </row>
+    <row r="48">
+      <c r="A48" s="4" t="inlineStr"/>
+      <c r="B48" s="4" t="inlineStr">
+        <is>
+          <t>Humble &amp; Farley, Continuous Delivery: Reliable Software Releases through Build Test and Deployment Automation (Addison-Wesley, 2010) — https://continuousdelivery.com/</t>
+        </is>
+      </c>
+      <c r="C48" s="4" t="inlineStr"/>
+      <c r="D48" s="4" t="inlineStr"/>
+    </row>
+    <row r="49">
+      <c r="A49" s="4" t="inlineStr"/>
+      <c r="B49" s="4" t="inlineStr">
+        <is>
+          <t>Amazon Web Services, AWS Well-Architected Framework (AWS, accessed 2026-07) — https://docs.aws.amazon.com/wellarchitected/latest/framework/welcome.html</t>
+        </is>
+      </c>
+      <c r="C49" s="4" t="inlineStr"/>
+      <c r="D49" s="4" t="inlineStr"/>
+    </row>
+    <row r="50">
+      <c r="A50" s="4" t="inlineStr"/>
+      <c r="B50" s="4" t="inlineStr">
+        <is>
+          <t>Burns, Beda, Hightower &amp; Evenson, Kubernetes: Up and Running, 3rd Edition (O'Reilly, 2022) — https://www.oreilly.com/library/view/kubernetes-up-and/9781098110192/</t>
+        </is>
+      </c>
+      <c r="C50" s="4" t="inlineStr"/>
+      <c r="D50" s="4" t="inlineStr"/>
+    </row>
+    <row r="51">
+      <c r="A51" s="4" t="inlineStr"/>
+      <c r="B51" s="4" t="inlineStr">
+        <is>
+          <t>Kurose &amp; Ross, Computer Networking: A Top-Down Approach, 8th ed. (Pearson, 2020) — https://www.pearson.com/en-us/subject-catalog/p/computer-networking/P200000003334/9780135928615</t>
+        </is>
+      </c>
+      <c r="C51" s="4" t="inlineStr"/>
+      <c r="D51" s="4" t="inlineStr"/>
+    </row>
+    <row r="52">
+      <c r="A52" s="4" t="inlineStr"/>
+      <c r="B52" s="4" t="inlineStr">
+        <is>
+          <t>Morris, Infrastructure as Code: Dynamic Systems for the Cloud Age, 2nd Edition (O'Reilly, 2021) — https://www.oreilly.com/library/view/infrastructure-as-code/9781098114664/</t>
+        </is>
+      </c>
+      <c r="C52" s="4" t="inlineStr"/>
+      <c r="D52" s="4" t="inlineStr"/>
+    </row>
+    <row r="53">
+      <c r="A53" s="4" t="inlineStr"/>
+      <c r="B53" s="4" t="inlineStr">
+        <is>
+          <t>Bottcher, What I Talk About When I Talk About Platforms (martinfowler.com, 2018) — https://martinfowler.com/articles/talk-about-platforms.html</t>
+        </is>
+      </c>
+      <c r="C53" s="4" t="inlineStr"/>
+      <c r="D53" s="4" t="inlineStr"/>
+    </row>
+    <row r="54">
+      <c r="A54" s="4" t="inlineStr"/>
+      <c r="B54" s="4" t="inlineStr">
+        <is>
+          <t>Majors, Fong-Jones &amp; Miranda, Observability Engineering: Achieving Production Excellence (O'Reilly, 2022) — https://www.oreilly.com/library/view/observability-engineering/9781492076438/</t>
+        </is>
+      </c>
+      <c r="C54" s="4" t="inlineStr"/>
+      <c r="D54" s="4" t="inlineStr"/>
+    </row>
+    <row r="55">
+      <c r="A55" s="4" t="inlineStr"/>
+      <c r="B55" s="4" t="inlineStr">
+        <is>
+          <t>Beyer, Jones, Petoff &amp; Murphy (eds.), Site Reliability Engineering: How Google Runs Production Systems (O'Reilly/Google, 2016) — https://sre.google/sre-book/table-of-contents/</t>
+        </is>
+      </c>
+      <c r="C55" s="4" t="inlineStr"/>
+      <c r="D55" s="4" t="inlineStr"/>
+    </row>
+    <row r="56">
+      <c r="A56" s="4" t="inlineStr"/>
+      <c r="B56" s="4" t="inlineStr">
+        <is>
+          <t>PagerDuty, Incident Response Documentation (accessed 2026-07) — https://response.pagerduty.com/</t>
+        </is>
+      </c>
+      <c r="C56" s="4" t="inlineStr"/>
+      <c r="D56" s="4" t="inlineStr"/>
+    </row>
+    <row r="57">
+      <c r="A57" s="4" t="inlineStr"/>
+      <c r="B57" s="4" t="inlineStr">
+        <is>
+          <t>Allspaw, Blameless PostMortems and a Just Culture, Code as Craft (Etsy Engineering Blog, 2012) — https://www.etsy.com/codeascraft/blameless-postmortems</t>
+        </is>
+      </c>
+      <c r="C57" s="4" t="inlineStr"/>
+      <c r="D57" s="4" t="inlineStr"/>
+    </row>
+    <row r="58">
+      <c r="A58" s="4" t="inlineStr"/>
+      <c r="B58" s="4" t="inlineStr">
+        <is>
+          <t>Gregg, Systems Performance: Enterprise and the Cloud, 2nd ed. (Addison-Wesley, 2020) — https://www.brendangregg.com/systems-performance-2nd-edition-book.html</t>
+        </is>
+      </c>
+      <c r="C58" s="4" t="inlineStr"/>
+      <c r="D58" s="4" t="inlineStr"/>
+    </row>
+    <row r="59">
+      <c r="A59" s="4" t="inlineStr"/>
+      <c r="B59" s="4" t="inlineStr">
+        <is>
+          <t>OWASP Foundation, OWASP Application Security Verification Standard (accessed 2026-07) — https://owasp.org/www-project-application-security-verification-standard/</t>
+        </is>
+      </c>
+      <c r="C59" s="4" t="inlineStr"/>
+      <c r="D59" s="4" t="inlineStr"/>
+    </row>
+    <row r="60">
+      <c r="A60" s="4" t="inlineStr"/>
+      <c r="B60" s="4" t="inlineStr">
+        <is>
+          <t>Ward &amp; Beyer, BeyondCorp: A New Approach to Enterprise Security, ;login: 39(6), 6-11 (USENIX, 2014) — https://www.usenix.org/system/files/login/articles/login_dec14_02_ward.pdf</t>
+        </is>
+      </c>
+      <c r="C60" s="4" t="inlineStr"/>
+      <c r="D60" s="4" t="inlineStr"/>
+    </row>
+    <row r="61">
+      <c r="A61" s="4" t="inlineStr"/>
+      <c r="B61" s="4" t="inlineStr">
+        <is>
+          <t>OpenSSF, SLSA (Supply-chain Levels for Software Artifacts), Version 1.0 (2023) — https://slsa.dev/spec/v1.0/levels</t>
+        </is>
+      </c>
+      <c r="C61" s="4" t="inlineStr"/>
+      <c r="D61" s="4" t="inlineStr"/>
+    </row>
+    <row r="62">
+      <c r="A62" s="4" t="inlineStr"/>
+      <c r="B62" s="4" t="inlineStr">
+        <is>
+          <t>NIST, The NIST Cybersecurity Framework (CSF) 2.0, NIST CSWP 29 (2024) — https://csrc.nist.gov/pubs/cswp/29/the-nist-cybersecurity-framework-csf-20/final</t>
+        </is>
+      </c>
+      <c r="C62" s="4" t="inlineStr"/>
+      <c r="D62" s="4" t="inlineStr"/>
+    </row>
+    <row r="63">
+      <c r="A63" s="4" t="inlineStr"/>
+      <c r="B63" s="4" t="inlineStr">
+        <is>
+          <t>Procida, Diataxis: A Systematic Framework for Technical Documentation (diataxis.fr, accessed 2026-07) — https://diataxis.fr/</t>
+        </is>
+      </c>
+      <c r="C63" s="4" t="inlineStr"/>
+      <c r="D63" s="4" t="inlineStr"/>
+    </row>
+    <row r="64">
+      <c r="A64" s="4" t="inlineStr"/>
+      <c r="B64" s="4" t="inlineStr">
+        <is>
+          <t>CNCF TAG App Delivery, Platform Engineering Maturity Model (2023) — https://tag-app-delivery.cncf.io/whitepapers/platform-eng-maturity-model/</t>
+        </is>
+      </c>
+      <c r="C64" s="4" t="inlineStr"/>
+      <c r="D64" s="4" t="inlineStr"/>
+    </row>
+    <row r="65">
+      <c r="A65" s="4" t="inlineStr"/>
+      <c r="B65" s="4" t="inlineStr">
+        <is>
+          <t>McConnell, Software Estimation: Demystifying the Black Art (Microsoft Press, 2006) — https://www.construx.com/store/software-estimation-demystifying-the-black-art/</t>
+        </is>
+      </c>
+      <c r="C65" s="4" t="inlineStr"/>
+      <c r="D65" s="4" t="inlineStr"/>
+    </row>
+    <row r="66">
+      <c r="A66" s="4" t="inlineStr"/>
+      <c r="B66" s="4" t="inlineStr">
+        <is>
+          <t>Reinertsen, The Principles of Product Development Flow: Second Generation Lean Product Development (Celeritas, 2009)</t>
+        </is>
+      </c>
+      <c r="C66" s="4" t="inlineStr"/>
+      <c r="D66" s="4" t="inlineStr"/>
+    </row>
+    <row r="67">
+      <c r="A67" s="4" t="inlineStr"/>
+      <c r="B67" s="4" t="inlineStr">
+        <is>
+          <t>Wenger, Communities of Practice: Learning, Meaning, and Identity (Cambridge University Press, 1998)</t>
+        </is>
+      </c>
+      <c r="C67" s="4" t="inlineStr"/>
+      <c r="D67" s="4" t="inlineStr"/>
+    </row>
+    <row r="68">
+      <c r="A68" s="4" t="inlineStr"/>
+      <c r="B68" s="4" t="inlineStr">
+        <is>
+          <t>Nygard, Documenting Architecture Decisions (Cognitect blog, 2011) — https://cognitect.com/blog/2011/11/15/documenting-architecture-decisions</t>
+        </is>
+      </c>
+      <c r="C68" s="4" t="inlineStr"/>
+      <c r="D68" s="4" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/roles/platform-engineering/ladder.xlsx
+++ b/roles/platform-engineering/ladder.xlsx
@@ -808,32 +808,44 @@
       </c>
       <c r="G2" s="4" t="inlineStr">
         <is>
-          <t>Depth: Runs scripted customer interviews and notes findings under a senior researcher's guidance. Evidenced by: Shadows platform users and sits in on interviews and support rotations, writing up the friction they hit. Scope: task.</t>
+          <t>Depth: Runs scripted customer interviews and notes findings under a senior researcher's guidance.
+Evidenced by: Shadows platform users and sits in on interviews and support rotations, writing up the friction they hit.
+Scope: task.</t>
         </is>
       </c>
       <c r="H2" s="4" t="inlineStr">
         <is>
-          <t>Depth: Plans and conducts standard discovery for a feature, synthesizing themes with normal review. Evidenced by: Runs structured interviews and support-channel reviews with the internal engineers using their component. Scope: component.</t>
+          <t>Depth: Plans and conducts standard discovery for a feature, synthesizing themes with normal review.
+Evidenced by: Runs structured interviews and support-channel reviews with the internal engineers using their component.
+Scope: component.</t>
         </is>
       </c>
       <c r="I2" s="4" t="inlineStr">
         <is>
-          <t>Depth: Independently frames ambiguous problems, selects fitting methods, and separates signal from noise. Evidenced by: Designs and runs the discovery process for a capability. Scope: capability / domain (terminal level).</t>
+          <t>Depth: Independently frames ambiguous problems, selects fitting methods, and separates signal from noise.
+Evidenced by: Designs and runs the discovery process for a capability.
+Scope: capability / domain (terminal level).</t>
         </is>
       </c>
       <c r="J2" s="4" t="inlineStr">
         <is>
-          <t>Depth: Designs the team's discovery approach and untangles findings others find contradictory. Evidenced by: Synthesizes research across several product teams into shared personas and friction maps other platform teams adopt. Scope: multiple teams.</t>
+          <t>Depth: Designs the team's discovery approach and untangles findings others find contradictory.
+Evidenced by: Synthesizes research across several product teams into shared personas and friction maps other platform teams adopt.
+Scope: multiple teams.</t>
         </is>
       </c>
       <c r="K2" s="4" t="inlineStr">
         <is>
-          <t>Depth: Sets the org's research strategy and anticipates emerging customer needs before they surface. Evidenced by: Establishes the organization's standing platform research practice. Scope: organization.</t>
+          <t>Depth: Sets the org's research strategy and anticipates emerging customer needs before they surface.
+Evidenced by: Establishes the organization's standing platform research practice.
+Scope: organization.</t>
         </is>
       </c>
       <c r="L2" s="4" t="inlineStr">
         <is>
-          <t>Depth: Defines what rigorous product discovery means and shapes the discipline's practice externally. Evidenced by: Represents the internal developer experience at company level. Scope: company.</t>
+          <t>Depth: Defines what rigorous product discovery means and shapes the discipline's practice externally.
+Evidenced by: Represents the internal developer experience at company level.
+Scope: company.</t>
         </is>
       </c>
     </row>
@@ -870,32 +882,44 @@
       </c>
       <c r="G3" s="4" t="inlineStr">
         <is>
-          <t>Depth: Pulls and reports defined product metrics under direction. Evidenced by: Pulls and charts existing adoption and usage numbers accurately when asked. Scope: task.</t>
+          <t>Depth: Pulls and reports defined product metrics under direction.
+Evidenced by: Pulls and charts existing adoption and usage numbers accurately when asked.
+Scope: task.</t>
         </is>
       </c>
       <c r="H3" s="4" t="inlineStr">
         <is>
-          <t>Depth: Builds and interprets metric dashboards for a product with normal review. Evidenced by: Instruments their component with adoption, retention, and satisfaction signals. Scope: component.</t>
+          <t>Depth: Builds and interprets metric dashboards for a product with normal review.
+Evidenced by: Instruments their component with adoption, retention, and satisfaction signals.
+Scope: component.</t>
         </is>
       </c>
       <c r="I3" s="4" t="inlineStr">
         <is>
-          <t>Depth: Independently designs metric frameworks and draws sound conclusions from messy data. Evidenced by: Defines the success metrics for a capability. Scope: capability / domain (terminal level).</t>
+          <t>Depth: Independently designs metric frameworks and draws sound conclusions from messy data.
+Evidenced by: Defines the success metrics for a capability.
+Scope: capability / domain (terminal level).</t>
         </is>
       </c>
       <c r="J3" s="4" t="inlineStr">
         <is>
-          <t>Depth: Defines the measurement model teams adopt and diagnoses misleading metrics others trust. Evidenced by: Standardizes how several platform teams measure adoption so their numbers compose. Scope: multiple teams.</t>
+          <t>Depth: Defines the measurement model teams adopt and diagnoses misleading metrics others trust.
+Evidenced by: Standardizes how several platform teams measure adoption so their numbers compose.
+Scope: multiple teams.</t>
         </is>
       </c>
       <c r="K3" s="4" t="inlineStr">
         <is>
-          <t>Depth: Sets product-analytics strategy across the org and anticipates which signals will matter. Evidenced by: Owns the organization's platform scorecard. Scope: organization.</t>
+          <t>Depth: Sets product-analytics strategy across the org and anticipates which signals will matter.
+Evidenced by: Owns the organization's platform scorecard.
+Scope: organization.</t>
         </is>
       </c>
       <c r="L3" s="4" t="inlineStr">
         <is>
-          <t>Depth: Defines rigorous product measurement for the discipline and is cited externally on it. Evidenced by: Frames platform value in company terms. Scope: company.</t>
+          <t>Depth: Defines rigorous product measurement for the discipline and is cited externally on it.
+Evidenced by: Frames platform value in company terms.
+Scope: company.</t>
         </is>
       </c>
     </row>
@@ -932,32 +956,44 @@
       </c>
       <c r="G4" s="4" t="inlineStr">
         <is>
-          <t>Depth: Checks for an existing tool, service, or open-source option before writing new code and raises what they find; asks whether a proposed task serves a real user need. Evidenced by: Finds that an existing internal CLI already covers most of a proposed new tool's use case and raises it in planning instead of starting a new build. Scope: task.</t>
+          <t>Depth: Checks for an existing tool, service, or open-source option before writing new code and raises what they find; asks whether a proposed task serves a real user need.
+Evidenced by: Finds that an existing internal CLI already covers most of a proposed new tool's use case and raises it in planning instead of starting a new build.
+Scope: task.</t>
         </is>
       </c>
       <c r="H4" s="4" t="inlineStr">
         <is>
-          <t>Depth: Proposes wrapping or configuring an existing service instead of building new when it meets the need, writing the comparison down and defending removal of unused features in their own component. Evidenced by: Recommends adopting the org's existing secrets-manager service instead of building a bespoke wrapper for their component, and writes up the build-vs-adopt comparison that settles it. Scope: component.</t>
+          <t>Depth: Proposes wrapping or configuring an existing service instead of building new when it meets the need, writing the comparison down and defending removal of unused features in their own component.
+Evidenced by: Recommends adopting the org's existing secrets-manager service instead of building a bespoke wrapper for their component, and writes up the build-vs-adopt comparison that settles it.
+Scope: component.</t>
         </is>
       </c>
       <c r="I4" s="4" t="inlineStr">
         <is>
-          <t>Depth: Keeps a whole capability at its thinnest viable size - makes explicit, documented build-buy-adopt decisions, ships the thinnest version that serves proven demand, and retires surface area whose maintenance cost exceeds its value. Evidenced by: Retires half a capability's plugin surface after usage telemetry shows only two of eight plugins are load-bearing, documenting the build-buy-adopt call for what stays. Scope: capability / domain (terminal level).</t>
+          <t>Depth: Keeps a whole capability at its thinnest viable size - makes explicit, documented build-buy-adopt decisions, ships the thinnest version that serves proven demand, and retires surface area whose maintenance cost exceeds its value.
+Evidenced by: Retires half a capability's plugin surface after usage telemetry shows only two of eight plugins are load-bearing, documenting the build-buy-adopt call for what stays.
+Scope: capability / domain (terminal level).</t>
         </is>
       </c>
       <c r="J4" s="4" t="inlineStr">
         <is>
-          <t>Depth: Arbitrates overlap and sprawl across teams - merges duplicate offerings, cuts under-used surface, and sets the bar for what deserves to be shared platform at all. Evidenced by: Merges two platform teams' overlapping feature-flag services into one and retires the duplicate. Scope: multiple teams.</t>
+          <t>Depth: Arbitrates overlap and sprawl across teams - merges duplicate offerings, cuts under-used surface, and sets the bar for what deserves to be shared platform at all.
+Evidenced by: Merges two platform teams' overlapping feature-flag services into one and retires the duplicate.
+Scope: multiple teams.</t>
         </is>
       </c>
       <c r="K4" s="4" t="inlineStr">
         <is>
-          <t>Depth: Shapes the organization's platform boundary - what the platform owns versus product teams versus vendors - and drives the organization to shed what it should not own. Evidenced by: Draws the line for what the platform organization owns versus what product teams should just buy, and gets teams to hand back components that crossed it. Scope: organization.</t>
+          <t>Depth: Shapes the organization's platform boundary - what the platform owns versus product teams versus vendors - and drives the organization to shed what it should not own.
+Evidenced by: Draws the line for what the platform organization owns versus what product teams should just buy, and gets teams to hand back components that crossed it.
+Scope: organization.</t>
         </is>
       </c>
       <c r="L4" s="4" t="inlineStr">
         <is>
-          <t>Depth: Sets the build-buy-adopt principles an entire company references, keeping company-scale platform investment proportional to the delivery it unlocks. Evidenced by: Kills a company-wide platform initiative whose maintenance cost has outgrown the delivery it unlocks, over objections that the build already happened. Scope: company.</t>
+          <t>Depth: Sets the build-buy-adopt principles an entire company references, keeping company-scale platform investment proportional to the delivery it unlocks.
+Evidenced by: Kills a company-wide platform initiative whose maintenance cost has outgrown the delivery it unlocks, over objections that the build already happened.
+Scope: company.</t>
         </is>
       </c>
     </row>
@@ -994,32 +1030,44 @@
       </c>
       <c r="G5" s="4" t="inlineStr">
         <is>
-          <t>Depth: Maintains roadmap items and updates status under guidance. Evidenced by: Explains why their current task is on the roadmap. Scope: task.</t>
+          <t>Depth: Maintains roadmap items and updates status under guidance.
+Evidenced by: Explains why their current task is on the roadmap.
+Scope: task.</t>
         </is>
       </c>
       <c r="H5" s="4" t="inlineStr">
         <is>
-          <t>Depth: Builds and sequences a credible roadmap for one product with normal review. Evidenced by: Sequences their component's backlog by user impact. Scope: component.</t>
+          <t>Depth: Builds and sequences a credible roadmap for one product with normal review.
+Evidenced by: Sequences their component's backlog by user impact.
+Scope: component.</t>
         </is>
       </c>
       <c r="I5" s="4" t="inlineStr">
         <is>
-          <t>Depth: Independently balances competing priorities and replans confidently under shifting constraints. Evidenced by: Owns the roadmap for a platform capability. Scope: capability / domain (terminal level).</t>
+          <t>Depth: Independently balances competing priorities and replans confidently under shifting constraints.
+Evidenced by: Owns the roadmap for a platform capability.
+Scope: capability / domain (terminal level).</t>
         </is>
       </c>
       <c r="J5" s="4" t="inlineStr">
         <is>
-          <t>Depth: Designs the planning approach others use and resolves cross-team portfolio conflicts. Evidenced by: Aligns roadmaps across platform teams. Scope: multiple teams.</t>
+          <t>Depth: Designs the planning approach others use and resolves cross-team portfolio conflicts.
+Evidenced by: Aligns roadmaps across platform teams.
+Scope: multiple teams.</t>
         </is>
       </c>
       <c r="K5" s="4" t="inlineStr">
         <is>
-          <t>Depth: Sets portfolio planning strategy and foresees where investment should shift next. Evidenced by: Drives the platform organization's investment strategy. Scope: organization.</t>
+          <t>Depth: Sets portfolio planning strategy and foresees where investment should shift next.
+Evidenced by: Drives the platform organization's investment strategy.
+Scope: organization.</t>
         </is>
       </c>
       <c r="L5" s="4" t="inlineStr">
         <is>
-          <t>Depth: Defines portfolio-planning best practice for the field and is recognized for it. Evidenced by: Sets multi-year platform direction for the company. Scope: company.</t>
+          <t>Depth: Defines portfolio-planning best practice for the field and is recognized for it.
+Evidenced by: Sets multi-year platform direction for the company.
+Scope: company.</t>
         </is>
       </c>
     </row>
@@ -1056,32 +1104,44 @@
       </c>
       <c r="G6" s="4" t="inlineStr">
         <is>
-          <t>Depth: Maintains existing self-service platform components under review, addressing documented user requests. Evidenced by: Follows the golden path as a real user would and reports exactly where it breaks. Scope: task.</t>
+          <t>Depth: Maintains existing self-service platform components under review, addressing documented user requests.
+Evidenced by: Follows the golden path as a real user would and reports exactly where it breaks.
+Scope: task.</t>
         </is>
       </c>
       <c r="H6" s="4" t="inlineStr">
         <is>
-          <t>Depth: Independently builds and supports standard platform capabilities and templates for routine developer needs with review. Evidenced by: Builds and maintains golden-path assets for their component. Scope: component.</t>
+          <t>Depth: Independently builds and supports standard platform capabilities and templates for routine developer needs with review.
+Evidenced by: Builds and maintains golden-path assets for their component.
+Scope: component.</t>
         </is>
       </c>
       <c r="I6" s="4" t="inlineStr">
         <is>
-          <t>Depth: Designs self-service workflows for ambiguous needs, reducing friction and resolving hard abstraction and adoption issues. Evidenced by: Designs a golden path for a whole use case end to end. Scope: capability / domain (terminal level).</t>
+          <t>Depth: Designs self-service workflows for ambiguous needs, reducing friction and resolving hard abstraction and adoption issues.
+Evidenced by: Designs a golden path for a whole use case end to end.
+Scope: capability / domain (terminal level).</t>
         </is>
       </c>
       <c r="J6" s="4" t="inlineStr">
         <is>
-          <t>Depth: Defines platform architecture and golden paths others adopt, solving deep developer-experience and leverage problems. Evidenced by: Reconciles golden paths across teams into coherent journeys. Scope: multiple teams.</t>
+          <t>Depth: Defines platform architecture and golden paths others adopt, solving deep developer-experience and leverage problems.
+Evidenced by: Reconciles golden paths across teams into coherent journeys.
+Scope: multiple teams.</t>
         </is>
       </c>
       <c r="K6" s="4" t="inlineStr">
         <is>
-          <t>Depth: Sets organization-wide platform strategy, anticipating how developer-experience engineering should evolve. Evidenced by: Defines the organization's paved-road strategy. Scope: organization.</t>
+          <t>Depth: Sets organization-wide platform strategy, anticipating how developer-experience engineering should evolve.
+Evidenced by: Defines the organization's paved-road strategy.
+Scope: organization.</t>
         </is>
       </c>
       <c r="L6" s="4" t="inlineStr">
         <is>
-          <t>Depth: Defines what excellent platform engineering means for the field, shaping industry developer-experience practice. Evidenced by: Makes the paved road the company default by economics and quality, not policy. Scope: company.</t>
+          <t>Depth: Defines what excellent platform engineering means for the field, shaping industry developer-experience practice.
+Evidenced by: Makes the paved road the company default by economics and quality, not policy.
+Scope: company.</t>
         </is>
       </c>
     </row>
@@ -1118,32 +1178,44 @@
       </c>
       <c r="G7" s="4" t="inlineStr">
         <is>
-          <t>Depth: Names the exact docs, errors, and setup steps that forced them to understand internals a consumer should not need, and files concrete simplification issues. Evidenced by: Flags that provisioning a database requires reading the underlying Terraform module's internals just to fill in one required field, and files the doc fix. Scope: task.</t>
+          <t>Depth: Names the exact docs, errors, and setup steps that forced them to understand internals a consumer should not need, and files concrete simplification issues.
+Evidenced by: Flags that provisioning a database requires reading the underlying Terraform module's internals just to fill in one required field, and files the doc fix.
+Scope: task.</t>
         </is>
       </c>
       <c r="H7" s="4" t="inlineStr">
         <is>
-          <t>Depth: Reduces the concepts and steps a consumer must hold to use their component - collapsing configuration, defaulting decisions, rewriting errors to say what to do next - and shows the before/after. Evidenced by: Collapses a twelve-field service-creation form down to two required fields by defaulting the rest, and shows the before/after time-to-first-deploy. Scope: component.</t>
+          <t>Depth: Reduces the concepts and steps a consumer must hold to use their component - collapsing configuration, defaulting decisions, rewriting errors to say what to do next - and shows the before/after.
+Evidenced by: Collapses a twelve-field service-creation form down to two required fields by defaulting the rest, and shows the before/after time-to-first-deploy.
+Scope: component.</t>
         </is>
       </c>
       <c r="I7" s="4" t="inlineStr">
         <is>
-          <t>Depth: Designs a capability's abstractions around what consumers must not have to know, so a first-time user succeeds without reading internals; measures load with time-to-first-success and support-ticket themes and treats regressions as defects. Evidenced by: Rewrites a capability's onboarding so a first-time consumer ships without reading the implementation, tracking time-to-first-success as the load metric. Scope: capability / domain (terminal level).</t>
+          <t>Depth: Designs a capability's abstractions around what consumers must not have to know, so a first-time user succeeds without reading internals; measures load with time-to-first-success and support-ticket themes and treats regressions as defects.
+Evidenced by: Rewrites a capability's onboarding so a first-time consumer ships without reading the implementation, tracking time-to-first-success as the load metric.
+Scope: capability / domain (terminal level).</t>
         </is>
       </c>
       <c r="J7" s="4" t="inlineStr">
         <is>
-          <t>Depth: Audits cognitive load across team boundaries - quantifying onboarding time, concepts-to-learn, and ticket themes - and drives the cross-boundary simplifications no single team could make. Evidenced by: Finds three teams independently solved the same secrets-rotation problem because none could see the others' internals, and drives the shared fix across all three. Scope: multiple teams.</t>
+          <t>Depth: Audits cognitive load across team boundaries - quantifying onboarding time, concepts-to-learn, and ticket themes - and drives the cross-boundary simplifications no single team could make.
+Evidenced by: Finds three teams independently solved the same secrets-rotation problem because none could see the others' internals, and drives the shared fix across all three.
+Scope: multiple teams.</t>
         </is>
       </c>
       <c r="K7" s="4" t="inlineStr">
         <is>
-          <t>Depth: Makes cognitive load a first-class organizational measure with explicit load budgets, vetoing designs that externalize complexity onto consuming teams. Evidenced by: Sets an explicit cognitive-load budget per platform surface and vetoes a design that would have pushed new required concepts onto every consuming team. Scope: organization.</t>
+          <t>Depth: Makes cognitive load a first-class organizational measure with explicit load budgets, vetoing designs that externalize complexity onto consuming teams.
+Evidenced by: Sets an explicit cognitive-load budget per platform surface and vetoes a design that would have pushed new required concepts onto every consuming team.
+Scope: organization.</t>
         </is>
       </c>
       <c r="L7" s="4" t="inlineStr">
         <is>
-          <t>Depth: Shapes company-level technology and team-boundary choices explicitly around team cognitive load, arguing for fewer, deeper abstractions over sprawling optionality. Evidenced by: Argues successfully against a company-wide multi-cloud push on cognitive-load grounds -- fewer, deeper abstractions over optionality -- and the simpler single-cloud default ships instead. Scope: company.</t>
+          <t>Depth: Shapes company-level technology and team-boundary choices explicitly around team cognitive load, arguing for fewer, deeper abstractions over sprawling optionality.
+Evidenced by: Argues successfully against a company-wide multi-cloud push on cognitive-load grounds -- fewer, deeper abstractions over optionality -- and the simpler single-cloud default ships instead.
+Scope: company.</t>
         </is>
       </c>
     </row>
@@ -1180,32 +1252,44 @@
       </c>
       <c r="G8" s="4" t="inlineStr">
         <is>
-          <t>Depth: Implements designs specified by others; asks why, not just how. Evidenced by: Explains the platform's architecture in their own words. Scope: task.</t>
+          <t>Depth: Implements designs specified by others; asks why, not just how.
+Evidenced by: Explains the platform's architecture in their own words.
+Scope: task.</t>
         </is>
       </c>
       <c r="H8" s="4" t="inlineStr">
         <is>
-          <t>Depth: Designs sound components; understands coupling, cohesion, interface design. Evidenced by: Designs a component within an established architecture. Scope: component.</t>
+          <t>Depth: Designs sound components; understands coupling, cohesion, interface design.
+Evidenced by: Designs a component within an established architecture.
+Scope: component.</t>
         </is>
       </c>
       <c r="I8" s="4" t="inlineStr">
         <is>
-          <t>Depth: Designs systems for evolution: clean seams, versioned interfaces, replaceable parts. Evidenced by: Selects patterns by trade-off in design docs that name alternatives, failure modes, and evolution paths. Scope: capability / domain (terminal level).</t>
+          <t>Depth: Designs systems for evolution: clean seams, versioned interfaces, replaceable parts.
+Evidenced by: Selects patterns by trade-off in design docs that name alternatives, failure modes, and evolution paths.
+Scope: capability / domain (terminal level).</t>
         </is>
       </c>
       <c r="J8" s="4" t="inlineStr">
         <is>
-          <t>Depth: Mastery of architecture for complex systems; sets patterns and prevents drift. Evidenced by: Drives designs that cut across several teams' systems. Scope: multiple teams.</t>
+          <t>Depth: Mastery of architecture for complex systems; sets patterns and prevents drift.
+Evidenced by: Drives designs that cut across several teams' systems.
+Scope: multiple teams.</t>
         </is>
       </c>
       <c r="K8" s="4" t="inlineStr">
         <is>
-          <t>Depth: Sets multi-year architecture direction across the org. Evidenced by: Sets the architectural direction the platform organization builds against. Scope: organization.</t>
+          <t>Depth: Sets multi-year architecture direction across the org.
+Evidenced by: Sets the architectural direction the platform organization builds against.
+Scope: organization.</t>
         </is>
       </c>
       <c r="L8" s="4" t="inlineStr">
         <is>
-          <t>Depth: Authoritative and externally credible; defines architectural approach others follow. Evidenced by: Makes the company's foundational architecture bets. Scope: company.</t>
+          <t>Depth: Authoritative and externally credible; defines architectural approach others follow.
+Evidenced by: Makes the company's foundational architecture bets.
+Scope: company.</t>
         </is>
       </c>
     </row>
@@ -1242,32 +1326,44 @@
       </c>
       <c r="G9" s="4" t="inlineStr">
         <is>
-          <t>Depth: Understands HTTP/REST and the deploy pipeline; makes guided changes. Evidenced by: Uses the platform's APIs correctly from documentation alone. Scope: task.</t>
+          <t>Depth: Understands HTTP/REST and the deploy pipeline; makes guided changes.
+Evidenced by: Uses the platform's APIs correctly from documentation alone.
+Scope: task.</t>
         </is>
       </c>
       <c r="H9" s="4" t="inlineStr">
         <is>
-          <t>Depth: Designs clean APIs; understands rate limits, retries, timeouts, idempotency. Evidenced by: Extends a component's interface without breaking consumers. Scope: component.</t>
+          <t>Depth: Designs clean APIs; understands rate limits, retries, timeouts, idempotency.
+Evidenced by: Extends a component's interface without breaking consumers.
+Scope: component.</t>
         </is>
       </c>
       <c r="I9" s="4" t="inlineStr">
         <is>
-          <t>Depth: Designs services for scale and cost; understands distributed failure modes. Evidenced by: Designs a capability's interface as a long-lived product contract. Scope: capability / domain (terminal level).</t>
+          <t>Depth: Designs services for scale and cost; understands distributed failure modes.
+Evidenced by: Designs a capability's interface as a long-lived product contract.
+Scope: capability / domain (terminal level).</t>
         </is>
       </c>
       <c r="J9" s="4" t="inlineStr">
         <is>
-          <t>Depth: Expert in platform/service design (multi-tenancy, capacity, shared services). Evidenced by: Aligns interface conventions across several teams' APIs so the platform feels like one product. Scope: multiple teams.</t>
+          <t>Depth: Expert in platform/service design (multi-tenancy, capacity, shared services).
+Evidenced by: Aligns interface conventions across several teams' APIs so the platform feels like one product.
+Scope: multiple teams.</t>
         </is>
       </c>
       <c r="K9" s="4" t="inlineStr">
         <is>
-          <t>Depth: Sets interface standards used across the org. Evidenced by: Owns the organization's interface standards. Scope: organization.</t>
+          <t>Depth: Sets interface standards used across the org.
+Evidenced by: Owns the organization's interface standards.
+Scope: organization.</t>
         </is>
       </c>
       <c r="L9" s="4" t="inlineStr">
         <is>
-          <t>Depth: Defines company-wide API approach; trusted with irreversible interface bets. Evidenced by: Sets the company's contract with its developers. Scope: company.</t>
+          <t>Depth: Defines company-wide API approach; trusted with irreversible interface bets.
+Evidenced by: Sets the company's contract with its developers.
+Scope: company.</t>
         </is>
       </c>
     </row>
@@ -1304,32 +1400,44 @@
       </c>
       <c r="G10" s="4" t="inlineStr">
         <is>
-          <t>Depth: Writes functional, readable code; uses version control correctly; responds well to review. Evidenced by: Ships small, working changes that follow the codebase's conventions and pass review with minor feedback. Scope: task.</t>
+          <t>Depth: Writes functional, readable code; uses version control correctly; responds well to review.
+Evidenced by: Ships small, working changes that follow the codebase's conventions and pass review with minor feedback.
+Scope: task.</t>
         </is>
       </c>
       <c r="H10" s="4" t="inlineStr">
         <is>
-          <t>Depth: Writes clean, documented, modular code; gives useful review feedback. Evidenced by: Ships production-quality code independently. Scope: component.</t>
+          <t>Depth: Writes clean, documented, modular code; gives useful review feedback.
+Evidenced by: Ships production-quality code independently.
+Scope: component.</t>
         </is>
       </c>
       <c r="I10" s="4" t="inlineStr">
         <is>
-          <t>Depth: Designs for maintainability; leads refactors of problem areas; review feedback teaches. Evidenced by: Writes the code others study to learn how it is done here. Scope: capability / domain (terminal level).</t>
+          <t>Depth: Designs for maintainability; leads refactors of problem areas; review feedback teaches.
+Evidenced by: Writes the code others study to learn how it is done here.
+Scope: capability / domain (terminal level).</t>
         </is>
       </c>
       <c r="J10" s="4" t="inlineStr">
         <is>
-          <t>Depth: Expert in code health at scale (shared libraries, deprecations, large migrations). Evidenced by: Raises the code-health baseline across teams. Scope: multiple teams.</t>
+          <t>Depth: Expert in code health at scale (shared libraries, deprecations, large migrations).
+Evidenced by: Raises the code-health baseline across teams.
+Scope: multiple teams.</t>
         </is>
       </c>
       <c r="K10" s="4" t="inlineStr">
         <is>
-          <t>Depth: Shapes org-wide engineering standards for long-lived codebases. Evidenced by: Defines what code quality means for the organization. Scope: organization.</t>
+          <t>Depth: Shapes org-wide engineering standards for long-lived codebases.
+Evidenced by: Defines what code quality means for the organization.
+Scope: organization.</t>
         </is>
       </c>
       <c r="L10" s="4" t="inlineStr">
         <is>
-          <t>Depth: Defines what good engineering looks like company-wide; externally recognized. Evidenced by: Holds the company's long-horizon code health against short-term pressure. Scope: company.</t>
+          <t>Depth: Defines what good engineering looks like company-wide; externally recognized.
+Evidenced by: Holds the company's long-horizon code health against short-term pressure.
+Scope: company.</t>
         </is>
       </c>
     </row>
@@ -1366,32 +1474,44 @@
       </c>
       <c r="G11" s="4" t="inlineStr">
         <is>
-          <t>Depth: Navigates the codebase and understands code shown; reviews small changes. Evidenced by: Reviews peers' changes for readability and test coverage and asks genuine questions. Scope: task.</t>
+          <t>Depth: Navigates the codebase and understands code shown; reviews small changes.
+Evidenced by: Reviews peers' changes for readability and test coverage and asks genuine questions.
+Scope: task.</t>
         </is>
       </c>
       <c r="H11" s="4" t="inlineStr">
         <is>
-          <t>Depth: Independently understands unfamiliar code; gives timely, specific review feedback. Evidenced by: Gives reviews that catch real defects. Scope: component.</t>
+          <t>Depth: Independently understands unfamiliar code; gives timely, specific review feedback.
+Evidenced by: Gives reviews that catch real defects.
+Scope: component.</t>
         </is>
       </c>
       <c r="I11" s="4" t="inlineStr">
         <is>
-          <t>Depth: Quickly grasps complex/legacy systems; reviews raise the bar across a domain. Evidenced by: Reviews for systemic risk, not just correctness. Scope: capability / domain (terminal level).</t>
+          <t>Depth: Quickly grasps complex/legacy systems; reviews raise the bar across a domain.
+Evidenced by: Reviews for systemic risk, not just correctness.
+Scope: capability / domain (terminal level).</t>
         </is>
       </c>
       <c r="J11" s="4" t="inlineStr">
         <is>
-          <t>Depth: Expert at reviewing high-risk changes; review standards spread across teams. Evidenced by: Calibrates review culture across teams. Scope: multiple teams.</t>
+          <t>Depth: Expert at reviewing high-risk changes; review standards spread across teams.
+Evidenced by: Calibrates review culture across teams.
+Scope: multiple teams.</t>
         </is>
       </c>
       <c r="K11" s="4" t="inlineStr">
         <is>
-          <t>Depth: Authority on review practice org-wide. Evidenced by: Designs the organization's quality gates. Scope: organization.</t>
+          <t>Depth: Authority on review practice org-wide.
+Evidenced by: Designs the organization's quality gates.
+Scope: organization.</t>
         </is>
       </c>
       <c r="L11" s="4" t="inlineStr">
         <is>
-          <t>Depth: Defines what good review looks like; shapes industry-facing practice. Evidenced by: Reviews the changes that change the company. Scope: company.</t>
+          <t>Depth: Defines what good review looks like; shapes industry-facing practice.
+Evidenced by: Reviews the changes that change the company.
+Scope: company.</t>
         </is>
       </c>
     </row>
@@ -1428,32 +1548,44 @@
       </c>
       <c r="G12" s="4" t="inlineStr">
         <is>
-          <t>Depth: Writes unit tests with guidance; tests own changes before merging. Evidenced by: Writes unit tests that pin the behavior of their change, including the failure path. Scope: task.</t>
+          <t>Depth: Writes unit tests with guidance; tests own changes before merging.
+Evidenced by: Writes unit tests that pin the behavior of their change, including the failure path.
+Scope: task.</t>
         </is>
       </c>
       <c r="H12" s="4" t="inlineStr">
         <is>
-          <t>Depth: Applies the testing pyramid; everything shipped arrives tested; mocks dependencies sensibly. Evidenced by: Balances unit, integration, and end-to-end coverage for their component. Scope: component.</t>
+          <t>Depth: Applies the testing pyramid; everything shipped arrives tested; mocks dependencies sensibly.
+Evidenced by: Balances unit, integration, and end-to-end coverage for their component.
+Scope: component.</t>
         </is>
       </c>
       <c r="I12" s="4" t="inlineStr">
         <is>
-          <t>Depth: Designs testable systems (contract, property-based, replay from prod); owns a test strategy. Evidenced by: Designs the verification strategy for a capability. Scope: capability / domain (terminal level).</t>
+          <t>Depth: Designs testable systems (contract, property-based, replay from prod); owns a test strategy.
+Evidenced by: Designs the verification strategy for a capability.
+Scope: capability / domain (terminal level).</t>
         </is>
       </c>
       <c r="J12" s="4" t="inlineStr">
         <is>
-          <t>Depth: Expert in test strategy at scale (test data, environments, deployment safety). Evidenced by: Builds test infrastructure several teams rely on. Scope: multiple teams.</t>
+          <t>Depth: Expert in test strategy at scale (test data, environments, deployment safety).
+Evidenced by: Builds test infrastructure several teams rely on.
+Scope: multiple teams.</t>
         </is>
       </c>
       <c r="K12" s="4" t="inlineStr">
         <is>
-          <t>Depth: Sets testing/verification discipline across the org. Evidenced by: Sets the organization's testing standards. Scope: organization.</t>
+          <t>Depth: Sets testing/verification discipline across the org.
+Evidenced by: Sets the organization's testing standards.
+Scope: organization.</t>
         </is>
       </c>
       <c r="L12" s="4" t="inlineStr">
         <is>
-          <t>Depth: Shapes the company-wide quality culture; advances verification practice. Evidenced by: Frames verification as company risk management. Scope: company.</t>
+          <t>Depth: Shapes the company-wide quality culture; advances verification practice.
+Evidenced by: Frames verification as company risk management.
+Scope: company.</t>
         </is>
       </c>
     </row>
@@ -1490,32 +1622,44 @@
       </c>
       <c r="G13" s="4" t="inlineStr">
         <is>
-          <t>Depth: Uses and makes guided fixes to existing pipelines. Evidenced by: Ships through the pipeline correctly. Scope: task.</t>
+          <t>Depth: Uses and makes guided fixes to existing pipelines.
+Evidenced by: Ships through the pipeline correctly.
+Scope: task.</t>
         </is>
       </c>
       <c r="H13" s="4" t="inlineStr">
         <is>
-          <t>Depth: Independently builds and improves pipelines for their area. Evidenced by: Owns their component's pipeline. Scope: component.</t>
+          <t>Depth: Independently builds and improves pipelines for their area.
+Evidenced by: Owns their component's pipeline.
+Scope: component.</t>
         </is>
       </c>
       <c r="I13" s="4" t="inlineStr">
         <is>
-          <t>Depth: Designs deployment safety (progressive delivery, rollback) for a domain. Evidenced by: Designs CI/CD as a product for a capability's users. Scope: capability / domain (terminal level).</t>
+          <t>Depth: Designs deployment safety (progressive delivery, rollback) for a domain.
+Evidenced by: Designs CI/CD as a product for a capability's users.
+Scope: capability / domain (terminal level).</t>
         </is>
       </c>
       <c r="J13" s="4" t="inlineStr">
         <is>
-          <t>Depth: Expert in delivery engineering at scale; sets standards across teams. Evidenced by: Builds delivery infrastructure multiple teams ship through. Scope: multiple teams.</t>
+          <t>Depth: Expert in delivery engineering at scale; sets standards across teams.
+Evidenced by: Builds delivery infrastructure multiple teams ship through.
+Scope: multiple teams.</t>
         </is>
       </c>
       <c r="K13" s="4" t="inlineStr">
         <is>
-          <t>Depth: Defines the org's delivery/release philosophy. Evidenced by: Owns the organization's delivery architecture. Scope: organization.</t>
+          <t>Depth: Defines the org's delivery/release philosophy.
+Evidenced by: Owns the organization's delivery architecture.
+Scope: organization.</t>
         </is>
       </c>
       <c r="L13" s="4" t="inlineStr">
         <is>
-          <t>Depth: Advances release engineering practice company-wide. Evidenced by: Sets company delivery strategy. Scope: company.</t>
+          <t>Depth: Advances release engineering practice company-wide.
+Evidenced by: Sets company delivery strategy.
+Scope: company.</t>
         </is>
       </c>
     </row>
@@ -1552,32 +1696,44 @@
       </c>
       <c r="G14" s="4" t="inlineStr">
         <is>
-          <t>Depth: Follows the release process exactly — flags, staged rollout steps, verification checklists — verifies their change in production, and rolls back with guidance. Evidenced by: Executes migration and release steps from a runbook accurately. Scope: task.</t>
+          <t>Depth: Follows the release process exactly — flags, staged rollout steps, verification checklists — verifies their change in production, and rolls back with guidance.
+Evidenced by: Executes migration and release steps from a runbook accurately.
+Scope: task.</t>
         </is>
       </c>
       <c r="H14" s="4" t="inlineStr">
         <is>
-          <t>Depth: Ships behind flags with a rollback plan by default, monitors rollouts and reverts on their own judgment when signals degrade, and writes changes that tolerate both versions running during rollout. Evidenced by: Migrates their component's consumers off an old interface. Scope: component.</t>
+          <t>Depth: Ships behind flags with a rollback plan by default, monitors rollouts and reverts on their own judgment when signals degrade, and writes changes that tolerate both versions running during rollout.
+Evidenced by: Migrates their component's consumers off an old interface.
+Scope: component.</t>
         </is>
       </c>
       <c r="I14" s="4" t="inlineStr">
         <is>
-          <t>Depth: Designs the rollout for risky changes — canary criteria, migration sequencing, flag lifecycle, kill switches — and reviews others' rollout plans for blast radius; the person teams ask how to ship something safely. Evidenced by: Plans and runs a capability-level deprecation as a managed migration. Scope: capability / domain (terminal level).</t>
+          <t>Depth: Designs the rollout for risky changes — canary criteria, migration sequencing, flag lifecycle, kill switches — and reviews others' rollout plans for blast radius; the person teams ask how to ship something safely.
+Evidenced by: Plans and runs a capability-level deprecation as a managed migration.
+Scope: capability / domain (terminal level).</t>
         </is>
       </c>
       <c r="J14" s="4" t="inlineStr">
         <is>
-          <t>Depth: Builds progressive-delivery machinery multiple teams release through (flag platforms, automated canary analysis, automated rollback), retiring deploy patterns that cause repeat incidents and measurably raising deploy frequency. Evidenced by: Coordinates migrations that cross team boundaries. Scope: multiple teams.</t>
+          <t>Depth: Builds progressive-delivery machinery multiple teams release through (flag platforms, automated canary analysis, automated rollback), retiring deploy patterns that cause repeat incidents and measurably raising deploy frequency.
+Evidenced by: Coordinates migrations that cross team boundaries.
+Scope: multiple teams.</t>
         </is>
       </c>
       <c r="K14" s="4" t="inlineStr">
         <is>
-          <t>Depth: Owns release policy for an organization and its delivery metrics — rollout standards, freeze rules, environment strategy — dismantling ceremony that adds no safety. Evidenced by: Sets the organization's deprecation policy. Scope: organization.</t>
+          <t>Depth: Owns release policy for an organization and its delivery metrics — rollout standards, freeze rules, environment strategy — dismantling ceremony that adds no safety.
+Evidenced by: Sets the organization's deprecation policy.
+Scope: organization.</t>
         </is>
       </c>
       <c r="L14" s="4" t="inlineStr">
         <is>
-          <t>Depth: Sets how an entire company's software reaches customers — the risk posture products ship under — and defends it to executives, auditors, and regulators. Evidenced by: Sets the company's compatibility promise. Scope: company.</t>
+          <t>Depth: Sets how an entire company's software reaches customers — the risk posture products ship under — and defends it to executives, auditors, and regulators.
+Evidenced by: Sets the company's compatibility promise.
+Scope: company.</t>
         </is>
       </c>
     </row>
@@ -1614,32 +1770,44 @@
       </c>
       <c r="G15" s="4" t="inlineStr">
         <is>
-          <t>Depth: Makes guided changes to existing infra; understands core cloud services. Evidenced by: Provisions and modifies cloud resources from documented patterns. Scope: task.</t>
+          <t>Depth: Makes guided changes to existing infra; understands core cloud services.
+Evidenced by: Provisions and modifies cloud resources from documented patterns.
+Scope: task.</t>
         </is>
       </c>
       <c r="H15" s="4" t="inlineStr">
         <is>
-          <t>Depth: Independently builds and manages standard resources using IaC. Evidenced by: Designs the cloud footprint for a component. Scope: component.</t>
+          <t>Depth: Independently builds and manages standard resources using IaC.
+Evidenced by: Designs the cloud footprint for a component.
+Scope: component.</t>
         </is>
       </c>
       <c r="I15" s="4" t="inlineStr">
         <is>
-          <t>Depth: Designs infra for scale, cost and resilience across a domain. Evidenced by: Architects a capability's infrastructure for the failure domains that matter. Scope: capability / domain (terminal level).</t>
+          <t>Depth: Designs infra for scale, cost and resilience across a domain.
+Evidenced by: Architects a capability's infrastructure for the failure domains that matter.
+Scope: capability / domain (terminal level).</t>
         </is>
       </c>
       <c r="J15" s="4" t="inlineStr">
         <is>
-          <t>Depth: Expert in infra platforms used by many teams; owns major cost strategy. Evidenced by: Designs shared infrastructure patterns. Scope: multiple teams.</t>
+          <t>Depth: Expert in infra platforms used by many teams; owns major cost strategy.
+Evidenced by: Designs shared infrastructure patterns.
+Scope: multiple teams.</t>
         </is>
       </c>
       <c r="K15" s="4" t="inlineStr">
         <is>
-          <t>Depth: Sets org infrastructure direction. Evidenced by: Sets the organization's cloud strategy. Scope: organization.</t>
+          <t>Depth: Sets org infrastructure direction.
+Evidenced by: Sets the organization's cloud strategy.
+Scope: organization.</t>
         </is>
       </c>
       <c r="L15" s="4" t="inlineStr">
         <is>
-          <t>Depth: Trusted with company-level platform bets; defines infra strategy. Evidenced by: Owns company-level infrastructure bets. Scope: company.</t>
+          <t>Depth: Trusted with company-level platform bets; defines infra strategy.
+Evidenced by: Owns company-level infrastructure bets.
+Scope: company.</t>
         </is>
       </c>
     </row>
@@ -1676,32 +1844,44 @@
       </c>
       <c r="G16" s="4" t="inlineStr">
         <is>
-          <t>Depth: Deploys workloads to an existing orchestrator under review, adjusting basic scheduling settings from examples. Evidenced by: Deploys and debugs workloads on the orchestrator with guidance. Scope: task.</t>
+          <t>Depth: Deploys workloads to an existing orchestrator under review, adjusting basic scheduling settings from examples.
+Evidenced by: Deploys and debugs workloads on the orchestrator with guidance.
+Scope: task.</t>
         </is>
       </c>
       <c r="H16" s="4" t="inlineStr">
         <is>
-          <t>Depth: Independently operates orchestrated workloads, manages routine scaling, placement, and health checks with normal review. Evidenced by: Owns their component's runtime configuration. Scope: component.</t>
+          <t>Depth: Independently operates orchestrated workloads, manages routine scaling, placement, and health checks with normal review.
+Evidenced by: Owns their component's runtime configuration.
+Scope: component.</t>
         </is>
       </c>
       <c r="I16" s="4" t="inlineStr">
         <is>
-          <t>Depth: Designs scheduling, affinity, and resource policies for ambiguous workloads and resolves hard orchestration failures. Evidenced by: Designs and operates cluster-level platform machinery. Scope: capability / domain (terminal level).</t>
+          <t>Depth: Designs scheduling, affinity, and resource policies for ambiguous workloads and resolves hard orchestration failures.
+Evidenced by: Designs and operates cluster-level platform machinery.
+Scope: capability / domain (terminal level).</t>
         </is>
       </c>
       <c r="J16" s="4" t="inlineStr">
         <is>
-          <t>Depth: Defines cluster topology and scheduling patterns others adopt, solving deep placement, contention, and lifecycle problems. Evidenced by: Sets workload standards multiple teams schedule against. Scope: multiple teams.</t>
+          <t>Depth: Defines cluster topology and scheduling patterns others adopt, solving deep placement, contention, and lifecycle problems.
+Evidenced by: Sets workload standards multiple teams schedule against.
+Scope: multiple teams.</t>
         </is>
       </c>
       <c r="K16" s="4" t="inlineStr">
         <is>
-          <t>Depth: Sets organization-wide orchestration strategy and standards, anticipating where workload scheduling is heading. Evidenced by: Owns the organization's runtime strategy. Scope: organization.</t>
+          <t>Depth: Sets organization-wide orchestration strategy and standards, anticipating where workload scheduling is heading.
+Evidenced by: Owns the organization's runtime strategy.
+Scope: organization.</t>
         </is>
       </c>
       <c r="L16" s="4" t="inlineStr">
         <is>
-          <t>Depth: Defines what effective orchestration means for the discipline, externally credible in shaping scheduling practice. Evidenced by: Decides company-level runtime direction. Scope: company.</t>
+          <t>Depth: Defines what effective orchestration means for the discipline, externally credible in shaping scheduling practice.
+Evidenced by: Decides company-level runtime direction.
+Scope: company.</t>
         </is>
       </c>
     </row>
@@ -1738,32 +1918,44 @@
       </c>
       <c r="G17" s="4" t="inlineStr">
         <is>
-          <t>Depth: Configures basic network segments and routes from designs under review, verifying connectivity. Evidenced by: Traces a request through DNS, load balancer, and service to locate a failure. Scope: task.</t>
+          <t>Depth: Configures basic network segments and routes from designs under review, verifying connectivity.
+Evidenced by: Traces a request through DNS, load balancer, and service to locate a failure.
+Scope: task.</t>
         </is>
       </c>
       <c r="H17" s="4" t="inlineStr">
         <is>
-          <t>Depth: Independently builds standard network topologies, manages routing and segmentation for routine needs with review. Evidenced by: Configures the networking and compute for their component. Scope: component.</t>
+          <t>Depth: Independently builds standard network topologies, manages routing and segmentation for routine needs with review.
+Evidenced by: Configures the networking and compute for their component.
+Scope: component.</t>
         </is>
       </c>
       <c r="I17" s="4" t="inlineStr">
         <is>
-          <t>Depth: Designs routing and addressing schemes for ambiguous topologies and diagnoses hard reachability and routing failures. Evidenced by: Designs network and compute topology for a capability. Scope: capability / domain (terminal level).</t>
+          <t>Depth: Designs routing and addressing schemes for ambiguous topologies and diagnoses hard reachability and routing failures.
+Evidenced by: Designs network and compute topology for a capability.
+Scope: capability / domain (terminal level).</t>
         </is>
       </c>
       <c r="J17" s="4" t="inlineStr">
         <is>
-          <t>Depth: Defines network architecture and routing patterns others adopt, solving deep segmentation, scale, and convergence problems. Evidenced by: Owns shared foundations several teams depend on. Scope: multiple teams.</t>
+          <t>Depth: Defines network architecture and routing patterns others adopt, solving deep segmentation, scale, and convergence problems.
+Evidenced by: Owns shared foundations several teams depend on.
+Scope: multiple teams.</t>
         </is>
       </c>
       <c r="K17" s="4" t="inlineStr">
         <is>
-          <t>Depth: Sets organization-wide network strategy and standards, anticipating shifts in network design and routing. Evidenced by: Sets organization standards for network architecture and compute platforms. Scope: organization.</t>
+          <t>Depth: Sets organization-wide network strategy and standards, anticipating shifts in network design and routing.
+Evidenced by: Sets organization standards for network architecture and compute platforms.
+Scope: organization.</t>
         </is>
       </c>
       <c r="L17" s="4" t="inlineStr">
         <is>
-          <t>Depth: Defines what good network design means for the field, externally credible in shaping routing practice. Evidenced by: Owns company-scale foundation decisions. Scope: company.</t>
+          <t>Depth: Defines what good network design means for the field, externally credible in shaping routing practice.
+Evidenced by: Owns company-scale foundation decisions.
+Scope: company.</t>
         </is>
       </c>
     </row>
@@ -1800,32 +1992,44 @@
       </c>
       <c r="G18" s="4" t="inlineStr">
         <is>
-          <t>Depth: Writes simple declarative resource definitions from templates, applying them under review in non-production environments. Evidenced by: Makes changes through the IaC workflow rather than the console. Scope: task.</t>
+          <t>Depth: Writes simple declarative resource definitions from templates, applying them under review in non-production environments.
+Evidenced by: Makes changes through the IaC workflow rather than the console.
+Scope: task.</t>
         </is>
       </c>
       <c r="H18" s="4" t="inlineStr">
         <is>
-          <t>Depth: Independently provisions standard infrastructure stacks, manages state and variables, and handles routine drift with normal review. Evidenced by: Writes reusable, parameterized modules for their component. Scope: component.</t>
+          <t>Depth: Independently provisions standard infrastructure stacks, manages state and variables, and handles routine drift with normal review.
+Evidenced by: Writes reusable, parameterized modules for their component.
+Scope: component.</t>
         </is>
       </c>
       <c r="I18" s="4" t="inlineStr">
         <is>
-          <t>Depth: Designs reusable modules for ambiguous needs, structures state safely, and is the go-to for tricky provisioning failures. Evidenced by: Designs the IaC architecture for a capability. Scope: capability / domain (terminal level).</t>
+          <t>Depth: Designs reusable modules for ambiguous needs, structures state safely, and is the go-to for tricky provisioning failures.
+Evidenced by: Designs the IaC architecture for a capability.
+Scope: capability / domain (terminal level).</t>
         </is>
       </c>
       <c r="J18" s="4" t="inlineStr">
         <is>
-          <t>Depth: Defines the provisioning patterns and module conventions others adopt, solving thorny dependency and idempotency problems. Evidenced by: Publishes module libraries and IaC conventions multiple teams build on. Scope: multiple teams.</t>
+          <t>Depth: Defines the provisioning patterns and module conventions others adopt, solving thorny dependency and idempotency problems.
+Evidenced by: Publishes module libraries and IaC conventions multiple teams build on.
+Scope: multiple teams.</t>
         </is>
       </c>
       <c r="K18" s="4" t="inlineStr">
         <is>
-          <t>Depth: Sets the organization-wide IaC strategy, governance, and standards, anticipating shifts in declarative provisioning practice. Evidenced by: Sets the organization's IaC standards. Scope: organization.</t>
+          <t>Depth: Sets the organization-wide IaC strategy, governance, and standards, anticipating shifts in declarative provisioning practice.
+Evidenced by: Sets the organization's IaC standards.
+Scope: organization.</t>
         </is>
       </c>
       <c r="L18" s="4" t="inlineStr">
         <is>
-          <t>Depth: Defines what good infrastructure-as-code means for the field, shaping provisioning practices recognized across the industry. Evidenced by: Treats the company's infrastructure definition as a strategic asset. Scope: company.</t>
+          <t>Depth: Defines what good infrastructure-as-code means for the field, shaping provisioning practices recognized across the industry.
+Evidenced by: Treats the company's infrastructure definition as a strategic asset.
+Scope: company.</t>
         </is>
       </c>
     </row>
@@ -1862,32 +2066,44 @@
       </c>
       <c r="G19" s="4" t="inlineStr">
         <is>
-          <t>Depth: Maintains existing self-service platform components under review, addressing documented user requests. Evidenced by: Uses the self-service tooling as users do and documents the gaps that forced manual steps. Scope: task.</t>
+          <t>Depth: Maintains existing self-service platform components under review, addressing documented user requests.
+Evidenced by: Uses the self-service tooling as users do and documents the gaps that forced manual steps.
+Scope: task.</t>
         </is>
       </c>
       <c r="H19" s="4" t="inlineStr">
         <is>
-          <t>Depth: Independently builds and supports standard platform capabilities and templates for routine developer needs with review. Evidenced by: Automates a manual provisioning flow for their component into a self-service action. Scope: component.</t>
+          <t>Depth: Independently builds and supports standard platform capabilities and templates for routine developer needs with review.
+Evidenced by: Automates a manual provisioning flow for their component into a self-service action.
+Scope: component.</t>
         </is>
       </c>
       <c r="I19" s="4" t="inlineStr">
         <is>
-          <t>Depth: Designs self-service workflows for ambiguous needs, reducing friction and resolving hard abstraction and adoption issues. Evidenced by: Designs self-service for a capability end to end. Scope: capability / domain (terminal level).</t>
+          <t>Depth: Designs self-service workflows for ambiguous needs, reducing friction and resolving hard abstraction and adoption issues.
+Evidenced by: Designs self-service for a capability end to end.
+Scope: capability / domain (terminal level).</t>
         </is>
       </c>
       <c r="J19" s="4" t="inlineStr">
         <is>
-          <t>Depth: Defines platform architecture and golden paths others adopt, solving deep developer-experience and leverage problems. Evidenced by: Unifies self-service across teams behind one coherent interface. Scope: multiple teams.</t>
+          <t>Depth: Defines platform architecture and golden paths others adopt, solving deep developer-experience and leverage problems.
+Evidenced by: Unifies self-service across teams behind one coherent interface.
+Scope: multiple teams.</t>
         </is>
       </c>
       <c r="K19" s="4" t="inlineStr">
         <is>
-          <t>Depth: Sets organization-wide platform strategy, anticipating how developer-experience engineering should evolve. Evidenced by: Drives the organization to a self-service operating model. Scope: organization.</t>
+          <t>Depth: Sets organization-wide platform strategy, anticipating how developer-experience engineering should evolve.
+Evidenced by: Drives the organization to a self-service operating model.
+Scope: organization.</t>
         </is>
       </c>
       <c r="L19" s="4" t="inlineStr">
         <is>
-          <t>Depth: Defines what excellent platform engineering means for the field, shaping industry developer-experience practice. Evidenced by: Makes self-service the company's default operating model for infrastructure. Scope: company.</t>
+          <t>Depth: Defines what excellent platform engineering means for the field, shaping industry developer-experience practice.
+Evidenced by: Makes self-service the company's default operating model for infrastructure.
+Scope: company.</t>
         </is>
       </c>
     </row>
@@ -1924,32 +2140,44 @@
       </c>
       <c r="G20" s="4" t="inlineStr">
         <is>
-          <t>Depth: Understands logs/metrics/traces; reads existing dashboards. Evidenced by: Traces a failing deploy to a specific pod's OOM-kill using the team's existing dashboard, without needing a teammate to point them to it. Scope: task.</t>
+          <t>Depth: Understands logs/metrics/traces; reads existing dashboards.
+Evidenced by: Traces a failing deploy to a specific pod's OOM-kill using the team's existing dashboard, without needing a teammate to point them to it.
+Scope: task.</t>
         </is>
       </c>
       <c r="H20" s="4" t="inlineStr">
         <is>
-          <t>Depth: Instruments their services; builds dashboards; tunes alerts to limit noise. Evidenced by: Instruments their component so strangers can debug it. Scope: component.</t>
+          <t>Depth: Instruments their services; builds dashboards; tunes alerts to limit noise.
+Evidenced by: Instruments their component so strangers can debug it.
+Scope: component.</t>
         </is>
       </c>
       <c r="I20" s="4" t="inlineStr">
         <is>
-          <t>Depth: Designs observability for complex systems (end-to-end traces, quality signals, cost attribution). Evidenced by: Designs the observability offering for a capability. Scope: capability / domain (terminal level).</t>
+          <t>Depth: Designs observability for complex systems (end-to-end traces, quality signals, cost attribution).
+Evidenced by: Designs the observability offering for a capability.
+Scope: capability / domain (terminal level).</t>
         </is>
       </c>
       <c r="J20" s="4" t="inlineStr">
         <is>
-          <t>Depth: Expert in instrumentation trade-offs at scale, incl. privacy-safe logging. Evidenced by: Builds observability infrastructure multiple teams instrument against. Scope: multiple teams.</t>
+          <t>Depth: Expert in instrumentation trade-offs at scale, incl. privacy-safe logging.
+Evidenced by: Builds observability infrastructure multiple teams instrument against.
+Scope: multiple teams.</t>
         </is>
       </c>
       <c r="K20" s="4" t="inlineStr">
         <is>
-          <t>Depth: Defines org observability strategy. Evidenced by: Sets the organization's observability strategy and standards. Scope: organization.</t>
+          <t>Depth: Defines org observability strategy.
+Evidenced by: Sets the organization's observability strategy and standards.
+Scope: organization.</t>
         </is>
       </c>
       <c r="L20" s="4" t="inlineStr">
         <is>
-          <t>Depth: Shapes company-wide operational visibility; advances practice. Evidenced by: Frames observability as company capability. Scope: company.</t>
+          <t>Depth: Shapes company-wide operational visibility; advances practice.
+Evidenced by: Frames observability as company capability.
+Scope: company.</t>
         </is>
       </c>
     </row>
@@ -1986,32 +2214,44 @@
       </c>
       <c r="G21" s="4" t="inlineStr">
         <is>
-          <t>Depth: Understands SLOs and common failure modes; keeps components healthy with guidance. Evidenced by: Explains their service's SLOs and reads burn-rate dashboards correctly. Scope: task.</t>
+          <t>Depth: Understands SLOs and common failure modes; keeps components healthy with guidance.
+Evidenced by: Explains their service's SLOs and reads burn-rate dashboards correctly.
+Scope: task.</t>
         </is>
       </c>
       <c r="H21" s="4" t="inlineStr">
         <is>
-          <t>Depth: Builds retries, timeouts and fallbacks; understands blast radius. Evidenced by: Adds a retry-with-backoff and a fallback path to a flaky downstream call so that dependency's failure doesn't cascade into their own component. Scope: component.</t>
+          <t>Depth: Builds retries, timeouts and fallbacks; understands blast radius.
+Evidenced by: Adds a retry-with-backoff and a fallback path to a flaky downstream call so that dependency's failure doesn't cascade into their own component.
+Scope: component.</t>
         </is>
       </c>
       <c r="I21" s="4" t="inlineStr">
         <is>
-          <t>Depth: Designs for graceful degradation; defines SLOs; accountable for a domain's reliability. Evidenced by: Negotiates SLOs for a capability with its internal customers. Scope: capability / domain (terminal level).</t>
+          <t>Depth: Designs for graceful degradation; defines SLOs; accountable for a domain's reliability.
+Evidenced by: Negotiates SLOs for a capability with its internal customers.
+Scope: capability / domain (terminal level).</t>
         </is>
       </c>
       <c r="J21" s="4" t="inlineStr">
         <is>
-          <t>Depth: Expert in resilience and capacity planning at scale; drives down incidents systemically. Evidenced by: Aligns SLOs across dependent services so promises compose. Scope: multiple teams.</t>
+          <t>Depth: Expert in resilience and capacity planning at scale; drives down incidents systemically.
+Evidenced by: Aligns SLOs across dependent services so promises compose.
+Scope: multiple teams.</t>
         </is>
       </c>
       <c r="K21" s="4" t="inlineStr">
         <is>
-          <t>Depth: Owns org-level reliability; fixes risk in process and org design. Evidenced by: Owns the organization's SLO framework and review cadence. Scope: organization.</t>
+          <t>Depth: Owns org-level reliability; fixes risk in process and org design.
+Evidenced by: Owns the organization's SLO framework and review cadence.
+Scope: organization.</t>
         </is>
       </c>
       <c r="L21" s="4" t="inlineStr">
         <is>
-          <t>Depth: Sets the company's reliability philosophy. Evidenced by: Sets company reliability targets against business risk and cost. Scope: company.</t>
+          <t>Depth: Sets the company's reliability philosophy.
+Evidenced by: Sets company reliability targets against business risk and cost.
+Scope: company.</t>
         </is>
       </c>
     </row>
@@ -2048,32 +2288,44 @@
       </c>
       <c r="G22" s="4" t="inlineStr">
         <is>
-          <t>Depth: Responds to alerts with support; follows runbooks; escalates appropriately. Evidenced by: Executes runbook steps accurately during incidents under supervision. Scope: task.</t>
+          <t>Depth: Responds to alerts with support; follows runbooks; escalates appropriately.
+Evidenced by: Executes runbook steps accurately during incidents under supervision.
+Scope: task.</t>
         </is>
       </c>
       <c r="H22" s="4" t="inlineStr">
         <is>
-          <t>Depth: Triages and resolves routine incidents; clear notes; takes on-call. Evidenced by: Serves as primary on-call for their component. Scope: component.</t>
+          <t>Depth: Triages and resolves routine incidents; clear notes; takes on-call.
+Evidenced by: Serves as primary on-call for their component.
+Scope: component.</t>
         </is>
       </c>
       <c r="I22" s="4" t="inlineStr">
         <is>
-          <t>Depth: Leads response to complex failures; blameless postmortems; same failure never recurs. Evidenced by: Commands complex multi-team incidents. Scope: capability / domain (terminal level).</t>
+          <t>Depth: Leads response to complex failures; blameless postmortems; same failure never recurs.
+Evidenced by: Commands complex multi-team incidents.
+Scope: capability / domain (terminal level).</t>
         </is>
       </c>
       <c r="J22" s="4" t="inlineStr">
         <is>
-          <t>Depth: Expert in incident-management design (rotations, severity, escalation). Evidenced by: Designs the incident-management system itself. Scope: multiple teams.</t>
+          <t>Depth: Expert in incident-management design (rotations, severity, escalation).
+Evidenced by: Designs the incident-management system itself.
+Scope: multiple teams.</t>
         </is>
       </c>
       <c r="K22" s="4" t="inlineStr">
         <is>
-          <t>Depth: Commands the highest-severity incidents; sets incident process org-wide. Evidenced by: Owns the organization's major-incident readiness. Scope: organization.</t>
+          <t>Depth: Commands the highest-severity incidents; sets incident process org-wide.
+Evidenced by: Owns the organization's major-incident readiness.
+Scope: organization.</t>
         </is>
       </c>
       <c r="L22" s="4" t="inlineStr">
         <is>
-          <t>Depth: Sets the company's incident philosophy; calm authority in the worst moments. Evidenced by: Leads the company's existential incidents and the reforms after them. Scope: company.</t>
+          <t>Depth: Sets the company's incident philosophy; calm authority in the worst moments.
+Evidenced by: Leads the company's existential incidents and the reforms after them.
+Scope: company.</t>
         </is>
       </c>
     </row>
@@ -2110,32 +2362,44 @@
       </c>
       <c r="G23" s="4" t="inlineStr">
         <is>
-          <t>Depth: Responds to alerts with support; follows runbooks; escalates appropriately. Evidenced by: Contributes accurate timelines and observations to incident reviews. Scope: task.</t>
+          <t>Depth: Responds to alerts with support; follows runbooks; escalates appropriately.
+Evidenced by: Contributes accurate timelines and observations to incident reviews.
+Scope: task.</t>
         </is>
       </c>
       <c r="H23" s="4" t="inlineStr">
         <is>
-          <t>Depth: Triages and resolves routine incidents; clear notes; takes on-call. Evidenced by: Writes blameless postmortems for their component's incidents. Scope: component.</t>
+          <t>Depth: Triages and resolves routine incidents; clear notes; takes on-call.
+Evidenced by: Writes blameless postmortems for their component's incidents.
+Scope: component.</t>
         </is>
       </c>
       <c r="I23" s="4" t="inlineStr">
         <is>
-          <t>Depth: Leads response to complex failures; blameless postmortems; same failure never recurs. Evidenced by: Facilitates incident reviews others attend voluntarily. Scope: capability / domain (terminal level).</t>
+          <t>Depth: Leads response to complex failures; blameless postmortems; same failure never recurs.
+Evidenced by: Facilitates incident reviews others attend voluntarily.
+Scope: capability / domain (terminal level).</t>
         </is>
       </c>
       <c r="J23" s="4" t="inlineStr">
         <is>
-          <t>Depth: Expert in incident-management design (rotations, severity, escalation). Evidenced by: Builds the learning system across teams. Scope: multiple teams.</t>
+          <t>Depth: Expert in incident-management design (rotations, severity, escalation).
+Evidenced by: Builds the learning system across teams.
+Scope: multiple teams.</t>
         </is>
       </c>
       <c r="K23" s="4" t="inlineStr">
         <is>
-          <t>Depth: Commands the highest-severity incidents; sets incident process org-wide. Evidenced by: Drives org-level resilience investment from incident evidence. Scope: organization.</t>
+          <t>Depth: Commands the highest-severity incidents; sets incident process org-wide.
+Evidenced by: Drives org-level resilience investment from incident evidence.
+Scope: organization.</t>
         </is>
       </c>
       <c r="L23" s="4" t="inlineStr">
         <is>
-          <t>Depth: Sets the company's incident philosophy; calm authority in the worst moments. Evidenced by: Shapes the company's safety culture. Scope: company.</t>
+          <t>Depth: Sets the company's incident philosophy; calm authority in the worst moments.
+Evidenced by: Shapes the company's safety culture.
+Scope: company.</t>
         </is>
       </c>
     </row>
@@ -2172,32 +2436,44 @@
       </c>
       <c r="G24" s="4" t="inlineStr">
         <is>
-          <t>Depth: Understands cost/latency drivers of what they build. Evidenced by: Reads utilization and saturation dashboards correctly and flags approaching limits with evidence. Scope: task.</t>
+          <t>Depth: Understands cost/latency drivers of what they build.
+Evidenced by: Reads utilization and saturation dashboards correctly and flags approaching limits with evidence.
+Scope: task.</t>
         </is>
       </c>
       <c r="H24" s="4" t="inlineStr">
         <is>
-          <t>Depth: Applies standard optimizations; stays within cost/latency budgets. Evidenced by: Load-tests their component and sizes it from measured headroom rather than guesswork. Scope: component.</t>
+          <t>Depth: Applies standard optimizations; stays within cost/latency budgets.
+Evidenced by: Load-tests their component and sizes it from measured headroom rather than guesswork.
+Scope: component.</t>
         </is>
       </c>
       <c r="I24" s="4" t="inlineStr">
         <is>
-          <t>Depth: Designs cost-aware architectures; defines and tracks unit economics for a domain. Evidenced by: Owns capacity planning for a capability. Scope: capability / domain (terminal level).</t>
+          <t>Depth: Designs cost-aware architectures; defines and tracks unit economics for a domain.
+Evidenced by: Owns capacity planning for a capability.
+Scope: capability / domain (terminal level).</t>
         </is>
       </c>
       <c r="J24" s="4" t="inlineStr">
         <is>
-          <t>Depth: Expert in economics at scale (fleet optimization, build-vs-buy). Evidenced by: Runs capacity planning across shared pools that multiple teams draw from. Scope: multiple teams.</t>
+          <t>Depth: Expert in economics at scale (fleet optimization, build-vs-buy).
+Evidenced by: Runs capacity planning across shared pools that multiple teams draw from.
+Scope: multiple teams.</t>
         </is>
       </c>
       <c r="K24" s="4" t="inlineStr">
         <is>
-          <t>Depth: Owns org-level spend strategy; cost decisions change margins. Evidenced by: Owns the organization's capacity and efficiency program. Scope: organization.</t>
+          <t>Depth: Owns org-level spend strategy; cost decisions change margins.
+Evidenced by: Owns the organization's capacity and efficiency program.
+Scope: organization.</t>
         </is>
       </c>
       <c r="L24" s="4" t="inlineStr">
         <is>
-          <t>Depth: Shapes the company economics of the products. Evidenced by: Treats infrastructure economics as company strategy. Scope: company.</t>
+          <t>Depth: Shapes the company economics of the products.
+Evidenced by: Treats infrastructure economics as company strategy.
+Scope: company.</t>
         </is>
       </c>
     </row>
@@ -2234,32 +2510,44 @@
       </c>
       <c r="G25" s="4" t="inlineStr">
         <is>
-          <t>Depth: Runs and lightly edits existing automation under review, flagging tasks that remain manual. Evidenced by: Executes operational runbooks accurately and improves the runbook when a step is wrong or missing. Scope: task.</t>
+          <t>Depth: Runs and lightly edits existing automation under review, flagging tasks that remain manual.
+Evidenced by: Executes operational runbooks accurately and improves the runbook when a step is wrong or missing.
+Scope: task.</t>
         </is>
       </c>
       <c r="H25" s="4" t="inlineStr">
         <is>
-          <t>Depth: Independently automates routine operational tasks and integrates them into standard workflows with normal review. Evidenced by: Automates the recurring manual work in their component. Scope: component.</t>
+          <t>Depth: Independently automates routine operational tasks and integrates them into standard workflows with normal review.
+Evidenced by: Automates the recurring manual work in their component.
+Scope: component.</t>
         </is>
       </c>
       <c r="I25" s="4" t="inlineStr">
         <is>
-          <t>Depth: Designs automation for ambiguous, error-prone toil and resolves hard reliability and orchestration issues in pipelines. Evidenced by: Measures toil for a capability and holds it under an explicit budget. Scope: capability / domain (terminal level).</t>
+          <t>Depth: Designs automation for ambiguous, error-prone toil and resolves hard reliability and orchestration issues in pipelines.
+Evidenced by: Measures toil for a capability and holds it under an explicit budget.
+Scope: capability / domain (terminal level).</t>
         </is>
       </c>
       <c r="J25" s="4" t="inlineStr">
         <is>
-          <t>Depth: Defines automation patterns and toil-elimination practices others adopt, solving deep workflow and safety problems. Evidenced by: Builds automation multiple teams reuse for their operational work. Scope: multiple teams.</t>
+          <t>Depth: Defines automation patterns and toil-elimination practices others adopt, solving deep workflow and safety problems.
+Evidenced by: Builds automation multiple teams reuse for their operational work.
+Scope: multiple teams.</t>
         </is>
       </c>
       <c r="K25" s="4" t="inlineStr">
         <is>
-          <t>Depth: Sets organization-wide automation strategy, anticipating where automation-first operations should head. Evidenced by: Sets the organization's toil policy. Scope: organization.</t>
+          <t>Depth: Sets organization-wide automation strategy, anticipating where automation-first operations should head.
+Evidenced by: Sets the organization's toil policy.
+Scope: organization.</t>
         </is>
       </c>
       <c r="L25" s="4" t="inlineStr">
         <is>
-          <t>Depth: Defines what automation-first operations means for the discipline, externally credible in shaping the practice. Evidenced by: Makes operational leverage a company-level argument. Scope: company.</t>
+          <t>Depth: Defines what automation-first operations means for the discipline, externally credible in shaping the practice.
+Evidenced by: Makes operational leverage a company-level argument.
+Scope: company.</t>
         </is>
       </c>
     </row>
@@ -2296,32 +2584,44 @@
       </c>
       <c r="G26" s="4" t="inlineStr">
         <is>
-          <t>Depth: Works within existing guardrails, reads a policy violation to its cause instead of requesting an exception, and explains what each guardrail protects against. Evidenced by: Traces a blocked deploy to a missing resource-limit field in the manifest instead of filing an exception request, and fixes it. Scope: task.</t>
+          <t>Depth: Works within existing guardrails, reads a policy violation to its cause instead of requesting an exception, and explains what each guardrail protects against.
+Evidenced by: Traces a blocked deploy to a missing resource-limit field in the manifest instead of filing an exception request, and fixes it.
+Scope: task.</t>
         </is>
       </c>
       <c r="H26" s="4" t="inlineStr">
         <is>
-          <t>Depth: Writes and tests policy rules for a component - admission checks, pipeline gates - with low false-positive rates and violation messages that tell the user how to comply. Evidenced by: Writes an admission-control rule for their component that catches unencrypted volumes with a message that tells the requester exactly which field to change. Scope: component.</t>
+          <t>Depth: Writes and tests policy rules for a component - admission checks, pipeline gates - with low false-positive rates and violation messages that tell the user how to comply.
+Evidenced by: Writes an admission-control rule for their component that catches unencrypted volumes with a message that tells the requester exactly which field to change.
+Scope: component.</t>
         </is>
       </c>
       <c r="I26" s="4" t="inlineStr">
         <is>
-          <t>Depth: Designs the guardrail architecture for a capability - what is blocked, warned, or audited, with documented threat reasoning - tuned so the safe path is the fast path, and runs an audited exception workflow without becoming the bottleneck. Evidenced by: Designs a capability's guardrail set -- what blocks, what warns, what only audits -- with the threat each rule defends against written down, and runs the exception process without becoming its bottleneck. Scope: capability / domain (terminal level).</t>
+          <t>Depth: Designs the guardrail architecture for a capability - what is blocked, warned, or audited, with documented threat reasoning - tuned so the safe path is the fast path, and runs an audited exception workflow without becoming the bottleneck.
+Evidenced by: Designs a capability's guardrail set -- what blocks, what warns, what only audits -- with the threat each rule defends against written down, and runs the exception process without becoming its bottleneck.
+Scope: capability / domain (terminal level).</t>
         </is>
       </c>
       <c r="J26" s="4" t="inlineStr">
         <is>
-          <t>Depth: Harmonizes policy across teams into a coherent, versioned policy library with a governed exception process, and adjudicates escalated safety-versus-velocity disputes. Evidenced by: Merges three teams' near-duplicate policy libraries into one versioned set and adjudicates which team's stricter rule wins. Scope: multiple teams.</t>
+          <t>Depth: Harmonizes policy across teams into a coherent, versioned policy library with a governed exception process, and adjudicates escalated safety-versus-velocity disputes.
+Evidenced by: Merges three teams' near-duplicate policy libraries into one versioned set and adjudicates which team's stricter rule wins.
+Scope: multiple teams.</t>
         </is>
       </c>
       <c r="K26" s="4" t="inlineStr">
         <is>
-          <t>Depth: Owns an organization's preventive-control strategy with security partners - the control catalog, its coverage, and the evidence it works - moving enforcement from review-time to platform-time. Evidenced by: Owns the guardrail catalog with the security team, moving a manual pre-launch review into an automated pipeline gate. Scope: organization.</t>
+          <t>Depth: Owns an organization's preventive-control strategy with security partners - the control catalog, its coverage, and the evidence it works - moving enforcement from review-time to platform-time.
+Evidenced by: Owns the guardrail catalog with the security team, moving a manual pre-launch review into an automated pipeline gate.
+Scope: organization.</t>
         </is>
       </c>
       <c r="L26" s="4" t="inlineStr">
         <is>
-          <t>Depth: Sets an organization-defining balance of enablement and control, accountable for guardrails that hold under audit and attack without throttling delivery. Evidenced by: Sets the company's default posture on where automation blocks versus warns, and defends it to auditors after an incident nearly reopens the debate. Scope: company.</t>
+          <t>Depth: Sets an organization-defining balance of enablement and control, accountable for guardrails that hold under audit and attack without throttling delivery.
+Evidenced by: Sets the company's default posture on where automation blocks versus warns, and defends it to auditors after an incident nearly reopens the debate.
+Scope: company.</t>
         </is>
       </c>
     </row>
@@ -2358,32 +2658,44 @@
       </c>
       <c r="G27" s="4" t="inlineStr">
         <is>
-          <t>Depth: Provisions and deprovisions accounts from documented procedures, with approvals and access reviewed before activation. Evidenced by: Requests and uses credentials through the sanctioned workflow. Scope: task.</t>
+          <t>Depth: Provisions and deprovisions accounts from documented procedures, with approvals and access reviewed before activation.
+Evidenced by: Requests and uses credentials through the sanctioned workflow.
+Scope: task.</t>
         </is>
       </c>
       <c r="H27" s="4" t="inlineStr">
         <is>
-          <t>Depth: Configures roles, group membership, and authentication factors independently for standard joiners, movers, and leavers. Evidenced by: Configures workload identity, scoped roles, and secret rotation for their component. Scope: component.</t>
+          <t>Depth: Configures roles, group membership, and authentication factors independently for standard joiners, movers, and leavers.
+Evidenced by: Configures workload identity, scoped roles, and secret rotation for their component.
+Scope: component.</t>
         </is>
       </c>
       <c r="I27" s="4" t="inlineStr">
         <is>
-          <t>Depth: Resolves complex entitlement conflicts and designs least-privilege role models for ambiguous, cross-system access needs. Evidenced by: Designs the identity model for a capability. Scope: capability / domain (terminal level).</t>
+          <t>Depth: Resolves complex entitlement conflicts and designs least-privilege role models for ambiguous, cross-system access needs.
+Evidenced by: Designs the identity model for a capability.
+Scope: capability / domain (terminal level).</t>
         </is>
       </c>
       <c r="J27" s="4" t="inlineStr">
         <is>
-          <t>Depth: Defines the identity lifecycle and authorization architecture that other engineers adopt across the organization. Evidenced by: Builds identity infrastructure multiple teams authenticate through. Scope: multiple teams.</t>
+          <t>Depth: Defines the identity lifecycle and authorization architecture that other engineers adopt across the organization.
+Evidenced by: Builds identity infrastructure multiple teams authenticate through.
+Scope: multiple teams.</t>
         </is>
       </c>
       <c r="K27" s="4" t="inlineStr">
         <is>
-          <t>Depth: Sets identity strategy, governs federation and privileged-access standards, and anticipates emerging access risks. Evidenced by: Owns the organization's identity architecture and its zero-trust roadmap. Scope: organization.</t>
+          <t>Depth: Sets identity strategy, governs federation and privileged-access standards, and anticipates emerging access risks.
+Evidenced by: Owns the organization's identity architecture and its zero-trust roadmap.
+Scope: organization.</t>
         </is>
       </c>
       <c r="L27" s="4" t="inlineStr">
         <is>
-          <t>Depth: Defines what sound identity practice means for the field and shapes how others govern access. Evidenced by: Sets company identity strategy across employee, workload, and customer boundaries. Scope: company.</t>
+          <t>Depth: Defines what sound identity practice means for the field and shapes how others govern access.
+Evidenced by: Sets company identity strategy across employee, workload, and customer boundaries.
+Scope: company.</t>
         </is>
       </c>
     </row>
@@ -2420,32 +2732,44 @@
       </c>
       <c r="G28" s="4" t="inlineStr">
         <is>
-          <t>Depth: Verifies artifact provenance and signatures following documented checks, escalating anomalies for review. Evidenced by: Keeps dependencies current on their tasks and acts on vulnerability-scanner findings with guidance. Scope: task.</t>
+          <t>Depth: Verifies artifact provenance and signatures following documented checks, escalating anomalies for review.
+Evidenced by: Keeps dependencies current on their tasks and acts on vulnerability-scanner findings with guidance.
+Scope: task.</t>
         </is>
       </c>
       <c r="H28" s="4" t="inlineStr">
         <is>
-          <t>Depth: Configures signing, dependency scanning, and provenance controls independently for standard pipelines. Evidenced by: Maintains their component's supply-chain hygiene. Scope: component.</t>
+          <t>Depth: Configures signing, dependency scanning, and provenance controls independently for standard pipelines.
+Evidenced by: Maintains their component's supply-chain hygiene.
+Scope: component.</t>
         </is>
       </c>
       <c r="I28" s="4" t="inlineStr">
         <is>
-          <t>Depth: Designs artifact-integrity and dependency-trust controls for complex, ambiguous supply chains. Evidenced by: Designs a capability's pipeline to a stated supply-chain integrity level. Scope: capability / domain (terminal level).</t>
+          <t>Depth: Designs artifact-integrity and dependency-trust controls for complex, ambiguous supply chains.
+Evidenced by: Designs a capability's pipeline to a stated supply-chain integrity level.
+Scope: capability / domain (terminal level).</t>
         </is>
       </c>
       <c r="J28" s="4" t="inlineStr">
         <is>
-          <t>Depth: Defines the supply-chain security architecture and verification patterns others adopt. Evidenced by: Builds supply-chain controls into the shared pipeline so every team inherits provenance and scanning by default. Scope: multiple teams.</t>
+          <t>Depth: Defines the supply-chain security architecture and verification patterns others adopt.
+Evidenced by: Builds supply-chain controls into the shared pipeline so every team inherits provenance and scanning by default.
+Scope: multiple teams.</t>
         </is>
       </c>
       <c r="K28" s="4" t="inlineStr">
         <is>
-          <t>Depth: Sets supply-chain assurance strategy and anticipates emerging artifact and dependency threats. Evidenced by: Owns the organization's supply-chain security program. Scope: organization.</t>
+          <t>Depth: Sets supply-chain assurance strategy and anticipates emerging artifact and dependency threats.
+Evidenced by: Owns the organization's supply-chain security program.
+Scope: organization.</t>
         </is>
       </c>
       <c r="L28" s="4" t="inlineStr">
         <is>
-          <t>Depth: Defines authoritative supply-chain security practice that shapes industry expectations. Evidenced by: Sets company supply-chain policy including third-party and vendor software. Scope: company.</t>
+          <t>Depth: Defines authoritative supply-chain security practice that shapes industry expectations.
+Evidenced by: Sets company supply-chain policy including third-party and vendor software.
+Scope: company.</t>
         </is>
       </c>
     </row>
@@ -2482,32 +2806,44 @@
       </c>
       <c r="G29" s="4" t="inlineStr">
         <is>
-          <t>Depth: Knows data handling has privacy implications; follows rules. Evidenced by: Follows the platform's compliance procedures accurately. Scope: task.</t>
+          <t>Depth: Knows data handling has privacy implications; follows rules.
+Evidenced by: Follows the platform's compliance procedures accurately.
+Scope: task.</t>
         </is>
       </c>
       <c r="H29" s="4" t="inlineStr">
         <is>
-          <t>Depth: Applies PII handling, redaction, residency and retention correctly. Evidenced by: Automates evidence collection for their component's controls. Scope: component.</t>
+          <t>Depth: Applies PII handling, redaction, residency and retention correctly.
+Evidenced by: Automates evidence collection for their component's controls.
+Scope: component.</t>
         </is>
       </c>
       <c r="I29" s="4" t="inlineStr">
         <is>
-          <t>Depth: Designs for compliance (consent, audit trails, regional rules); owns readiness for a domain. Evidenced by: Maps a capability's controls to the frameworks the company answers to and designs them to be inherited. Scope: capability / domain (terminal level).</t>
+          <t>Depth: Designs for compliance (consent, audit trails, regional rules); owns readiness for a domain.
+Evidenced by: Maps a capability's controls to the frameworks the company answers to and designs them to be inherited.
+Scope: capability / domain (terminal level).</t>
         </is>
       </c>
       <c r="J29" s="4" t="inlineStr">
         <is>
-          <t>Depth: Expert at translating regulation into controls; represents engineering in audits. Evidenced by: Rationalizes overlapping control implementations across teams into shared, platform-enforced controls. Scope: multiple teams.</t>
+          <t>Depth: Expert at translating regulation into controls; represents engineering in audits.
+Evidenced by: Rationalizes overlapping control implementations across teams into shared, platform-enforced controls.
+Scope: multiple teams.</t>
         </is>
       </c>
       <c r="K29" s="4" t="inlineStr">
         <is>
-          <t>Depth: Sets org compliance strategy; anticipates regulation. Evidenced by: Owns the organization's compliance-as-code strategy with legal and security partners. Scope: organization.</t>
+          <t>Depth: Sets org compliance strategy; anticipates regulation.
+Evidenced by: Owns the organization's compliance-as-code strategy with legal and security partners.
+Scope: organization.</t>
         </is>
       </c>
       <c r="L29" s="4" t="inlineStr">
         <is>
-          <t>Depth: Authoritative on the landscape; trusted interface to regulators. Evidenced by: Shapes company posture on regulatory strategy where infrastructure is implicated. Scope: company.</t>
+          <t>Depth: Authoritative on the landscape; trusted interface to regulators.
+Evidenced by: Shapes company posture on regulatory strategy where infrastructure is implicated.
+Scope: company.</t>
         </is>
       </c>
     </row>
@@ -2544,32 +2880,44 @@
       </c>
       <c r="G30" s="4" t="inlineStr">
         <is>
-          <t>Depth: Writes and updates doc pages within an existing structure under guidance. Evidenced by: Fixes documentation errors they hit instead of working around them. Scope: task.</t>
+          <t>Depth: Writes and updates doc pages within an existing structure under guidance.
+Evidenced by: Fixes documentation errors they hit instead of working around them.
+Scope: task.</t>
         </is>
       </c>
       <c r="H30" s="4" t="inlineStr">
         <is>
-          <t>Depth: Authors and organizes documentation for a product area with normal review. Evidenced by: Keeps their component's docs shippable. Scope: component.</t>
+          <t>Depth: Authors and organizes documentation for a product area with normal review.
+Evidenced by: Keeps their component's docs shippable.
+Scope: component.</t>
         </is>
       </c>
       <c r="I30" s="4" t="inlineStr">
         <is>
-          <t>Depth: Independently architects coherent doc structures for complex, evolving products. Evidenced by: Designs a capability's documentation as part of the product. Scope: capability / domain (terminal level).</t>
+          <t>Depth: Independently architects coherent doc structures for complex, evolving products.
+Evidenced by: Designs a capability's documentation as part of the product.
+Scope: capability / domain (terminal level).</t>
         </is>
       </c>
       <c r="J30" s="4" t="inlineStr">
         <is>
-          <t>Depth: Defines information-architecture standards others adopt and restructures tangled doc sets. Evidenced by: Sets documentation conventions multiple teams follow. Scope: multiple teams.</t>
+          <t>Depth: Defines information-architecture standards others adopt and restructures tangled doc sets.
+Evidenced by: Sets documentation conventions multiple teams follow.
+Scope: multiple teams.</t>
         </is>
       </c>
       <c r="K30" s="4" t="inlineStr">
         <is>
-          <t>Depth: Sets the org's documentation strategy and anticipates structural scaling needs. Evidenced by: Owns the organization's developer-facing knowledge strategy. Scope: organization.</t>
+          <t>Depth: Sets the org's documentation strategy and anticipates structural scaling needs.
+Evidenced by: Owns the organization's developer-facing knowledge strategy.
+Scope: organization.</t>
         </is>
       </c>
       <c r="L30" s="4" t="inlineStr">
         <is>
-          <t>Depth: Defines great developer documentation and information architecture for the field. Evidenced by: Writes the canonical company documents. Scope: company.</t>
+          <t>Depth: Defines great developer documentation and information architecture for the field.
+Evidenced by: Writes the canonical company documents.
+Scope: company.</t>
         </is>
       </c>
     </row>
@@ -2606,32 +2954,44 @@
       </c>
       <c r="G31" s="4" t="inlineStr">
         <is>
-          <t>Depth: Communicates status clearly; documentation is accurate. Evidenced by: Writes clear tickets, PR descriptions, and status updates that need no follow-up questions. Scope: task.</t>
+          <t>Depth: Communicates status clearly; documentation is accurate.
+Evidenced by: Writes clear tickets, PR descriptions, and status updates that need no follow-up questions.
+Scope: task.</t>
         </is>
       </c>
       <c r="H31" s="4" t="inlineStr">
         <is>
-          <t>Depth: Writes clear design notes, runbooks and PRs; explains trade-offs without overselling. Evidenced by: Writes short design docs that state the problem, options, and recommendation. Scope: component.</t>
+          <t>Depth: Writes clear design notes, runbooks and PRs; explains trade-offs without overselling.
+Evidenced by: Writes short design docs that state the problem, options, and recommendation.
+Scope: component.</t>
         </is>
       </c>
       <c r="I31" s="4" t="inlineStr">
         <is>
-          <t>Depth: Writes design docs that drive decisions; translates technical risk for non-technical stakeholders. Evidenced by: Writes design docs that make complex trade-offs decidable by non-experts. Scope: capability / domain (terminal level).</t>
+          <t>Depth: Writes design docs that drive decisions; translates technical risk for non-technical stakeholders.
+Evidenced by: Writes design docs that make complex trade-offs decidable by non-experts.
+Scope: capability / domain (terminal level).</t>
         </is>
       </c>
       <c r="J31" s="4" t="inlineStr">
         <is>
-          <t>Depth: Expert at making complex capability/risk legible to executives without dumbing it down; RFCs align orgs. Evidenced by: Writes the cross-team proposals that settle contested technical questions. Scope: multiple teams.</t>
+          <t>Depth: Expert at making complex capability/risk legible to executives without dumbing it down; RFCs align orgs.
+Evidenced by: Writes the cross-team proposals that settle contested technical questions.
+Scope: multiple teams.</t>
         </is>
       </c>
       <c r="K31" s="4" t="inlineStr">
         <is>
-          <t>Depth: Strategy memos leadership acts on; org-wide and external reach. Evidenced by: Sets the organization's bar for decision writing. Scope: organization.</t>
+          <t>Depth: Strategy memos leadership acts on; org-wide and external reach.
+Evidenced by: Sets the organization's bar for decision writing.
+Scope: organization.</t>
         </is>
       </c>
       <c r="L31" s="4" t="inlineStr">
         <is>
-          <t>Depth: A clarifying voice at company scale; externally recognized. Evidenced by: Communicates deep technical trade-offs to executives in the language of business risk without losing correctness. Scope: company.</t>
+          <t>Depth: A clarifying voice at company scale; externally recognized.
+Evidenced by: Communicates deep technical trade-offs to executives in the language of business risk without losing correctness.
+Scope: company.</t>
         </is>
       </c>
     </row>
@@ -2668,32 +3028,44 @@
       </c>
       <c r="G32" s="4" t="inlineStr">
         <is>
-          <t>Depth: Engages community channels and answers routine questions under guidance. Evidenced by: Answers user questions in support channels accurately or routes them fast. Scope: task.</t>
+          <t>Depth: Engages community channels and answers routine questions under guidance.
+Evidenced by: Answers user questions in support channels accurately or routes them fast.
+Scope: task.</t>
         </is>
       </c>
       <c r="H32" s="4" t="inlineStr">
         <is>
-          <t>Depth: Grows and supports a developer community segment with normal review. Evidenced by: Runs enablement for their component. Scope: component.</t>
+          <t>Depth: Grows and supports a developer community segment with normal review.
+Evidenced by: Runs enablement for their component.
+Scope: component.</t>
         </is>
       </c>
       <c r="I32" s="4" t="inlineStr">
         <is>
-          <t>Depth: Independently builds thriving communities and defuses tense community conflicts. Evidenced by: Drives adoption of a capability through evangelism rather than mandate. Scope: capability / domain (terminal level).</t>
+          <t>Depth: Independently builds thriving communities and defuses tense community conflicts.
+Evidenced by: Drives adoption of a capability through evangelism rather than mandate.
+Scope: capability / domain (terminal level).</t>
         </is>
       </c>
       <c r="J32" s="4" t="inlineStr">
         <is>
-          <t>Depth: Defines community-building practices others adopt and revives flagging communities. Evidenced by: Builds the enablement machinery platform teams share. Scope: multiple teams.</t>
+          <t>Depth: Defines community-building practices others adopt and revives flagging communities.
+Evidenced by: Builds the enablement machinery platform teams share.
+Scope: multiple teams.</t>
         </is>
       </c>
       <c r="K32" s="4" t="inlineStr">
         <is>
-          <t>Depth: Sets the org's community strategy and anticipates where developer interest is shifting. Evidenced by: Owns the platform's internal brand and narrative. Scope: organization.</t>
+          <t>Depth: Sets the org's community strategy and anticipates where developer interest is shifting.
+Evidenced by: Owns the platform's internal brand and narrative.
+Scope: organization.</t>
         </is>
       </c>
       <c r="L32" s="4" t="inlineStr">
         <is>
-          <t>Depth: Defines what great developer advocacy means and is externally recognized for it. Evidenced by: Represents the company's engineering platform externally. Scope: company.</t>
+          <t>Depth: Defines what great developer advocacy means and is externally recognized for it.
+Evidenced by: Represents the company's engineering platform externally.
+Scope: company.</t>
         </is>
       </c>
     </row>
@@ -2730,32 +3102,44 @@
       </c>
       <c r="G33" s="4" t="inlineStr">
         <is>
-          <t>Depth: Prepares updates and gathers input for stakeholders under direction. Evidenced by: Communicates status honestly and early - especially bad news. Scope: task.</t>
+          <t>Depth: Prepares updates and gathers input for stakeholders under direction.
+Evidenced by: Communicates status honestly and early - especially bad news.
+Scope: task.</t>
         </is>
       </c>
       <c r="H33" s="4" t="inlineStr">
         <is>
-          <t>Depth: Manages routine stakeholder relationships and communications with normal review. Evidenced by: Manages expectations for their component with its consuming teams. Scope: component.</t>
+          <t>Depth: Manages routine stakeholder relationships and communications with normal review.
+Evidenced by: Manages expectations for their component with its consuming teams.
+Scope: component.</t>
         </is>
       </c>
       <c r="I33" s="4" t="inlineStr">
         <is>
-          <t>Depth: Independently aligns conflicting stakeholders and navigates tense executive conversations. Evidenced by: Runs the stakeholder relationships for a capability. Scope: capability / domain (terminal level).</t>
+          <t>Depth: Independently aligns conflicting stakeholders and navigates tense executive conversations.
+Evidenced by: Runs the stakeholder relationships for a capability.
+Scope: capability / domain (terminal level).</t>
         </is>
       </c>
       <c r="J33" s="4" t="inlineStr">
         <is>
-          <t>Depth: Defines stakeholder-engagement approaches others adopt and brokers the hardest alignment. Evidenced by: Aligns competing demands from multiple teams into a roadmap each can live with. Scope: multiple teams.</t>
+          <t>Depth: Defines stakeholder-engagement approaches others adopt and brokers the hardest alignment.
+Evidenced by: Aligns competing demands from multiple teams into a roadmap each can live with.
+Scope: multiple teams.</t>
         </is>
       </c>
       <c r="K33" s="4" t="inlineStr">
         <is>
-          <t>Depth: Sets executive-engagement strategy and anticipates leadership concerns before they arise. Evidenced by: Manages the platform's relationship with organization leadership. Scope: organization.</t>
+          <t>Depth: Sets executive-engagement strategy and anticipates leadership concerns before they arise.
+Evidenced by: Manages the platform's relationship with organization leadership.
+Scope: organization.</t>
         </is>
       </c>
       <c r="L33" s="4" t="inlineStr">
         <is>
-          <t>Depth: Defines exemplary stakeholder management for the discipline and is externally credible on it. Evidenced by: Operates at executive level as the technical counterpart on company decisions that touch the platform. Scope: company.</t>
+          <t>Depth: Defines exemplary stakeholder management for the discipline and is externally credible on it.
+Evidenced by: Operates at executive level as the technical counterpart on company decisions that touch the platform.
+Scope: company.</t>
         </is>
       </c>
     </row>
@@ -2792,32 +3176,44 @@
       </c>
       <c r="G34" s="4" t="inlineStr">
         <is>
-          <t>Depth: Responsive to feedback; pairs willingly; asks for help appropriately. Evidenced by: Works in the open. Scope: task.</t>
+          <t>Depth: Responsive to feedback; pairs willingly; asks for help appropriately.
+Evidenced by: Works in the open.
+Scope: task.</t>
         </is>
       </c>
       <c r="H34" s="4" t="inlineStr">
         <is>
-          <t>Depth: Collaborates smoothly with adjacent functions; handles disagreement constructively. Evidenced by: Partners directly with the teams that consume their component. Scope: component.</t>
+          <t>Depth: Collaborates smoothly with adjacent functions; handles disagreement constructively.
+Evidenced by: Partners directly with the teams that consume their component.
+Scope: component.</t>
         </is>
       </c>
       <c r="I34" s="4" t="inlineStr">
         <is>
-          <t>Depth: Builds strong cross-team relationships; resolves friction directly. Evidenced by: Builds the working relationships a capability depends on. Scope: capability / domain (terminal level).</t>
+          <t>Depth: Builds strong cross-team relationships; resolves friction directly.
+Evidenced by: Builds the working relationships a capability depends on.
+Scope: capability / domain (terminal level).</t>
         </is>
       </c>
       <c r="J34" s="4" t="inlineStr">
         <is>
-          <t>Depth: Expert at aligning teams with competing priorities; mediates disputes between senior people. Evidenced by: Creates the collaboration structures that let teams decide without escalation. Scope: multiple teams.</t>
+          <t>Depth: Expert at aligning teams with competing priorities; mediates disputes between senior people.
+Evidenced by: Creates the collaboration structures that let teams decide without escalation.
+Scope: multiple teams.</t>
         </is>
       </c>
       <c r="K34" s="4" t="inlineStr">
         <is>
-          <t>Depth: Creates the forums and processes through which collaboration happens. Evidenced by: Brokers alignment between organizations. Scope: organization.</t>
+          <t>Depth: Creates the forums and processes through which collaboration happens.
+Evidenced by: Brokers alignment between organizations.
+Scope: organization.</t>
         </is>
       </c>
       <c r="L34" s="4" t="inlineStr">
         <is>
-          <t>Depth: Builds coalitions at company scale and externally. Evidenced by: Aligns the company's technical factions. Scope: company.</t>
+          <t>Depth: Builds coalitions at company scale and externally.
+Evidenced by: Aligns the company's technical factions.
+Scope: company.</t>
         </is>
       </c>
     </row>
@@ -2854,32 +3250,44 @@
       </c>
       <c r="G35" s="4" t="inlineStr">
         <is>
-          <t>Depth: Learns to estimate; surfaces blockers; plans own tasks with guidance. Evidenced by: Breaks an assigned task into steps, estimates them honestly, and flags slippage as soon as it is visible. Scope: task.</t>
+          <t>Depth: Learns to estimate; surfaces blockers; plans own tasks with guidance.
+Evidenced by: Breaks an assigned task into steps, estimates them honestly, and flags slippage as soon as it is visible.
+Scope: task.</t>
         </is>
       </c>
       <c r="H35" s="4" t="inlineStr">
         <is>
-          <t>Depth: Estimates scoped work realistically; plans own 1-3 week projects. Evidenced by: Plans component-level work in increments that ship value early. Scope: component.</t>
+          <t>Depth: Estimates scoped work realistically; plans own 1-3 week projects.
+Evidenced by: Plans component-level work in increments that ship value early.
+Scope: component.</t>
         </is>
       </c>
       <c r="I35" s="4" t="inlineStr">
         <is>
-          <t>Depth: Plans quarter-scale, multi-workstream efforts including dependencies. Evidenced by: Plans a capability across quarters with explicit risk buffers. Scope: capability / domain (terminal level).</t>
+          <t>Depth: Plans quarter-scale, multi-workstream efforts including dependencies.
+Evidenced by: Plans a capability across quarters with explicit risk buffers.
+Scope: capability / domain (terminal level).</t>
         </is>
       </c>
       <c r="J35" s="4" t="inlineStr">
         <is>
-          <t>Depth: Expert at planning large programs; anticipates risk early. Evidenced by: Builds plans that coordinate multiple teams' streams. Scope: multiple teams.</t>
+          <t>Depth: Expert at planning large programs; anticipates risk early.
+Evidenced by: Builds plans that coordinate multiple teams' streams.
+Scope: multiple teams.</t>
         </is>
       </c>
       <c r="K35" s="4" t="inlineStr">
         <is>
-          <t>Depth: Plans org-level programs across quarters/years. Evidenced by: Runs the organization's platform planning cycle. Scope: organization.</t>
+          <t>Depth: Plans org-level programs across quarters/years.
+Evidenced by: Runs the organization's platform planning cycle.
+Scope: organization.</t>
         </is>
       </c>
       <c r="L35" s="4" t="inlineStr">
         <is>
-          <t>Depth: Shapes how the company plans major technical change. Evidenced by: Sets the multi-year planning cycle major technical bets are sequenced against, and defends the sequencing to the executives funding it. Scope: company.</t>
+          <t>Depth: Shapes how the company plans major technical change.
+Evidenced by: Sets the multi-year planning cycle major technical bets are sequenced against, and defends the sequencing to the executives funding it.
+Scope: company.</t>
         </is>
       </c>
     </row>
@@ -2916,32 +3324,44 @@
       </c>
       <c r="G36" s="4" t="inlineStr">
         <is>
-          <t>Depth: Works highest-priority-first when told the priorities. Evidenced by: Works their queue in the agreed order and raises it explicitly when a new ask conflicts with committed work. Scope: task.</t>
+          <t>Depth: Works highest-priority-first when told the priorities.
+Evidenced by: Works their queue in the agreed order and raises it explicitly when a new ask conflicts with committed work.
+Scope: task.</t>
         </is>
       </c>
       <c r="H36" s="4" t="inlineStr">
         <is>
-          <t>Depth: Makes sound priority calls within scope; time-boxes uncertain work. Evidenced by: Orders their component's backlog by user impact and cost of delay. Scope: component.</t>
+          <t>Depth: Makes sound priority calls within scope; time-boxes uncertain work.
+Evidenced by: Orders their component's backlog by user impact and cost of delay.
+Scope: component.</t>
         </is>
       </c>
       <c r="I36" s="4" t="inlineStr">
         <is>
-          <t>Depth: Balances cost/value/risk across a domain; resists hype; decisions hold up over months. Evidenced by: Sequences a capability's investment across feature work, reliability, migrations, and toil paydown using explicit cost-of-delay reasoning. Scope: capability / domain (terminal level).</t>
+          <t>Depth: Balances cost/value/risk across a domain; resists hype; decisions hold up over months.
+Evidenced by: Sequences a capability's investment across feature work, reliability, migrations, and toil paydown using explicit cost-of-delay reasoning.
+Scope: capability / domain (terminal level).</t>
         </is>
       </c>
       <c r="J36" s="4" t="inlineStr">
         <is>
-          <t>Depth: Expert at portfolio-level trade-offs; surfaces hidden assumptions; trusted tiebreaker. Evidenced by: Arbitrates priority across teams competing for shared platform capacity. Scope: multiple teams.</t>
+          <t>Depth: Expert at portfolio-level trade-offs; surfaces hidden assumptions; trusted tiebreaker.
+Evidenced by: Arbitrates priority across teams competing for shared platform capacity.
+Scope: multiple teams.</t>
         </is>
       </c>
       <c r="K36" s="4" t="inlineStr">
         <is>
-          <t>Depth: Sets decision frameworks for the org. Evidenced by: Sets the organization's platform investment allocation. Scope: organization.</t>
+          <t>Depth: Sets decision frameworks for the org.
+Evidenced by: Sets the organization's platform investment allocation.
+Scope: organization.</t>
         </is>
       </c>
       <c r="L36" s="4" t="inlineStr">
         <is>
-          <t>Depth: Influences company strategic direction through judgment. Evidenced by: Advises company leadership on technology sequencing. Scope: company.</t>
+          <t>Depth: Influences company strategic direction through judgment.
+Evidenced by: Advises company leadership on technology sequencing.
+Scope: company.</t>
         </is>
       </c>
     </row>
@@ -2978,32 +3398,44 @@
       </c>
       <c r="G37" s="4" t="inlineStr">
         <is>
-          <t>Depth: Receptive to mentoring; shares what they learn. Evidenced by: Asks for help effectively - showing what they tried - and passes on what they learn. Scope: task.</t>
+          <t>Depth: Receptive to mentoring; shares what they learn.
+Evidenced by: Asks for help effectively - showing what they tried - and passes on what they learn.
+Scope: task.</t>
         </is>
       </c>
       <c r="H37" s="4" t="inlineStr">
         <is>
-          <t>Depth: Helps onboard teammates; informally mentors juniors. Evidenced by: Onboards new teammates with pairing and honest context. Scope: component.</t>
+          <t>Depth: Helps onboard teammates; informally mentors juniors.
+Evidenced by: Onboards new teammates with pairing and honest context.
+Scope: component.</t>
         </is>
       </c>
       <c r="I37" s="4" t="inlineStr">
         <is>
-          <t>Depth: Coaches engineers with growth-oriented feedback; measurably improves a team's skill. Evidenced by: Mentors engineers deliberately. Scope: capability / domain (terminal level).</t>
+          <t>Depth: Coaches engineers with growth-oriented feedback; measurably improves a team's skill.
+Evidenced by: Mentors engineers deliberately.
+Scope: capability / domain (terminal level).</t>
         </is>
       </c>
       <c r="J37" s="4" t="inlineStr">
         <is>
-          <t>Depth: Develops future leads across teams; shapes hiring and onboarding. Evidenced by: Grows senior engineers across teams toward staff scope. Scope: multiple teams.</t>
+          <t>Depth: Develops future leads across teams; shapes hiring and onboarding.
+Evidenced by: Grows senior engineers across teams toward staff scope.
+Scope: multiple teams.</t>
         </is>
       </c>
       <c r="K37" s="4" t="inlineStr">
         <is>
-          <t>Depth: Develops senior engineers and leaders; builds culture deliberately. Evidenced by: Builds the organization's technical talent systems. Scope: organization.</t>
+          <t>Depth: Develops senior engineers and leaders; builds culture deliberately.
+Evidenced by: Builds the organization's technical talent systems.
+Scope: organization.</t>
         </is>
       </c>
       <c r="L37" s="4" t="inlineStr">
         <is>
-          <t>Depth: Develops the next generation of top talent; legacy outlasts tenure. Evidenced by: Develops the company's next generation of principal-level technical leaders. Scope: company.</t>
+          <t>Depth: Develops the next generation of top talent; legacy outlasts tenure.
+Evidenced by: Develops the company's next generation of principal-level technical leaders.
+Scope: company.</t>
         </is>
       </c>
     </row>
@@ -3040,32 +3472,44 @@
       </c>
       <c r="G38" s="4" t="inlineStr">
         <is>
-          <t>Depth: Contributes informed opinions in technical discussions. Evidenced by: Raises a concrete thundering-herd failure scenario against a proposed retry strategy in a design review, and the design changes because of it. Scope: task.</t>
+          <t>Depth: Contributes informed opinions in technical discussions.
+Evidenced by: Raises a concrete thundering-herd failure scenario against a proposed retry strategy in a design review, and the design changes because of it.
+Scope: task.</t>
         </is>
       </c>
       <c r="H38" s="4" t="inlineStr">
         <is>
-          <t>Depth: Influences component-level decisions through credibility. Evidenced by: Proposes direction within their component. Scope: component.</t>
+          <t>Depth: Influences component-level decisions through credibility.
+Evidenced by: Proposes direction within their component.
+Scope: component.</t>
         </is>
       </c>
       <c r="I38" s="4" t="inlineStr">
         <is>
-          <t>Depth: Sets technical direction for a domain; others align to their calls. Evidenced by: Picks the message-queue technology a capability standardizes on for its next migration cycle, and engineers building on it align their designs to that call without relitigating it. Scope: capability / domain (terminal level).</t>
+          <t>Depth: Sets technical direction for a domain; others align to their calls.
+Evidenced by: Picks the message-queue technology a capability standardizes on for its next migration cycle, and engineers building on it align their designs to that call without relitigating it.
+Scope: capability / domain (terminal level).</t>
         </is>
       </c>
       <c r="J38" s="4" t="inlineStr">
         <is>
-          <t>Depth: Shapes how multiple teams approach problems; trusted tiebreaker. Evidenced by: Aligns multiple teams behind a shared technical direction without authority over them. Scope: multiple teams.</t>
+          <t>Depth: Shapes how multiple teams approach problems; trusted tiebreaker.
+Evidenced by: Aligns multiple teams behind a shared technical direction without authority over them.
+Scope: multiple teams.</t>
         </is>
       </c>
       <c r="K38" s="4" t="inlineStr">
         <is>
-          <t>Depth: Influences org-wide technical strategy. Evidenced by: Writes the organization's technical strategy and makes it operational. Scope: organization.</t>
+          <t>Depth: Influences org-wide technical strategy.
+Evidenced by: Writes the organization's technical strategy and makes it operational.
+Scope: organization.</t>
         </is>
       </c>
       <c r="L38" s="4" t="inlineStr">
         <is>
-          <t>Depth: Influences company strategic direction through insight. Evidenced by: Sets company-level technical direction. Scope: company.</t>
+          <t>Depth: Influences company strategic direction through insight.
+Evidenced by: Sets company-level technical direction.
+Scope: company.</t>
         </is>
       </c>
     </row>

--- a/roles/platform-engineering/ladder.xlsx
+++ b/roles/platform-engineering/ladder.xlsx
@@ -809,43 +809,37 @@
       <c r="G2" s="4" t="inlineStr">
         <is>
           <t>Depth: Runs scripted customer interviews and notes findings under a senior researcher's guidance.
-Evidenced by: Shadows platform users and sits in on interviews and support rotations, writing up the friction they hit.
-Scope: task.</t>
+Evidenced by: Shadows platform users and sits in on interviews and support rotations, writing up the friction they hit.</t>
         </is>
       </c>
       <c r="H2" s="4" t="inlineStr">
         <is>
           <t>Depth: Plans and conducts standard discovery for a feature, synthesizing themes with normal review.
-Evidenced by: Runs structured interviews and support-channel reviews with the internal engineers using their component.
-Scope: component.</t>
+Evidenced by: Runs structured interviews and support-channel reviews with the internal engineers using their component.</t>
         </is>
       </c>
       <c r="I2" s="4" t="inlineStr">
         <is>
           <t>Depth: Independently frames ambiguous problems, selects fitting methods, and separates signal from noise.
-Evidenced by: Designs and runs the discovery process for a capability.
-Scope: capability / domain (terminal level).</t>
+Evidenced by: Designs and runs the discovery process for a capability.</t>
         </is>
       </c>
       <c r="J2" s="4" t="inlineStr">
         <is>
           <t>Depth: Designs the team's discovery approach and untangles findings others find contradictory.
-Evidenced by: Synthesizes research across several product teams into shared personas and friction maps other platform teams adopt.
-Scope: multiple teams.</t>
+Evidenced by: Synthesizes research across several product teams into shared personas and friction maps other platform teams adopt.</t>
         </is>
       </c>
       <c r="K2" s="4" t="inlineStr">
         <is>
           <t>Depth: Sets the org's research strategy and anticipates emerging customer needs before they surface.
-Evidenced by: Establishes the organization's standing platform research practice.
-Scope: organization.</t>
+Evidenced by: Establishes the organization's standing platform research practice.</t>
         </is>
       </c>
       <c r="L2" s="4" t="inlineStr">
         <is>
           <t>Depth: Defines what rigorous product discovery means and shapes the discipline's practice externally.
-Evidenced by: Represents the internal developer experience at company level.
-Scope: company.</t>
+Evidenced by: Represents the internal developer experience at company level.</t>
         </is>
       </c>
     </row>
@@ -883,43 +877,37 @@
       <c r="G3" s="4" t="inlineStr">
         <is>
           <t>Depth: Pulls and reports defined product metrics under direction.
-Evidenced by: Pulls and charts existing adoption and usage numbers accurately when asked.
-Scope: task.</t>
+Evidenced by: Pulls and charts existing adoption and usage numbers accurately when asked.</t>
         </is>
       </c>
       <c r="H3" s="4" t="inlineStr">
         <is>
           <t>Depth: Builds and interprets metric dashboards for a product with normal review.
-Evidenced by: Instruments their component with adoption, retention, and satisfaction signals.
-Scope: component.</t>
+Evidenced by: Instruments their component with adoption, retention, and satisfaction signals.</t>
         </is>
       </c>
       <c r="I3" s="4" t="inlineStr">
         <is>
           <t>Depth: Independently designs metric frameworks and draws sound conclusions from messy data.
-Evidenced by: Defines the success metrics for a capability.
-Scope: capability / domain (terminal level).</t>
+Evidenced by: Defines the success metrics for a capability.</t>
         </is>
       </c>
       <c r="J3" s="4" t="inlineStr">
         <is>
           <t>Depth: Defines the measurement model teams adopt and diagnoses misleading metrics others trust.
-Evidenced by: Standardizes how several platform teams measure adoption so their numbers compose.
-Scope: multiple teams.</t>
+Evidenced by: Standardizes how several platform teams measure adoption so their numbers compose.</t>
         </is>
       </c>
       <c r="K3" s="4" t="inlineStr">
         <is>
           <t>Depth: Sets product-analytics strategy across the org and anticipates which signals will matter.
-Evidenced by: Owns the organization's platform scorecard.
-Scope: organization.</t>
+Evidenced by: Owns the organization's platform scorecard.</t>
         </is>
       </c>
       <c r="L3" s="4" t="inlineStr">
         <is>
           <t>Depth: Defines rigorous product measurement for the discipline and is cited externally on it.
-Evidenced by: Frames platform value in company terms.
-Scope: company.</t>
+Evidenced by: Frames platform value in company terms.</t>
         </is>
       </c>
     </row>
@@ -957,43 +945,37 @@
       <c r="G4" s="4" t="inlineStr">
         <is>
           <t>Depth: Checks for an existing tool, service, or open-source option before writing new code and raises what they find; asks whether a proposed task serves a real user need.
-Evidenced by: Finds that an existing internal CLI already covers most of a proposed new tool's use case and raises it in planning instead of starting a new build.
-Scope: task.</t>
+Evidenced by: Finds that an existing internal CLI already covers most of a proposed new tool's use case and raises it in planning instead of starting a new build.</t>
         </is>
       </c>
       <c r="H4" s="4" t="inlineStr">
         <is>
           <t>Depth: Proposes wrapping or configuring an existing service instead of building new when it meets the need, writing the comparison down and defending removal of unused features in their own component.
-Evidenced by: Recommends adopting the org's existing secrets-manager service instead of building a bespoke wrapper for their component, and writes up the build-vs-adopt comparison that settles it.
-Scope: component.</t>
+Evidenced by: Recommends adopting the org's existing secrets-manager service instead of building a bespoke wrapper for their component, and writes up the build-vs-adopt comparison that settles it.</t>
         </is>
       </c>
       <c r="I4" s="4" t="inlineStr">
         <is>
           <t>Depth: Keeps a whole capability at its thinnest viable size - makes explicit, documented build-buy-adopt decisions, ships the thinnest version that serves proven demand, and retires surface area whose maintenance cost exceeds its value.
-Evidenced by: Retires half a capability's plugin surface after usage telemetry shows only two of eight plugins are load-bearing, documenting the build-buy-adopt call for what stays.
-Scope: capability / domain (terminal level).</t>
+Evidenced by: Retires half a capability's plugin surface after usage telemetry shows only two of eight plugins are load-bearing, documenting the build-buy-adopt call for what stays.</t>
         </is>
       </c>
       <c r="J4" s="4" t="inlineStr">
         <is>
           <t>Depth: Arbitrates overlap and sprawl across teams - merges duplicate offerings, cuts under-used surface, and sets the bar for what deserves to be shared platform at all.
-Evidenced by: Merges two platform teams' overlapping feature-flag services into one and retires the duplicate.
-Scope: multiple teams.</t>
+Evidenced by: Merges two platform teams' overlapping feature-flag services into one and retires the duplicate.</t>
         </is>
       </c>
       <c r="K4" s="4" t="inlineStr">
         <is>
           <t>Depth: Shapes the organization's platform boundary - what the platform owns versus product teams versus vendors - and drives the organization to shed what it should not own.
-Evidenced by: Draws the line for what the platform organization owns versus what product teams should just buy, and gets teams to hand back components that crossed it.
-Scope: organization.</t>
+Evidenced by: Draws the line for what the platform organization owns versus what product teams should just buy, and gets teams to hand back components that crossed it.</t>
         </is>
       </c>
       <c r="L4" s="4" t="inlineStr">
         <is>
           <t>Depth: Sets the build-buy-adopt principles an entire company references, keeping company-scale platform investment proportional to the delivery it unlocks.
-Evidenced by: Kills a company-wide platform initiative whose maintenance cost has outgrown the delivery it unlocks, over objections that the build already happened.
-Scope: company.</t>
+Evidenced by: Kills a company-wide platform initiative whose maintenance cost has outgrown the delivery it unlocks, over objections that the build already happened.</t>
         </is>
       </c>
     </row>
@@ -1031,43 +1013,37 @@
       <c r="G5" s="4" t="inlineStr">
         <is>
           <t>Depth: Maintains roadmap items and updates status under guidance.
-Evidenced by: Explains why their current task is on the roadmap.
-Scope: task.</t>
+Evidenced by: Explains why their current task is on the roadmap.</t>
         </is>
       </c>
       <c r="H5" s="4" t="inlineStr">
         <is>
           <t>Depth: Builds and sequences a credible roadmap for one product with normal review.
-Evidenced by: Sequences their component's backlog by user impact.
-Scope: component.</t>
+Evidenced by: Sequences their component's backlog by user impact.</t>
         </is>
       </c>
       <c r="I5" s="4" t="inlineStr">
         <is>
           <t>Depth: Independently balances competing priorities and replans confidently under shifting constraints.
-Evidenced by: Owns the roadmap for a platform capability.
-Scope: capability / domain (terminal level).</t>
+Evidenced by: Owns the roadmap for a platform capability.</t>
         </is>
       </c>
       <c r="J5" s="4" t="inlineStr">
         <is>
           <t>Depth: Designs the planning approach others use and resolves cross-team portfolio conflicts.
-Evidenced by: Aligns roadmaps across platform teams.
-Scope: multiple teams.</t>
+Evidenced by: Aligns roadmaps across platform teams.</t>
         </is>
       </c>
       <c r="K5" s="4" t="inlineStr">
         <is>
           <t>Depth: Sets portfolio planning strategy and foresees where investment should shift next.
-Evidenced by: Drives the platform organization's investment strategy.
-Scope: organization.</t>
+Evidenced by: Drives the platform organization's investment strategy.</t>
         </is>
       </c>
       <c r="L5" s="4" t="inlineStr">
         <is>
           <t>Depth: Defines portfolio-planning best practice for the field and is recognized for it.
-Evidenced by: Sets multi-year platform direction for the company.
-Scope: company.</t>
+Evidenced by: Sets multi-year platform direction for the company.</t>
         </is>
       </c>
     </row>
@@ -1105,43 +1081,37 @@
       <c r="G6" s="4" t="inlineStr">
         <is>
           <t>Depth: Maintains existing self-service platform components under review, addressing documented user requests.
-Evidenced by: Follows the golden path as a real user would and reports exactly where it breaks.
-Scope: task.</t>
+Evidenced by: Follows the golden path as a real user would and reports exactly where it breaks.</t>
         </is>
       </c>
       <c r="H6" s="4" t="inlineStr">
         <is>
           <t>Depth: Independently builds and supports standard platform capabilities and templates for routine developer needs with review.
-Evidenced by: Builds and maintains golden-path assets for their component.
-Scope: component.</t>
+Evidenced by: Builds and maintains golden-path assets for their component.</t>
         </is>
       </c>
       <c r="I6" s="4" t="inlineStr">
         <is>
           <t>Depth: Designs self-service workflows for ambiguous needs, reducing friction and resolving hard abstraction and adoption issues.
-Evidenced by: Designs a golden path for a whole use case end to end.
-Scope: capability / domain (terminal level).</t>
+Evidenced by: Designs a golden path for a whole use case end to end.</t>
         </is>
       </c>
       <c r="J6" s="4" t="inlineStr">
         <is>
           <t>Depth: Defines platform architecture and golden paths others adopt, solving deep developer-experience and leverage problems.
-Evidenced by: Reconciles golden paths across teams into coherent journeys.
-Scope: multiple teams.</t>
+Evidenced by: Reconciles golden paths across teams into coherent journeys.</t>
         </is>
       </c>
       <c r="K6" s="4" t="inlineStr">
         <is>
           <t>Depth: Sets organization-wide platform strategy, anticipating how developer-experience engineering should evolve.
-Evidenced by: Defines the organization's paved-road strategy.
-Scope: organization.</t>
+Evidenced by: Defines the organization's paved-road strategy.</t>
         </is>
       </c>
       <c r="L6" s="4" t="inlineStr">
         <is>
           <t>Depth: Defines what excellent platform engineering means for the field, shaping industry developer-experience practice.
-Evidenced by: Makes the paved road the company default by economics and quality, not policy.
-Scope: company.</t>
+Evidenced by: Makes the paved road the company default by economics and quality, not policy.</t>
         </is>
       </c>
     </row>
@@ -1179,43 +1149,37 @@
       <c r="G7" s="4" t="inlineStr">
         <is>
           <t>Depth: Names the exact docs, errors, and setup steps that forced them to understand internals a consumer should not need, and files concrete simplification issues.
-Evidenced by: Flags that provisioning a database requires reading the underlying Terraform module's internals just to fill in one required field, and files the doc fix.
-Scope: task.</t>
+Evidenced by: Flags that provisioning a database requires reading the underlying Terraform module's internals just to fill in one required field, and files the doc fix.</t>
         </is>
       </c>
       <c r="H7" s="4" t="inlineStr">
         <is>
           <t>Depth: Reduces the concepts and steps a consumer must hold to use their component - collapsing configuration, defaulting decisions, rewriting errors to say what to do next - and shows the before/after.
-Evidenced by: Collapses a twelve-field service-creation form down to two required fields by defaulting the rest, and shows the before/after time-to-first-deploy.
-Scope: component.</t>
+Evidenced by: Collapses a twelve-field service-creation form down to two required fields by defaulting the rest, and shows the before/after time-to-first-deploy.</t>
         </is>
       </c>
       <c r="I7" s="4" t="inlineStr">
         <is>
           <t>Depth: Designs a capability's abstractions around what consumers must not have to know, so a first-time user succeeds without reading internals; measures load with time-to-first-success and support-ticket themes and treats regressions as defects.
-Evidenced by: Rewrites a capability's onboarding so a first-time consumer ships without reading the implementation, tracking time-to-first-success as the load metric.
-Scope: capability / domain (terminal level).</t>
+Evidenced by: Rewrites a capability's onboarding so a first-time consumer ships without reading the implementation, tracking time-to-first-success as the load metric.</t>
         </is>
       </c>
       <c r="J7" s="4" t="inlineStr">
         <is>
           <t>Depth: Audits cognitive load across team boundaries - quantifying onboarding time, concepts-to-learn, and ticket themes - and drives the cross-boundary simplifications no single team could make.
-Evidenced by: Finds three teams independently solved the same secrets-rotation problem because none could see the others' internals, and drives the shared fix across all three.
-Scope: multiple teams.</t>
+Evidenced by: Finds three teams independently solved the same secrets-rotation problem because none could see the others' internals, and drives the shared fix across all three.</t>
         </is>
       </c>
       <c r="K7" s="4" t="inlineStr">
         <is>
           <t>Depth: Makes cognitive load a first-class organizational measure with explicit load budgets, vetoing designs that externalize complexity onto consuming teams.
-Evidenced by: Sets an explicit cognitive-load budget per platform surface and vetoes a design that would have pushed new required concepts onto every consuming team.
-Scope: organization.</t>
+Evidenced by: Sets an explicit cognitive-load budget per platform surface and vetoes a design that would have pushed new required concepts onto every consuming team.</t>
         </is>
       </c>
       <c r="L7" s="4" t="inlineStr">
         <is>
           <t>Depth: Shapes company-level technology and team-boundary choices explicitly around team cognitive load, arguing for fewer, deeper abstractions over sprawling optionality.
-Evidenced by: Argues successfully against a company-wide multi-cloud push on cognitive-load grounds -- fewer, deeper abstractions over optionality -- and the simpler single-cloud default ships instead.
-Scope: company.</t>
+Evidenced by: Argues successfully against a company-wide multi-cloud push on cognitive-load grounds -- fewer, deeper abstractions over optionality -- and the simpler single-cloud default ships instead.</t>
         </is>
       </c>
     </row>
@@ -1253,43 +1217,37 @@
       <c r="G8" s="4" t="inlineStr">
         <is>
           <t>Depth: Implements designs specified by others; asks why, not just how.
-Evidenced by: Explains the platform's architecture in their own words.
-Scope: task.</t>
+Evidenced by: Explains the platform's architecture in their own words.</t>
         </is>
       </c>
       <c r="H8" s="4" t="inlineStr">
         <is>
           <t>Depth: Designs sound components; understands coupling, cohesion, interface design.
-Evidenced by: Designs a component within an established architecture.
-Scope: component.</t>
+Evidenced by: Designs a component within an established architecture.</t>
         </is>
       </c>
       <c r="I8" s="4" t="inlineStr">
         <is>
           <t>Depth: Designs systems for evolution: clean seams, versioned interfaces, replaceable parts.
-Evidenced by: Selects patterns by trade-off in design docs that name alternatives, failure modes, and evolution paths.
-Scope: capability / domain (terminal level).</t>
+Evidenced by: Selects patterns by trade-off in design docs that name alternatives, failure modes, and evolution paths.</t>
         </is>
       </c>
       <c r="J8" s="4" t="inlineStr">
         <is>
           <t>Depth: Mastery of architecture for complex systems; sets patterns and prevents drift.
-Evidenced by: Drives designs that cut across several teams' systems.
-Scope: multiple teams.</t>
+Evidenced by: Drives designs that cut across several teams' systems.</t>
         </is>
       </c>
       <c r="K8" s="4" t="inlineStr">
         <is>
           <t>Depth: Sets multi-year architecture direction across the org.
-Evidenced by: Sets the architectural direction the platform organization builds against.
-Scope: organization.</t>
+Evidenced by: Sets the architectural direction the platform organization builds against.</t>
         </is>
       </c>
       <c r="L8" s="4" t="inlineStr">
         <is>
           <t>Depth: Authoritative and externally credible; defines architectural approach others follow.
-Evidenced by: Makes the company's foundational architecture bets.
-Scope: company.</t>
+Evidenced by: Makes the company's foundational architecture bets.</t>
         </is>
       </c>
     </row>
@@ -1327,43 +1285,37 @@
       <c r="G9" s="4" t="inlineStr">
         <is>
           <t>Depth: Understands HTTP/REST and the deploy pipeline; makes guided changes.
-Evidenced by: Uses the platform's APIs correctly from documentation alone.
-Scope: task.</t>
+Evidenced by: Uses the platform's APIs correctly from documentation alone.</t>
         </is>
       </c>
       <c r="H9" s="4" t="inlineStr">
         <is>
           <t>Depth: Designs clean APIs; understands rate limits, retries, timeouts, idempotency.
-Evidenced by: Extends a component's interface without breaking consumers.
-Scope: component.</t>
+Evidenced by: Extends a component's interface without breaking consumers.</t>
         </is>
       </c>
       <c r="I9" s="4" t="inlineStr">
         <is>
           <t>Depth: Designs services for scale and cost; understands distributed failure modes.
-Evidenced by: Designs a capability's interface as a long-lived product contract.
-Scope: capability / domain (terminal level).</t>
+Evidenced by: Designs a capability's interface as a long-lived product contract.</t>
         </is>
       </c>
       <c r="J9" s="4" t="inlineStr">
         <is>
           <t>Depth: Expert in platform/service design (multi-tenancy, capacity, shared services).
-Evidenced by: Aligns interface conventions across several teams' APIs so the platform feels like one product.
-Scope: multiple teams.</t>
+Evidenced by: Aligns interface conventions across several teams' APIs so the platform feels like one product.</t>
         </is>
       </c>
       <c r="K9" s="4" t="inlineStr">
         <is>
           <t>Depth: Sets interface standards used across the org.
-Evidenced by: Owns the organization's interface standards.
-Scope: organization.</t>
+Evidenced by: Owns the organization's interface standards.</t>
         </is>
       </c>
       <c r="L9" s="4" t="inlineStr">
         <is>
           <t>Depth: Defines company-wide API approach; trusted with irreversible interface bets.
-Evidenced by: Sets the company's contract with its developers.
-Scope: company.</t>
+Evidenced by: Sets the company's contract with its developers.</t>
         </is>
       </c>
     </row>
@@ -1401,43 +1353,37 @@
       <c r="G10" s="4" t="inlineStr">
         <is>
           <t>Depth: Writes functional, readable code; uses version control correctly; responds well to review.
-Evidenced by: Ships small, working changes that follow the codebase's conventions and pass review with minor feedback.
-Scope: task.</t>
+Evidenced by: Ships small, working changes that follow the codebase's conventions and pass review with minor feedback.</t>
         </is>
       </c>
       <c r="H10" s="4" t="inlineStr">
         <is>
           <t>Depth: Writes clean, documented, modular code; gives useful review feedback.
-Evidenced by: Ships production-quality code independently.
-Scope: component.</t>
+Evidenced by: Ships production-quality code independently.</t>
         </is>
       </c>
       <c r="I10" s="4" t="inlineStr">
         <is>
           <t>Depth: Designs for maintainability; leads refactors of problem areas; review feedback teaches.
-Evidenced by: Writes the code others study to learn how it is done here.
-Scope: capability / domain (terminal level).</t>
+Evidenced by: Writes the code others study to learn how it is done here.</t>
         </is>
       </c>
       <c r="J10" s="4" t="inlineStr">
         <is>
           <t>Depth: Expert in code health at scale (shared libraries, deprecations, large migrations).
-Evidenced by: Raises the code-health baseline across teams.
-Scope: multiple teams.</t>
+Evidenced by: Raises the code-health baseline across teams.</t>
         </is>
       </c>
       <c r="K10" s="4" t="inlineStr">
         <is>
           <t>Depth: Shapes org-wide engineering standards for long-lived codebases.
-Evidenced by: Defines what code quality means for the organization.
-Scope: organization.</t>
+Evidenced by: Defines what code quality means for the organization.</t>
         </is>
       </c>
       <c r="L10" s="4" t="inlineStr">
         <is>
           <t>Depth: Defines what good engineering looks like company-wide; externally recognized.
-Evidenced by: Holds the company's long-horizon code health against short-term pressure.
-Scope: company.</t>
+Evidenced by: Holds the company's long-horizon code health against short-term pressure.</t>
         </is>
       </c>
     </row>
@@ -1475,43 +1421,37 @@
       <c r="G11" s="4" t="inlineStr">
         <is>
           <t>Depth: Navigates the codebase and understands code shown; reviews small changes.
-Evidenced by: Reviews peers' changes for readability and test coverage and asks genuine questions.
-Scope: task.</t>
+Evidenced by: Reviews peers' changes for readability and test coverage and asks genuine questions.</t>
         </is>
       </c>
       <c r="H11" s="4" t="inlineStr">
         <is>
           <t>Depth: Independently understands unfamiliar code; gives timely, specific review feedback.
-Evidenced by: Gives reviews that catch real defects.
-Scope: component.</t>
+Evidenced by: Gives reviews that catch real defects.</t>
         </is>
       </c>
       <c r="I11" s="4" t="inlineStr">
         <is>
           <t>Depth: Quickly grasps complex/legacy systems; reviews raise the bar across a domain.
-Evidenced by: Reviews for systemic risk, not just correctness.
-Scope: capability / domain (terminal level).</t>
+Evidenced by: Reviews for systemic risk, not just correctness.</t>
         </is>
       </c>
       <c r="J11" s="4" t="inlineStr">
         <is>
           <t>Depth: Expert at reviewing high-risk changes; review standards spread across teams.
-Evidenced by: Calibrates review culture across teams.
-Scope: multiple teams.</t>
+Evidenced by: Calibrates review culture across teams.</t>
         </is>
       </c>
       <c r="K11" s="4" t="inlineStr">
         <is>
           <t>Depth: Authority on review practice org-wide.
-Evidenced by: Designs the organization's quality gates.
-Scope: organization.</t>
+Evidenced by: Designs the organization's quality gates.</t>
         </is>
       </c>
       <c r="L11" s="4" t="inlineStr">
         <is>
           <t>Depth: Defines what good review looks like; shapes industry-facing practice.
-Evidenced by: Reviews the changes that change the company.
-Scope: company.</t>
+Evidenced by: Reviews the changes that change the company.</t>
         </is>
       </c>
     </row>
@@ -1549,43 +1489,37 @@
       <c r="G12" s="4" t="inlineStr">
         <is>
           <t>Depth: Writes unit tests with guidance; tests own changes before merging.
-Evidenced by: Writes unit tests that pin the behavior of their change, including the failure path.
-Scope: task.</t>
+Evidenced by: Writes unit tests that pin the behavior of their change, including the failure path.</t>
         </is>
       </c>
       <c r="H12" s="4" t="inlineStr">
         <is>
           <t>Depth: Applies the testing pyramid; everything shipped arrives tested; mocks dependencies sensibly.
-Evidenced by: Balances unit, integration, and end-to-end coverage for their component.
-Scope: component.</t>
+Evidenced by: Balances unit, integration, and end-to-end coverage for their component.</t>
         </is>
       </c>
       <c r="I12" s="4" t="inlineStr">
         <is>
           <t>Depth: Designs testable systems (contract, property-based, replay from prod); owns a test strategy.
-Evidenced by: Designs the verification strategy for a capability.
-Scope: capability / domain (terminal level).</t>
+Evidenced by: Designs the verification strategy for a capability.</t>
         </is>
       </c>
       <c r="J12" s="4" t="inlineStr">
         <is>
           <t>Depth: Expert in test strategy at scale (test data, environments, deployment safety).
-Evidenced by: Builds test infrastructure several teams rely on.
-Scope: multiple teams.</t>
+Evidenced by: Builds test infrastructure several teams rely on.</t>
         </is>
       </c>
       <c r="K12" s="4" t="inlineStr">
         <is>
           <t>Depth: Sets testing/verification discipline across the org.
-Evidenced by: Sets the organization's testing standards.
-Scope: organization.</t>
+Evidenced by: Sets the organization's testing standards.</t>
         </is>
       </c>
       <c r="L12" s="4" t="inlineStr">
         <is>
           <t>Depth: Shapes the company-wide quality culture; advances verification practice.
-Evidenced by: Frames verification as company risk management.
-Scope: company.</t>
+Evidenced by: Frames verification as company risk management.</t>
         </is>
       </c>
     </row>
@@ -1623,43 +1557,37 @@
       <c r="G13" s="4" t="inlineStr">
         <is>
           <t>Depth: Uses and makes guided fixes to existing pipelines.
-Evidenced by: Ships through the pipeline correctly.
-Scope: task.</t>
+Evidenced by: Ships through the pipeline correctly.</t>
         </is>
       </c>
       <c r="H13" s="4" t="inlineStr">
         <is>
           <t>Depth: Independently builds and improves pipelines for their area.
-Evidenced by: Owns their component's pipeline.
-Scope: component.</t>
+Evidenced by: Owns their component's pipeline.</t>
         </is>
       </c>
       <c r="I13" s="4" t="inlineStr">
         <is>
           <t>Depth: Designs deployment safety (progressive delivery, rollback) for a domain.
-Evidenced by: Designs CI/CD as a product for a capability's users.
-Scope: capability / domain (terminal level).</t>
+Evidenced by: Designs CI/CD as a product for a capability's users.</t>
         </is>
       </c>
       <c r="J13" s="4" t="inlineStr">
         <is>
           <t>Depth: Expert in delivery engineering at scale; sets standards across teams.
-Evidenced by: Builds delivery infrastructure multiple teams ship through.
-Scope: multiple teams.</t>
+Evidenced by: Builds delivery infrastructure multiple teams ship through.</t>
         </is>
       </c>
       <c r="K13" s="4" t="inlineStr">
         <is>
           <t>Depth: Defines the org's delivery/release philosophy.
-Evidenced by: Owns the organization's delivery architecture.
-Scope: organization.</t>
+Evidenced by: Owns the organization's delivery architecture.</t>
         </is>
       </c>
       <c r="L13" s="4" t="inlineStr">
         <is>
           <t>Depth: Advances release engineering practice company-wide.
-Evidenced by: Sets company delivery strategy.
-Scope: company.</t>
+Evidenced by: Sets company delivery strategy.</t>
         </is>
       </c>
     </row>
@@ -1697,43 +1625,37 @@
       <c r="G14" s="4" t="inlineStr">
         <is>
           <t>Depth: Follows the release process exactly — flags, staged rollout steps, verification checklists — verifies their change in production, and rolls back with guidance.
-Evidenced by: Executes migration and release steps from a runbook accurately.
-Scope: task.</t>
+Evidenced by: Executes migration and release steps from a runbook accurately.</t>
         </is>
       </c>
       <c r="H14" s="4" t="inlineStr">
         <is>
           <t>Depth: Ships behind flags with a rollback plan by default, monitors rollouts and reverts on their own judgment when signals degrade, and writes changes that tolerate both versions running during rollout.
-Evidenced by: Migrates their component's consumers off an old interface.
-Scope: component.</t>
+Evidenced by: Migrates their component's consumers off an old interface.</t>
         </is>
       </c>
       <c r="I14" s="4" t="inlineStr">
         <is>
           <t>Depth: Designs the rollout for risky changes — canary criteria, migration sequencing, flag lifecycle, kill switches — and reviews others' rollout plans for blast radius; the person teams ask how to ship something safely.
-Evidenced by: Plans and runs a capability-level deprecation as a managed migration.
-Scope: capability / domain (terminal level).</t>
+Evidenced by: Plans and runs a capability-level deprecation as a managed migration.</t>
         </is>
       </c>
       <c r="J14" s="4" t="inlineStr">
         <is>
           <t>Depth: Builds progressive-delivery machinery multiple teams release through (flag platforms, automated canary analysis, automated rollback), retiring deploy patterns that cause repeat incidents and measurably raising deploy frequency.
-Evidenced by: Coordinates migrations that cross team boundaries.
-Scope: multiple teams.</t>
+Evidenced by: Coordinates migrations that cross team boundaries.</t>
         </is>
       </c>
       <c r="K14" s="4" t="inlineStr">
         <is>
           <t>Depth: Owns release policy for an organization and its delivery metrics — rollout standards, freeze rules, environment strategy — dismantling ceremony that adds no safety.
-Evidenced by: Sets the organization's deprecation policy.
-Scope: organization.</t>
+Evidenced by: Sets the organization's deprecation policy.</t>
         </is>
       </c>
       <c r="L14" s="4" t="inlineStr">
         <is>
           <t>Depth: Sets how an entire company's software reaches customers — the risk posture products ship under — and defends it to executives, auditors, and regulators.
-Evidenced by: Sets the company's compatibility promise.
-Scope: company.</t>
+Evidenced by: Sets the company's compatibility promise.</t>
         </is>
       </c>
     </row>
@@ -1771,43 +1693,37 @@
       <c r="G15" s="4" t="inlineStr">
         <is>
           <t>Depth: Makes guided changes to existing infra; understands core cloud services.
-Evidenced by: Provisions and modifies cloud resources from documented patterns.
-Scope: task.</t>
+Evidenced by: Provisions and modifies cloud resources from documented patterns.</t>
         </is>
       </c>
       <c r="H15" s="4" t="inlineStr">
         <is>
           <t>Depth: Independently builds and manages standard resources using IaC.
-Evidenced by: Designs the cloud footprint for a component.
-Scope: component.</t>
+Evidenced by: Designs the cloud footprint for a component.</t>
         </is>
       </c>
       <c r="I15" s="4" t="inlineStr">
         <is>
           <t>Depth: Designs infra for scale, cost and resilience across a domain.
-Evidenced by: Architects a capability's infrastructure for the failure domains that matter.
-Scope: capability / domain (terminal level).</t>
+Evidenced by: Architects a capability's infrastructure for the failure domains that matter.</t>
         </is>
       </c>
       <c r="J15" s="4" t="inlineStr">
         <is>
           <t>Depth: Expert in infra platforms used by many teams; owns major cost strategy.
-Evidenced by: Designs shared infrastructure patterns.
-Scope: multiple teams.</t>
+Evidenced by: Designs shared infrastructure patterns.</t>
         </is>
       </c>
       <c r="K15" s="4" t="inlineStr">
         <is>
           <t>Depth: Sets org infrastructure direction.
-Evidenced by: Sets the organization's cloud strategy.
-Scope: organization.</t>
+Evidenced by: Sets the organization's cloud strategy.</t>
         </is>
       </c>
       <c r="L15" s="4" t="inlineStr">
         <is>
           <t>Depth: Trusted with company-level platform bets; defines infra strategy.
-Evidenced by: Owns company-level infrastructure bets.
-Scope: company.</t>
+Evidenced by: Owns company-level infrastructure bets.</t>
         </is>
       </c>
     </row>
@@ -1845,43 +1761,37 @@
       <c r="G16" s="4" t="inlineStr">
         <is>
           <t>Depth: Deploys workloads to an existing orchestrator under review, adjusting basic scheduling settings from examples.
-Evidenced by: Deploys and debugs workloads on the orchestrator with guidance.
-Scope: task.</t>
+Evidenced by: Deploys and debugs workloads on the orchestrator with guidance.</t>
         </is>
       </c>
       <c r="H16" s="4" t="inlineStr">
         <is>
           <t>Depth: Independently operates orchestrated workloads, manages routine scaling, placement, and health checks with normal review.
-Evidenced by: Owns their component's runtime configuration.
-Scope: component.</t>
+Evidenced by: Owns their component's runtime configuration.</t>
         </is>
       </c>
       <c r="I16" s="4" t="inlineStr">
         <is>
           <t>Depth: Designs scheduling, affinity, and resource policies for ambiguous workloads and resolves hard orchestration failures.
-Evidenced by: Designs and operates cluster-level platform machinery.
-Scope: capability / domain (terminal level).</t>
+Evidenced by: Designs and operates cluster-level platform machinery.</t>
         </is>
       </c>
       <c r="J16" s="4" t="inlineStr">
         <is>
           <t>Depth: Defines cluster topology and scheduling patterns others adopt, solving deep placement, contention, and lifecycle problems.
-Evidenced by: Sets workload standards multiple teams schedule against.
-Scope: multiple teams.</t>
+Evidenced by: Sets workload standards multiple teams schedule against.</t>
         </is>
       </c>
       <c r="K16" s="4" t="inlineStr">
         <is>
           <t>Depth: Sets organization-wide orchestration strategy and standards, anticipating where workload scheduling is heading.
-Evidenced by: Owns the organization's runtime strategy.
-Scope: organization.</t>
+Evidenced by: Owns the organization's runtime strategy.</t>
         </is>
       </c>
       <c r="L16" s="4" t="inlineStr">
         <is>
           <t>Depth: Defines what effective orchestration means for the discipline, externally credible in shaping scheduling practice.
-Evidenced by: Decides company-level runtime direction.
-Scope: company.</t>
+Evidenced by: Decides company-level runtime direction.</t>
         </is>
       </c>
     </row>
@@ -1919,43 +1829,37 @@
       <c r="G17" s="4" t="inlineStr">
         <is>
           <t>Depth: Configures basic network segments and routes from designs under review, verifying connectivity.
-Evidenced by: Traces a request through DNS, load balancer, and service to locate a failure.
-Scope: task.</t>
+Evidenced by: Traces a request through DNS, load balancer, and service to locate a failure.</t>
         </is>
       </c>
       <c r="H17" s="4" t="inlineStr">
         <is>
           <t>Depth: Independently builds standard network topologies, manages routing and segmentation for routine needs with review.
-Evidenced by: Configures the networking and compute for their component.
-Scope: component.</t>
+Evidenced by: Configures the networking and compute for their component.</t>
         </is>
       </c>
       <c r="I17" s="4" t="inlineStr">
         <is>
           <t>Depth: Designs routing and addressing schemes for ambiguous topologies and diagnoses hard reachability and routing failures.
-Evidenced by: Designs network and compute topology for a capability.
-Scope: capability / domain (terminal level).</t>
+Evidenced by: Designs network and compute topology for a capability.</t>
         </is>
       </c>
       <c r="J17" s="4" t="inlineStr">
         <is>
           <t>Depth: Defines network architecture and routing patterns others adopt, solving deep segmentation, scale, and convergence problems.
-Evidenced by: Owns shared foundations several teams depend on.
-Scope: multiple teams.</t>
+Evidenced by: Owns shared foundations several teams depend on.</t>
         </is>
       </c>
       <c r="K17" s="4" t="inlineStr">
         <is>
           <t>Depth: Sets organization-wide network strategy and standards, anticipating shifts in network design and routing.
-Evidenced by: Sets organization standards for network architecture and compute platforms.
-Scope: organization.</t>
+Evidenced by: Sets organization standards for network architecture and compute platforms.</t>
         </is>
       </c>
       <c r="L17" s="4" t="inlineStr">
         <is>
           <t>Depth: Defines what good network design means for the field, externally credible in shaping routing practice.
-Evidenced by: Owns company-scale foundation decisions.
-Scope: company.</t>
+Evidenced by: Owns company-scale foundation decisions.</t>
         </is>
       </c>
     </row>
@@ -1993,43 +1897,37 @@
       <c r="G18" s="4" t="inlineStr">
         <is>
           <t>Depth: Writes simple declarative resource definitions from templates, applying them under review in non-production environments.
-Evidenced by: Makes changes through the IaC workflow rather than the console.
-Scope: task.</t>
+Evidenced by: Makes changes through the IaC workflow rather than the console.</t>
         </is>
       </c>
       <c r="H18" s="4" t="inlineStr">
         <is>
           <t>Depth: Independently provisions standard infrastructure stacks, manages state and variables, and handles routine drift with normal review.
-Evidenced by: Writes reusable, parameterized modules for their component.
-Scope: component.</t>
+Evidenced by: Writes reusable, parameterized modules for their component.</t>
         </is>
       </c>
       <c r="I18" s="4" t="inlineStr">
         <is>
           <t>Depth: Designs reusable modules for ambiguous needs, structures state safely, and is the go-to for tricky provisioning failures.
-Evidenced by: Designs the IaC architecture for a capability.
-Scope: capability / domain (terminal level).</t>
+Evidenced by: Designs the IaC architecture for a capability.</t>
         </is>
       </c>
       <c r="J18" s="4" t="inlineStr">
         <is>
           <t>Depth: Defines the provisioning patterns and module conventions others adopt, solving thorny dependency and idempotency problems.
-Evidenced by: Publishes module libraries and IaC conventions multiple teams build on.
-Scope: multiple teams.</t>
+Evidenced by: Publishes module libraries and IaC conventions multiple teams build on.</t>
         </is>
       </c>
       <c r="K18" s="4" t="inlineStr">
         <is>
           <t>Depth: Sets the organization-wide IaC strategy, governance, and standards, anticipating shifts in declarative provisioning practice.
-Evidenced by: Sets the organization's IaC standards.
-Scope: organization.</t>
+Evidenced by: Sets the organization's IaC standards.</t>
         </is>
       </c>
       <c r="L18" s="4" t="inlineStr">
         <is>
           <t>Depth: Defines what good infrastructure-as-code means for the field, shaping provisioning practices recognized across the industry.
-Evidenced by: Treats the company's infrastructure definition as a strategic asset.
-Scope: company.</t>
+Evidenced by: Treats the company's infrastructure definition as a strategic asset.</t>
         </is>
       </c>
     </row>
@@ -2067,43 +1965,37 @@
       <c r="G19" s="4" t="inlineStr">
         <is>
           <t>Depth: Maintains existing self-service platform components under review, addressing documented user requests.
-Evidenced by: Uses the self-service tooling as users do and documents the gaps that forced manual steps.
-Scope: task.</t>
+Evidenced by: Uses the self-service tooling as users do and documents the gaps that forced manual steps.</t>
         </is>
       </c>
       <c r="H19" s="4" t="inlineStr">
         <is>
           <t>Depth: Independently builds and supports standard platform capabilities and templates for routine developer needs with review.
-Evidenced by: Automates a manual provisioning flow for their component into a self-service action.
-Scope: component.</t>
+Evidenced by: Automates a manual provisioning flow for their component into a self-service action.</t>
         </is>
       </c>
       <c r="I19" s="4" t="inlineStr">
         <is>
           <t>Depth: Designs self-service workflows for ambiguous needs, reducing friction and resolving hard abstraction and adoption issues.
-Evidenced by: Designs self-service for a capability end to end.
-Scope: capability / domain (terminal level).</t>
+Evidenced by: Designs self-service for a capability end to end.</t>
         </is>
       </c>
       <c r="J19" s="4" t="inlineStr">
         <is>
           <t>Depth: Defines platform architecture and golden paths others adopt, solving deep developer-experience and leverage problems.
-Evidenced by: Unifies self-service across teams behind one coherent interface.
-Scope: multiple teams.</t>
+Evidenced by: Unifies self-service across teams behind one coherent interface.</t>
         </is>
       </c>
       <c r="K19" s="4" t="inlineStr">
         <is>
           <t>Depth: Sets organization-wide platform strategy, anticipating how developer-experience engineering should evolve.
-Evidenced by: Drives the organization to a self-service operating model.
-Scope: organization.</t>
+Evidenced by: Drives the organization to a self-service operating model.</t>
         </is>
       </c>
       <c r="L19" s="4" t="inlineStr">
         <is>
           <t>Depth: Defines what excellent platform engineering means for the field, shaping industry developer-experience practice.
-Evidenced by: Makes self-service the company's default operating model for infrastructure.
-Scope: company.</t>
+Evidenced by: Makes self-service the company's default operating model for infrastructure.</t>
         </is>
       </c>
     </row>
@@ -2141,43 +2033,37 @@
       <c r="G20" s="4" t="inlineStr">
         <is>
           <t>Depth: Understands logs/metrics/traces; reads existing dashboards.
-Evidenced by: Traces a failing deploy to a specific pod's OOM-kill using the team's existing dashboard, without needing a teammate to point them to it.
-Scope: task.</t>
+Evidenced by: Traces a failing deploy to a specific pod's OOM-kill using the team's existing dashboard, without needing a teammate to point them to it.</t>
         </is>
       </c>
       <c r="H20" s="4" t="inlineStr">
         <is>
           <t>Depth: Instruments their services; builds dashboards; tunes alerts to limit noise.
-Evidenced by: Instruments their component so strangers can debug it.
-Scope: component.</t>
+Evidenced by: Instruments their component so strangers can debug it.</t>
         </is>
       </c>
       <c r="I20" s="4" t="inlineStr">
         <is>
           <t>Depth: Designs observability for complex systems (end-to-end traces, quality signals, cost attribution).
-Evidenced by: Designs the observability offering for a capability.
-Scope: capability / domain (terminal level).</t>
+Evidenced by: Designs the observability offering for a capability.</t>
         </is>
       </c>
       <c r="J20" s="4" t="inlineStr">
         <is>
           <t>Depth: Expert in instrumentation trade-offs at scale, incl. privacy-safe logging.
-Evidenced by: Builds observability infrastructure multiple teams instrument against.
-Scope: multiple teams.</t>
+Evidenced by: Builds observability infrastructure multiple teams instrument against.</t>
         </is>
       </c>
       <c r="K20" s="4" t="inlineStr">
         <is>
           <t>Depth: Defines org observability strategy.
-Evidenced by: Sets the organization's observability strategy and standards.
-Scope: organization.</t>
+Evidenced by: Sets the organization's observability strategy and standards.</t>
         </is>
       </c>
       <c r="L20" s="4" t="inlineStr">
         <is>
           <t>Depth: Shapes company-wide operational visibility; advances practice.
-Evidenced by: Frames observability as company capability.
-Scope: company.</t>
+Evidenced by: Frames observability as company capability.</t>
         </is>
       </c>
     </row>
@@ -2215,43 +2101,37 @@
       <c r="G21" s="4" t="inlineStr">
         <is>
           <t>Depth: Understands SLOs and common failure modes; keeps components healthy with guidance.
-Evidenced by: Explains their service's SLOs and reads burn-rate dashboards correctly.
-Scope: task.</t>
+Evidenced by: Explains their service's SLOs and reads burn-rate dashboards correctly.</t>
         </is>
       </c>
       <c r="H21" s="4" t="inlineStr">
         <is>
           <t>Depth: Builds retries, timeouts and fallbacks; understands blast radius.
-Evidenced by: Adds a retry-with-backoff and a fallback path to a flaky downstream call so that dependency's failure doesn't cascade into their own component.
-Scope: component.</t>
+Evidenced by: Adds a retry-with-backoff and a fallback path to a flaky downstream call so that dependency's failure doesn't cascade into their own component.</t>
         </is>
       </c>
       <c r="I21" s="4" t="inlineStr">
         <is>
           <t>Depth: Designs for graceful degradation; defines SLOs; accountable for a domain's reliability.
-Evidenced by: Negotiates SLOs for a capability with its internal customers.
-Scope: capability / domain (terminal level).</t>
+Evidenced by: Negotiates SLOs for a capability with its internal customers.</t>
         </is>
       </c>
       <c r="J21" s="4" t="inlineStr">
         <is>
           <t>Depth: Expert in resilience and capacity planning at scale; drives down incidents systemically.
-Evidenced by: Aligns SLOs across dependent services so promises compose.
-Scope: multiple teams.</t>
+Evidenced by: Aligns SLOs across dependent services so promises compose.</t>
         </is>
       </c>
       <c r="K21" s="4" t="inlineStr">
         <is>
           <t>Depth: Owns org-level reliability; fixes risk in process and org design.
-Evidenced by: Owns the organization's SLO framework and review cadence.
-Scope: organization.</t>
+Evidenced by: Owns the organization's SLO framework and review cadence.</t>
         </is>
       </c>
       <c r="L21" s="4" t="inlineStr">
         <is>
           <t>Depth: Sets the company's reliability philosophy.
-Evidenced by: Sets company reliability targets against business risk and cost.
-Scope: company.</t>
+Evidenced by: Sets company reliability targets against business risk and cost.</t>
         </is>
       </c>
     </row>
@@ -2289,43 +2169,37 @@
       <c r="G22" s="4" t="inlineStr">
         <is>
           <t>Depth: Responds to alerts with support; follows runbooks; escalates appropriately.
-Evidenced by: Executes runbook steps accurately during incidents under supervision.
-Scope: task.</t>
+Evidenced by: Executes runbook steps accurately during incidents under supervision.</t>
         </is>
       </c>
       <c r="H22" s="4" t="inlineStr">
         <is>
           <t>Depth: Triages and resolves routine incidents; clear notes; takes on-call.
-Evidenced by: Serves as primary on-call for their component.
-Scope: component.</t>
+Evidenced by: Serves as primary on-call for their component.</t>
         </is>
       </c>
       <c r="I22" s="4" t="inlineStr">
         <is>
           <t>Depth: Leads response to complex failures; blameless postmortems; same failure never recurs.
-Evidenced by: Commands complex multi-team incidents.
-Scope: capability / domain (terminal level).</t>
+Evidenced by: Commands complex multi-team incidents.</t>
         </is>
       </c>
       <c r="J22" s="4" t="inlineStr">
         <is>
           <t>Depth: Expert in incident-management design (rotations, severity, escalation).
-Evidenced by: Designs the incident-management system itself.
-Scope: multiple teams.</t>
+Evidenced by: Designs the incident-management system itself.</t>
         </is>
       </c>
       <c r="K22" s="4" t="inlineStr">
         <is>
           <t>Depth: Commands the highest-severity incidents; sets incident process org-wide.
-Evidenced by: Owns the organization's major-incident readiness.
-Scope: organization.</t>
+Evidenced by: Owns the organization's major-incident readiness.</t>
         </is>
       </c>
       <c r="L22" s="4" t="inlineStr">
         <is>
           <t>Depth: Sets the company's incident philosophy; calm authority in the worst moments.
-Evidenced by: Leads the company's existential incidents and the reforms after them.
-Scope: company.</t>
+Evidenced by: Leads the company's existential incidents and the reforms after them.</t>
         </is>
       </c>
     </row>
@@ -2363,43 +2237,37 @@
       <c r="G23" s="4" t="inlineStr">
         <is>
           <t>Depth: Responds to alerts with support; follows runbooks; escalates appropriately.
-Evidenced by: Contributes accurate timelines and observations to incident reviews.
-Scope: task.</t>
+Evidenced by: Contributes accurate timelines and observations to incident reviews.</t>
         </is>
       </c>
       <c r="H23" s="4" t="inlineStr">
         <is>
           <t>Depth: Triages and resolves routine incidents; clear notes; takes on-call.
-Evidenced by: Writes blameless postmortems for their component's incidents.
-Scope: component.</t>
+Evidenced by: Writes blameless postmortems for their component's incidents.</t>
         </is>
       </c>
       <c r="I23" s="4" t="inlineStr">
         <is>
           <t>Depth: Leads response to complex failures; blameless postmortems; same failure never recurs.
-Evidenced by: Facilitates incident reviews others attend voluntarily.
-Scope: capability / domain (terminal level).</t>
+Evidenced by: Facilitates incident reviews others attend voluntarily.</t>
         </is>
       </c>
       <c r="J23" s="4" t="inlineStr">
         <is>
           <t>Depth: Expert in incident-management design (rotations, severity, escalation).
-Evidenced by: Builds the learning system across teams.
-Scope: multiple teams.</t>
+Evidenced by: Builds the learning system across teams.</t>
         </is>
       </c>
       <c r="K23" s="4" t="inlineStr">
         <is>
           <t>Depth: Commands the highest-severity incidents; sets incident process org-wide.
-Evidenced by: Drives org-level resilience investment from incident evidence.
-Scope: organization.</t>
+Evidenced by: Drives org-level resilience investment from incident evidence.</t>
         </is>
       </c>
       <c r="L23" s="4" t="inlineStr">
         <is>
           <t>Depth: Sets the company's incident philosophy; calm authority in the worst moments.
-Evidenced by: Shapes the company's safety culture.
-Scope: company.</t>
+Evidenced by: Shapes the company's safety culture.</t>
         </is>
       </c>
     </row>
@@ -2437,43 +2305,37 @@
       <c r="G24" s="4" t="inlineStr">
         <is>
           <t>Depth: Understands cost/latency drivers of what they build.
-Evidenced by: Reads utilization and saturation dashboards correctly and flags approaching limits with evidence.
-Scope: task.</t>
+Evidenced by: Reads utilization and saturation dashboards correctly and flags approaching limits with evidence.</t>
         </is>
       </c>
       <c r="H24" s="4" t="inlineStr">
         <is>
           <t>Depth: Applies standard optimizations; stays within cost/latency budgets.
-Evidenced by: Load-tests their component and sizes it from measured headroom rather than guesswork.
-Scope: component.</t>
+Evidenced by: Load-tests their component and sizes it from measured headroom rather than guesswork.</t>
         </is>
       </c>
       <c r="I24" s="4" t="inlineStr">
         <is>
           <t>Depth: Designs cost-aware architectures; defines and tracks unit economics for a domain.
-Evidenced by: Owns capacity planning for a capability.
-Scope: capability / domain (terminal level).</t>
+Evidenced by: Owns capacity planning for a capability.</t>
         </is>
       </c>
       <c r="J24" s="4" t="inlineStr">
         <is>
           <t>Depth: Expert in economics at scale (fleet optimization, build-vs-buy).
-Evidenced by: Runs capacity planning across shared pools that multiple teams draw from.
-Scope: multiple teams.</t>
+Evidenced by: Runs capacity planning across shared pools that multiple teams draw from.</t>
         </is>
       </c>
       <c r="K24" s="4" t="inlineStr">
         <is>
           <t>Depth: Owns org-level spend strategy; cost decisions change margins.
-Evidenced by: Owns the organization's capacity and efficiency program.
-Scope: organization.</t>
+Evidenced by: Owns the organization's capacity and efficiency program.</t>
         </is>
       </c>
       <c r="L24" s="4" t="inlineStr">
         <is>
           <t>Depth: Shapes the company economics of the products.
-Evidenced by: Treats infrastructure economics as company strategy.
-Scope: company.</t>
+Evidenced by: Treats infrastructure economics as company strategy.</t>
         </is>
       </c>
     </row>
@@ -2511,43 +2373,37 @@
       <c r="G25" s="4" t="inlineStr">
         <is>
           <t>Depth: Runs and lightly edits existing automation under review, flagging tasks that remain manual.
-Evidenced by: Executes operational runbooks accurately and improves the runbook when a step is wrong or missing.
-Scope: task.</t>
+Evidenced by: Executes operational runbooks accurately and improves the runbook when a step is wrong or missing.</t>
         </is>
       </c>
       <c r="H25" s="4" t="inlineStr">
         <is>
           <t>Depth: Independently automates routine operational tasks and integrates them into standard workflows with normal review.
-Evidenced by: Automates the recurring manual work in their component.
-Scope: component.</t>
+Evidenced by: Automates the recurring manual work in their component.</t>
         </is>
       </c>
       <c r="I25" s="4" t="inlineStr">
         <is>
           <t>Depth: Designs automation for ambiguous, error-prone toil and resolves hard reliability and orchestration issues in pipelines.
-Evidenced by: Measures toil for a capability and holds it under an explicit budget.
-Scope: capability / domain (terminal level).</t>
+Evidenced by: Measures toil for a capability and holds it under an explicit budget.</t>
         </is>
       </c>
       <c r="J25" s="4" t="inlineStr">
         <is>
           <t>Depth: Defines automation patterns and toil-elimination practices others adopt, solving deep workflow and safety problems.
-Evidenced by: Builds automation multiple teams reuse for their operational work.
-Scope: multiple teams.</t>
+Evidenced by: Builds automation multiple teams reuse for their operational work.</t>
         </is>
       </c>
       <c r="K25" s="4" t="inlineStr">
         <is>
           <t>Depth: Sets organization-wide automation strategy, anticipating where automation-first operations should head.
-Evidenced by: Sets the organization's toil policy.
-Scope: organization.</t>
+Evidenced by: Sets the organization's toil policy.</t>
         </is>
       </c>
       <c r="L25" s="4" t="inlineStr">
         <is>
           <t>Depth: Defines what automation-first operations means for the discipline, externally credible in shaping the practice.
-Evidenced by: Makes operational leverage a company-level argument.
-Scope: company.</t>
+Evidenced by: Makes operational leverage a company-level argument.</t>
         </is>
       </c>
     </row>
@@ -2585,43 +2441,37 @@
       <c r="G26" s="4" t="inlineStr">
         <is>
           <t>Depth: Works within existing guardrails, reads a policy violation to its cause instead of requesting an exception, and explains what each guardrail protects against.
-Evidenced by: Traces a blocked deploy to a missing resource-limit field in the manifest instead of filing an exception request, and fixes it.
-Scope: task.</t>
+Evidenced by: Traces a blocked deploy to a missing resource-limit field in the manifest instead of filing an exception request, and fixes it.</t>
         </is>
       </c>
       <c r="H26" s="4" t="inlineStr">
         <is>
           <t>Depth: Writes and tests policy rules for a component - admission checks, pipeline gates - with low false-positive rates and violation messages that tell the user how to comply.
-Evidenced by: Writes an admission-control rule for their component that catches unencrypted volumes with a message that tells the requester exactly which field to change.
-Scope: component.</t>
+Evidenced by: Writes an admission-control rule for their component that catches unencrypted volumes with a message that tells the requester exactly which field to change.</t>
         </is>
       </c>
       <c r="I26" s="4" t="inlineStr">
         <is>
           <t>Depth: Designs the guardrail architecture for a capability - what is blocked, warned, or audited, with documented threat reasoning - tuned so the safe path is the fast path, and runs an audited exception workflow without becoming the bottleneck.
-Evidenced by: Designs a capability's guardrail set -- what blocks, what warns, what only audits -- with the threat each rule defends against written down, and runs the exception process without becoming its bottleneck.
-Scope: capability / domain (terminal level).</t>
+Evidenced by: Designs a capability's guardrail set -- what blocks, what warns, what only audits -- with the threat each rule defends against written down, and runs the exception process without becoming its bottleneck.</t>
         </is>
       </c>
       <c r="J26" s="4" t="inlineStr">
         <is>
           <t>Depth: Harmonizes policy across teams into a coherent, versioned policy library with a governed exception process, and adjudicates escalated safety-versus-velocity disputes.
-Evidenced by: Merges three teams' near-duplicate policy libraries into one versioned set and adjudicates which team's stricter rule wins.
-Scope: multiple teams.</t>
+Evidenced by: Merges three teams' near-duplicate policy libraries into one versioned set and adjudicates which team's stricter rule wins.</t>
         </is>
       </c>
       <c r="K26" s="4" t="inlineStr">
         <is>
           <t>Depth: Owns an organization's preventive-control strategy with security partners - the control catalog, its coverage, and the evidence it works - moving enforcement from review-time to platform-time.
-Evidenced by: Owns the guardrail catalog with the security team, moving a manual pre-launch review into an automated pipeline gate.
-Scope: organization.</t>
+Evidenced by: Owns the guardrail catalog with the security team, moving a manual pre-launch review into an automated pipeline gate.</t>
         </is>
       </c>
       <c r="L26" s="4" t="inlineStr">
         <is>
           <t>Depth: Sets an organization-defining balance of enablement and control, accountable for guardrails that hold under audit and attack without throttling delivery.
-Evidenced by: Sets the company's default posture on where automation blocks versus warns, and defends it to auditors after an incident nearly reopens the debate.
-Scope: company.</t>
+Evidenced by: Sets the company's default posture on where automation blocks versus warns, and defends it to auditors after an incident nearly reopens the debate.</t>
         </is>
       </c>
     </row>
@@ -2659,43 +2509,37 @@
       <c r="G27" s="4" t="inlineStr">
         <is>
           <t>Depth: Provisions and deprovisions accounts from documented procedures, with approvals and access reviewed before activation.
-Evidenced by: Requests and uses credentials through the sanctioned workflow.
-Scope: task.</t>
+Evidenced by: Requests and uses credentials through the sanctioned workflow.</t>
         </is>
       </c>
       <c r="H27" s="4" t="inlineStr">
         <is>
           <t>Depth: Configures roles, group membership, and authentication factors independently for standard joiners, movers, and leavers.
-Evidenced by: Configures workload identity, scoped roles, and secret rotation for their component.
-Scope: component.</t>
+Evidenced by: Configures workload identity, scoped roles, and secret rotation for their component.</t>
         </is>
       </c>
       <c r="I27" s="4" t="inlineStr">
         <is>
           <t>Depth: Resolves complex entitlement conflicts and designs least-privilege role models for ambiguous, cross-system access needs.
-Evidenced by: Designs the identity model for a capability.
-Scope: capability / domain (terminal level).</t>
+Evidenced by: Designs the identity model for a capability.</t>
         </is>
       </c>
       <c r="J27" s="4" t="inlineStr">
         <is>
           <t>Depth: Defines the identity lifecycle and authorization architecture that other engineers adopt across the organization.
-Evidenced by: Builds identity infrastructure multiple teams authenticate through.
-Scope: multiple teams.</t>
+Evidenced by: Builds identity infrastructure multiple teams authenticate through.</t>
         </is>
       </c>
       <c r="K27" s="4" t="inlineStr">
         <is>
           <t>Depth: Sets identity strategy, governs federation and privileged-access standards, and anticipates emerging access risks.
-Evidenced by: Owns the organization's identity architecture and its zero-trust roadmap.
-Scope: organization.</t>
+Evidenced by: Owns the organization's identity architecture and its zero-trust roadmap.</t>
         </is>
       </c>
       <c r="L27" s="4" t="inlineStr">
         <is>
           <t>Depth: Defines what sound identity practice means for the field and shapes how others govern access.
-Evidenced by: Sets company identity strategy across employee, workload, and customer boundaries.
-Scope: company.</t>
+Evidenced by: Sets company identity strategy across employee, workload, and customer boundaries.</t>
         </is>
       </c>
     </row>
@@ -2733,43 +2577,37 @@
       <c r="G28" s="4" t="inlineStr">
         <is>
           <t>Depth: Verifies artifact provenance and signatures following documented checks, escalating anomalies for review.
-Evidenced by: Keeps dependencies current on their tasks and acts on vulnerability-scanner findings with guidance.
-Scope: task.</t>
+Evidenced by: Keeps dependencies current on their tasks and acts on vulnerability-scanner findings with guidance.</t>
         </is>
       </c>
       <c r="H28" s="4" t="inlineStr">
         <is>
           <t>Depth: Configures signing, dependency scanning, and provenance controls independently for standard pipelines.
-Evidenced by: Maintains their component's supply-chain hygiene.
-Scope: component.</t>
+Evidenced by: Maintains their component's supply-chain hygiene.</t>
         </is>
       </c>
       <c r="I28" s="4" t="inlineStr">
         <is>
           <t>Depth: Designs artifact-integrity and dependency-trust controls for complex, ambiguous supply chains.
-Evidenced by: Designs a capability's pipeline to a stated supply-chain integrity level.
-Scope: capability / domain (terminal level).</t>
+Evidenced by: Designs a capability's pipeline to a stated supply-chain integrity level.</t>
         </is>
       </c>
       <c r="J28" s="4" t="inlineStr">
         <is>
           <t>Depth: Defines the supply-chain security architecture and verification patterns others adopt.
-Evidenced by: Builds supply-chain controls into the shared pipeline so every team inherits provenance and scanning by default.
-Scope: multiple teams.</t>
+Evidenced by: Builds supply-chain controls into the shared pipeline so every team inherits provenance and scanning by default.</t>
         </is>
       </c>
       <c r="K28" s="4" t="inlineStr">
         <is>
           <t>Depth: Sets supply-chain assurance strategy and anticipates emerging artifact and dependency threats.
-Evidenced by: Owns the organization's supply-chain security program.
-Scope: organization.</t>
+Evidenced by: Owns the organization's supply-chain security program.</t>
         </is>
       </c>
       <c r="L28" s="4" t="inlineStr">
         <is>
           <t>Depth: Defines authoritative supply-chain security practice that shapes industry expectations.
-Evidenced by: Sets company supply-chain policy including third-party and vendor software.
-Scope: company.</t>
+Evidenced by: Sets company supply-chain policy including third-party and vendor software.</t>
         </is>
       </c>
     </row>
@@ -2807,43 +2645,37 @@
       <c r="G29" s="4" t="inlineStr">
         <is>
           <t>Depth: Knows data handling has privacy implications; follows rules.
-Evidenced by: Follows the platform's compliance procedures accurately.
-Scope: task.</t>
+Evidenced by: Follows the platform's compliance procedures accurately.</t>
         </is>
       </c>
       <c r="H29" s="4" t="inlineStr">
         <is>
           <t>Depth: Applies PII handling, redaction, residency and retention correctly.
-Evidenced by: Automates evidence collection for their component's controls.
-Scope: component.</t>
+Evidenced by: Automates evidence collection for their component's controls.</t>
         </is>
       </c>
       <c r="I29" s="4" t="inlineStr">
         <is>
           <t>Depth: Designs for compliance (consent, audit trails, regional rules); owns readiness for a domain.
-Evidenced by: Maps a capability's controls to the frameworks the company answers to and designs them to be inherited.
-Scope: capability / domain (terminal level).</t>
+Evidenced by: Maps a capability's controls to the frameworks the company answers to and designs them to be inherited.</t>
         </is>
       </c>
       <c r="J29" s="4" t="inlineStr">
         <is>
           <t>Depth: Expert at translating regulation into controls; represents engineering in audits.
-Evidenced by: Rationalizes overlapping control implementations across teams into shared, platform-enforced controls.
-Scope: multiple teams.</t>
+Evidenced by: Rationalizes overlapping control implementations across teams into shared, platform-enforced controls.</t>
         </is>
       </c>
       <c r="K29" s="4" t="inlineStr">
         <is>
           <t>Depth: Sets org compliance strategy; anticipates regulation.
-Evidenced by: Owns the organization's compliance-as-code strategy with legal and security partners.
-Scope: organization.</t>
+Evidenced by: Owns the organization's compliance-as-code strategy with legal and security partners.</t>
         </is>
       </c>
       <c r="L29" s="4" t="inlineStr">
         <is>
           <t>Depth: Authoritative on the landscape; trusted interface to regulators.
-Evidenced by: Shapes company posture on regulatory strategy where infrastructure is implicated.
-Scope: company.</t>
+Evidenced by: Shapes company posture on regulatory strategy where infrastructure is implicated.</t>
         </is>
       </c>
     </row>
@@ -2881,43 +2713,37 @@
       <c r="G30" s="4" t="inlineStr">
         <is>
           <t>Depth: Writes and updates doc pages within an existing structure under guidance.
-Evidenced by: Fixes documentation errors they hit instead of working around them.
-Scope: task.</t>
+Evidenced by: Fixes documentation errors they hit instead of working around them.</t>
         </is>
       </c>
       <c r="H30" s="4" t="inlineStr">
         <is>
           <t>Depth: Authors and organizes documentation for a product area with normal review.
-Evidenced by: Keeps their component's docs shippable.
-Scope: component.</t>
+Evidenced by: Keeps their component's docs shippable.</t>
         </is>
       </c>
       <c r="I30" s="4" t="inlineStr">
         <is>
           <t>Depth: Independently architects coherent doc structures for complex, evolving products.
-Evidenced by: Designs a capability's documentation as part of the product.
-Scope: capability / domain (terminal level).</t>
+Evidenced by: Designs a capability's documentation as part of the product.</t>
         </is>
       </c>
       <c r="J30" s="4" t="inlineStr">
         <is>
           <t>Depth: Defines information-architecture standards others adopt and restructures tangled doc sets.
-Evidenced by: Sets documentation conventions multiple teams follow.
-Scope: multiple teams.</t>
+Evidenced by: Sets documentation conventions multiple teams follow.</t>
         </is>
       </c>
       <c r="K30" s="4" t="inlineStr">
         <is>
           <t>Depth: Sets the org's documentation strategy and anticipates structural scaling needs.
-Evidenced by: Owns the organization's developer-facing knowledge strategy.
-Scope: organization.</t>
+Evidenced by: Owns the organization's developer-facing knowledge strategy.</t>
         </is>
       </c>
       <c r="L30" s="4" t="inlineStr">
         <is>
           <t>Depth: Defines great developer documentation and information architecture for the field.
-Evidenced by: Writes the canonical company documents.
-Scope: company.</t>
+Evidenced by: Writes the canonical company documents.</t>
         </is>
       </c>
     </row>
@@ -2955,43 +2781,37 @@
       <c r="G31" s="4" t="inlineStr">
         <is>
           <t>Depth: Communicates status clearly; documentation is accurate.
-Evidenced by: Writes clear tickets, PR descriptions, and status updates that need no follow-up questions.
-Scope: task.</t>
+Evidenced by: Writes clear tickets, PR descriptions, and status updates that need no follow-up questions.</t>
         </is>
       </c>
       <c r="H31" s="4" t="inlineStr">
         <is>
           <t>Depth: Writes clear design notes, runbooks and PRs; explains trade-offs without overselling.
-Evidenced by: Writes short design docs that state the problem, options, and recommendation.
-Scope: component.</t>
+Evidenced by: Writes short design docs that state the problem, options, and recommendation.</t>
         </is>
       </c>
       <c r="I31" s="4" t="inlineStr">
         <is>
           <t>Depth: Writes design docs that drive decisions; translates technical risk for non-technical stakeholders.
-Evidenced by: Writes design docs that make complex trade-offs decidable by non-experts.
-Scope: capability / domain (terminal level).</t>
+Evidenced by: Writes design docs that make complex trade-offs decidable by non-experts.</t>
         </is>
       </c>
       <c r="J31" s="4" t="inlineStr">
         <is>
           <t>Depth: Expert at making complex capability/risk legible to executives without dumbing it down; RFCs align orgs.
-Evidenced by: Writes the cross-team proposals that settle contested technical questions.
-Scope: multiple teams.</t>
+Evidenced by: Writes the cross-team proposals that settle contested technical questions.</t>
         </is>
       </c>
       <c r="K31" s="4" t="inlineStr">
         <is>
           <t>Depth: Strategy memos leadership acts on; org-wide and external reach.
-Evidenced by: Sets the organization's bar for decision writing.
-Scope: organization.</t>
+Evidenced by: Sets the organization's bar for decision writing.</t>
         </is>
       </c>
       <c r="L31" s="4" t="inlineStr">
         <is>
           <t>Depth: A clarifying voice at company scale; externally recognized.
-Evidenced by: Communicates deep technical trade-offs to executives in the language of business risk without losing correctness.
-Scope: company.</t>
+Evidenced by: Communicates deep technical trade-offs to executives in the language of business risk without losing correctness.</t>
         </is>
       </c>
     </row>
@@ -3029,43 +2849,37 @@
       <c r="G32" s="4" t="inlineStr">
         <is>
           <t>Depth: Engages community channels and answers routine questions under guidance.
-Evidenced by: Answers user questions in support channels accurately or routes them fast.
-Scope: task.</t>
+Evidenced by: Answers user questions in support channels accurately or routes them fast.</t>
         </is>
       </c>
       <c r="H32" s="4" t="inlineStr">
         <is>
           <t>Depth: Grows and supports a developer community segment with normal review.
-Evidenced by: Runs enablement for their component.
-Scope: component.</t>
+Evidenced by: Runs enablement for their component.</t>
         </is>
       </c>
       <c r="I32" s="4" t="inlineStr">
         <is>
           <t>Depth: Independently builds thriving communities and defuses tense community conflicts.
-Evidenced by: Drives adoption of a capability through evangelism rather than mandate.
-Scope: capability / domain (terminal level).</t>
+Evidenced by: Drives adoption of a capability through evangelism rather than mandate.</t>
         </is>
       </c>
       <c r="J32" s="4" t="inlineStr">
         <is>
           <t>Depth: Defines community-building practices others adopt and revives flagging communities.
-Evidenced by: Builds the enablement machinery platform teams share.
-Scope: multiple teams.</t>
+Evidenced by: Builds the enablement machinery platform teams share.</t>
         </is>
       </c>
       <c r="K32" s="4" t="inlineStr">
         <is>
           <t>Depth: Sets the org's community strategy and anticipates where developer interest is shifting.
-Evidenced by: Owns the platform's internal brand and narrative.
-Scope: organization.</t>
+Evidenced by: Owns the platform's internal brand and narrative.</t>
         </is>
       </c>
       <c r="L32" s="4" t="inlineStr">
         <is>
           <t>Depth: Defines what great developer advocacy means and is externally recognized for it.
-Evidenced by: Represents the company's engineering platform externally.
-Scope: company.</t>
+Evidenced by: Represents the company's engineering platform externally.</t>
         </is>
       </c>
     </row>
@@ -3103,43 +2917,37 @@
       <c r="G33" s="4" t="inlineStr">
         <is>
           <t>Depth: Prepares updates and gathers input for stakeholders under direction.
-Evidenced by: Communicates status honestly and early - especially bad news.
-Scope: task.</t>
+Evidenced by: Communicates status honestly and early - especially bad news.</t>
         </is>
       </c>
       <c r="H33" s="4" t="inlineStr">
         <is>
           <t>Depth: Manages routine stakeholder relationships and communications with normal review.
-Evidenced by: Manages expectations for their component with its consuming teams.
-Scope: component.</t>
+Evidenced by: Manages expectations for their component with its consuming teams.</t>
         </is>
       </c>
       <c r="I33" s="4" t="inlineStr">
         <is>
           <t>Depth: Independently aligns conflicting stakeholders and navigates tense executive conversations.
-Evidenced by: Runs the stakeholder relationships for a capability.
-Scope: capability / domain (terminal level).</t>
+Evidenced by: Runs the stakeholder relationships for a capability.</t>
         </is>
       </c>
       <c r="J33" s="4" t="inlineStr">
         <is>
           <t>Depth: Defines stakeholder-engagement approaches others adopt and brokers the hardest alignment.
-Evidenced by: Aligns competing demands from multiple teams into a roadmap each can live with.
-Scope: multiple teams.</t>
+Evidenced by: Aligns competing demands from multiple teams into a roadmap each can live with.</t>
         </is>
       </c>
       <c r="K33" s="4" t="inlineStr">
         <is>
           <t>Depth: Sets executive-engagement strategy and anticipates leadership concerns before they arise.
-Evidenced by: Manages the platform's relationship with organization leadership.
-Scope: organization.</t>
+Evidenced by: Manages the platform's relationship with organization leadership.</t>
         </is>
       </c>
       <c r="L33" s="4" t="inlineStr">
         <is>
           <t>Depth: Defines exemplary stakeholder management for the discipline and is externally credible on it.
-Evidenced by: Operates at executive level as the technical counterpart on company decisions that touch the platform.
-Scope: company.</t>
+Evidenced by: Operates at executive level as the technical counterpart on company decisions that touch the platform.</t>
         </is>
       </c>
     </row>
@@ -3177,43 +2985,37 @@
       <c r="G34" s="4" t="inlineStr">
         <is>
           <t>Depth: Responsive to feedback; pairs willingly; asks for help appropriately.
-Evidenced by: Works in the open.
-Scope: task.</t>
+Evidenced by: Works in the open.</t>
         </is>
       </c>
       <c r="H34" s="4" t="inlineStr">
         <is>
           <t>Depth: Collaborates smoothly with adjacent functions; handles disagreement constructively.
-Evidenced by: Partners directly with the teams that consume their component.
-Scope: component.</t>
+Evidenced by: Partners directly with the teams that consume their component.</t>
         </is>
       </c>
       <c r="I34" s="4" t="inlineStr">
         <is>
           <t>Depth: Builds strong cross-team relationships; resolves friction directly.
-Evidenced by: Builds the working relationships a capability depends on.
-Scope: capability / domain (terminal level).</t>
+Evidenced by: Builds the working relationships a capability depends on.</t>
         </is>
       </c>
       <c r="J34" s="4" t="inlineStr">
         <is>
           <t>Depth: Expert at aligning teams with competing priorities; mediates disputes between senior people.
-Evidenced by: Creates the collaboration structures that let teams decide without escalation.
-Scope: multiple teams.</t>
+Evidenced by: Creates the collaboration structures that let teams decide without escalation.</t>
         </is>
       </c>
       <c r="K34" s="4" t="inlineStr">
         <is>
           <t>Depth: Creates the forums and processes through which collaboration happens.
-Evidenced by: Brokers alignment between organizations.
-Scope: organization.</t>
+Evidenced by: Brokers alignment between organizations.</t>
         </is>
       </c>
       <c r="L34" s="4" t="inlineStr">
         <is>
           <t>Depth: Builds coalitions at company scale and externally.
-Evidenced by: Aligns the company's technical factions.
-Scope: company.</t>
+Evidenced by: Aligns the company's technical factions.</t>
         </is>
       </c>
     </row>
@@ -3251,43 +3053,37 @@
       <c r="G35" s="4" t="inlineStr">
         <is>
           <t>Depth: Learns to estimate; surfaces blockers; plans own tasks with guidance.
-Evidenced by: Breaks an assigned task into steps, estimates them honestly, and flags slippage as soon as it is visible.
-Scope: task.</t>
+Evidenced by: Breaks an assigned task into steps, estimates them honestly, and flags slippage as soon as it is visible.</t>
         </is>
       </c>
       <c r="H35" s="4" t="inlineStr">
         <is>
           <t>Depth: Estimates scoped work realistically; plans own 1-3 week projects.
-Evidenced by: Plans component-level work in increments that ship value early.
-Scope: component.</t>
+Evidenced by: Plans component-level work in increments that ship value early.</t>
         </is>
       </c>
       <c r="I35" s="4" t="inlineStr">
         <is>
           <t>Depth: Plans quarter-scale, multi-workstream efforts including dependencies.
-Evidenced by: Plans a capability across quarters with explicit risk buffers.
-Scope: capability / domain (terminal level).</t>
+Evidenced by: Plans a capability across quarters with explicit risk buffers.</t>
         </is>
       </c>
       <c r="J35" s="4" t="inlineStr">
         <is>
           <t>Depth: Expert at planning large programs; anticipates risk early.
-Evidenced by: Builds plans that coordinate multiple teams' streams.
-Scope: multiple teams.</t>
+Evidenced by: Builds plans that coordinate multiple teams' streams.</t>
         </is>
       </c>
       <c r="K35" s="4" t="inlineStr">
         <is>
           <t>Depth: Plans org-level programs across quarters/years.
-Evidenced by: Runs the organization's platform planning cycle.
-Scope: organization.</t>
+Evidenced by: Runs the organization's platform planning cycle.</t>
         </is>
       </c>
       <c r="L35" s="4" t="inlineStr">
         <is>
           <t>Depth: Shapes how the company plans major technical change.
-Evidenced by: Sets the multi-year planning cycle major technical bets are sequenced against, and defends the sequencing to the executives funding it.
-Scope: company.</t>
+Evidenced by: Sets the multi-year planning cycle major technical bets are sequenced against, and defends the sequencing to the executives funding it.</t>
         </is>
       </c>
     </row>
@@ -3325,43 +3121,37 @@
       <c r="G36" s="4" t="inlineStr">
         <is>
           <t>Depth: Works highest-priority-first when told the priorities.
-Evidenced by: Works their queue in the agreed order and raises it explicitly when a new ask conflicts with committed work.
-Scope: task.</t>
+Evidenced by: Works their queue in the agreed order and raises it explicitly when a new ask conflicts with committed work.</t>
         </is>
       </c>
       <c r="H36" s="4" t="inlineStr">
         <is>
           <t>Depth: Makes sound priority calls within scope; time-boxes uncertain work.
-Evidenced by: Orders their component's backlog by user impact and cost of delay.
-Scope: component.</t>
+Evidenced by: Orders their component's backlog by user impact and cost of delay.</t>
         </is>
       </c>
       <c r="I36" s="4" t="inlineStr">
         <is>
           <t>Depth: Balances cost/value/risk across a domain; resists hype; decisions hold up over months.
-Evidenced by: Sequences a capability's investment across feature work, reliability, migrations, and toil paydown using explicit cost-of-delay reasoning.
-Scope: capability / domain (terminal level).</t>
+Evidenced by: Sequences a capability's investment across feature work, reliability, migrations, and toil paydown using explicit cost-of-delay reasoning.</t>
         </is>
       </c>
       <c r="J36" s="4" t="inlineStr">
         <is>
           <t>Depth: Expert at portfolio-level trade-offs; surfaces hidden assumptions; trusted tiebreaker.
-Evidenced by: Arbitrates priority across teams competing for shared platform capacity.
-Scope: multiple teams.</t>
+Evidenced by: Arbitrates priority across teams competing for shared platform capacity.</t>
         </is>
       </c>
       <c r="K36" s="4" t="inlineStr">
         <is>
           <t>Depth: Sets decision frameworks for the org.
-Evidenced by: Sets the organization's platform investment allocation.
-Scope: organization.</t>
+Evidenced by: Sets the organization's platform investment allocation.</t>
         </is>
       </c>
       <c r="L36" s="4" t="inlineStr">
         <is>
           <t>Depth: Influences company strategic direction through judgment.
-Evidenced by: Advises company leadership on technology sequencing.
-Scope: company.</t>
+Evidenced by: Advises company leadership on technology sequencing.</t>
         </is>
       </c>
     </row>
@@ -3399,43 +3189,37 @@
       <c r="G37" s="4" t="inlineStr">
         <is>
           <t>Depth: Receptive to mentoring; shares what they learn.
-Evidenced by: Asks for help effectively - showing what they tried - and passes on what they learn.
-Scope: task.</t>
+Evidenced by: Asks for help effectively - showing what they tried - and passes on what they learn.</t>
         </is>
       </c>
       <c r="H37" s="4" t="inlineStr">
         <is>
           <t>Depth: Helps onboard teammates; informally mentors juniors.
-Evidenced by: Onboards new teammates with pairing and honest context.
-Scope: component.</t>
+Evidenced by: Onboards new teammates with pairing and honest context.</t>
         </is>
       </c>
       <c r="I37" s="4" t="inlineStr">
         <is>
           <t>Depth: Coaches engineers with growth-oriented feedback; measurably improves a team's skill.
-Evidenced by: Mentors engineers deliberately.
-Scope: capability / domain (terminal level).</t>
+Evidenced by: Mentors engineers deliberately.</t>
         </is>
       </c>
       <c r="J37" s="4" t="inlineStr">
         <is>
           <t>Depth: Develops future leads across teams; shapes hiring and onboarding.
-Evidenced by: Grows senior engineers across teams toward staff scope.
-Scope: multiple teams.</t>
+Evidenced by: Grows senior engineers across teams toward staff scope.</t>
         </is>
       </c>
       <c r="K37" s="4" t="inlineStr">
         <is>
           <t>Depth: Develops senior engineers and leaders; builds culture deliberately.
-Evidenced by: Builds the organization's technical talent systems.
-Scope: organization.</t>
+Evidenced by: Builds the organization's technical talent systems.</t>
         </is>
       </c>
       <c r="L37" s="4" t="inlineStr">
         <is>
           <t>Depth: Develops the next generation of top talent; legacy outlasts tenure.
-Evidenced by: Develops the company's next generation of principal-level technical leaders.
-Scope: company.</t>
+Evidenced by: Develops the company's next generation of principal-level technical leaders.</t>
         </is>
       </c>
     </row>
@@ -3473,43 +3257,37 @@
       <c r="G38" s="4" t="inlineStr">
         <is>
           <t>Depth: Contributes informed opinions in technical discussions.
-Evidenced by: Raises a concrete thundering-herd failure scenario against a proposed retry strategy in a design review, and the design changes because of it.
-Scope: task.</t>
+Evidenced by: Raises a concrete thundering-herd failure scenario against a proposed retry strategy in a design review, and the design changes because of it.</t>
         </is>
       </c>
       <c r="H38" s="4" t="inlineStr">
         <is>
           <t>Depth: Influences component-level decisions through credibility.
-Evidenced by: Proposes direction within their component.
-Scope: component.</t>
+Evidenced by: Proposes direction within their component.</t>
         </is>
       </c>
       <c r="I38" s="4" t="inlineStr">
         <is>
           <t>Depth: Sets technical direction for a domain; others align to their calls.
-Evidenced by: Picks the message-queue technology a capability standardizes on for its next migration cycle, and engineers building on it align their designs to that call without relitigating it.
-Scope: capability / domain (terminal level).</t>
+Evidenced by: Picks the message-queue technology a capability standardizes on for its next migration cycle, and engineers building on it align their designs to that call without relitigating it.</t>
         </is>
       </c>
       <c r="J38" s="4" t="inlineStr">
         <is>
           <t>Depth: Shapes how multiple teams approach problems; trusted tiebreaker.
-Evidenced by: Aligns multiple teams behind a shared technical direction without authority over them.
-Scope: multiple teams.</t>
+Evidenced by: Aligns multiple teams behind a shared technical direction without authority over them.</t>
         </is>
       </c>
       <c r="K38" s="4" t="inlineStr">
         <is>
           <t>Depth: Influences org-wide technical strategy.
-Evidenced by: Writes the organization's technical strategy and makes it operational.
-Scope: organization.</t>
+Evidenced by: Writes the organization's technical strategy and makes it operational.</t>
         </is>
       </c>
       <c r="L38" s="4" t="inlineStr">
         <is>
           <t>Depth: Influences company strategic direction through insight.
-Evidenced by: Sets company-level technical direction.
-Scope: company.</t>
+Evidenced by: Sets company-level technical direction.</t>
         </is>
       </c>
     </row>
